--- a/ejemplos/resultados/departamento.xlsx
+++ b/ejemplos/resultados/departamento.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asignacion" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profesores" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asignaturas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carga por profesor" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura por asignatura" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detalle - Lo que imparte" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="Asignacion">OFFSET(Asignacion!$A$4,0,0,COUNTA(Asignacion!$A$4:$A$34),12)</definedName>
-    <definedName name="Profesores">OFFSET(Profesores!$A$4,0,0,COUNTA(Profesores!$A$4:$A$27),7)</definedName>
-    <definedName name="Asignaturas">OFFSET(Asignaturas!$A$4,0,0,COUNTA(Asignaturas!$A$4:$A$27),12)</definedName>
+    <definedName name="Asignacion">OFFSET('Asignacion'!$A$4,0,0,COUNTA('Asignacion'!$A$4:$A$34),12)</definedName>
+    <definedName name="Profesores">OFFSET('Carga por profesor'!$A$4,0,0,COUNTA('Carga por profesor'!$A$4:$A$27),7)</definedName>
+    <definedName name="Asignaturas">OFFSET('Cobertura por asignatura'!$A$4,0,0,COUNTA('Cobertura por asignatura'!$A$4:$A$27),12)</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -502,23 +503,25 @@
   <sheetPr>
     <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="42" customWidth="1" min="9" max="9"/>
-    <col width="42" customWidth="1" min="10" max="10"/>
-    <col width="42" customWidth="1" min="11" max="11"/>
-    <col width="42" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col hidden="1" width="24" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -589,6 +592,16 @@
           <t>Cuenta</t>
         </is>
       </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>(nivel de las marcas)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -611,31 +624,39 @@
         </is>
       </c>
       <c r="F4" s="3">
-        <f>IF($A4="","",IFERROR(VLOOKUP($B4,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A4=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B4)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B4)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B4)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G4" s="3">
-        <f>IF($A4="","",IF(($C4="Conf"),IFERROR(VLOOKUP($B4,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B4,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A4=""),"",IF(EXACT($C4,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B4)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B4)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B4)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B4)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B4)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B4)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H4" s="3">
-        <f>IF($A4="","",IFERROR(VLOOKUP($E4,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A4=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E4)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E4)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E4)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I4" s="3">
-        <f>IF($A4="","",IF(OR(($E4=""),($B4="")),"",($E4&amp;"|"&amp;$B4)))</f>
+        <f>IF(AND($A4=""),"",IF(OR(($E4=""),($B4="")),"",(IF(ISNUMBER($E4),IF($E4=0,"0",ROUND($E4,9-INT(LOG10(ABS($E4))))&amp;""),$E4&amp;"")&amp;"|"&amp;IF(ISNUMBER($B4),IF($B4=0,"0",ROUND($B4,9-INT(LOG10(ABS($B4))))&amp;""),$B4&amp;""))))</f>
         <v/>
       </c>
       <c r="J4" s="3">
-        <f>IF($A4="","",($B4&amp;" "&amp;$C4&amp;" "&amp;$D4))</f>
+        <f>IF(AND($A4=""),"",(IF(ISNUMBER($B4),IF($B4=0,"0",ROUND($B4,9-INT(LOG10(ABS($B4))))&amp;""),$B4&amp;"")&amp;" "&amp;IF(ISNUMBER($C4),IF($C4=0,"0",ROUND($C4,9-INT(LOG10(ABS($C4))))&amp;""),$C4&amp;"")&amp;" "&amp;IF(ISNUMBER($D4),IF($D4=0,"0",ROUND($D4,9-INT(LOG10(ABS($D4))))&amp;""),$D4&amp;"")))</f>
         <v/>
       </c>
       <c r="K4" s="3">
-        <f>IF($A4="","",IF(($I4=""),"",IFERROR(VLOOKUP($I4,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A4=""),"",IF(EXACT($I4,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I4)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I4)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I4)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L4" s="3">
-        <f>IF($A4="","",IF(AND(NOT(($I4="")),($K4=$J4)),1,0))</f>
+        <f>IF(AND($A4=""),"",IF(AND(NOT(EXACT($I4,"")),EXACT($K4,$J4)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M4" s="3">
+        <f>IF(AND($A4=""),"",MID(IF(AND(NOT(($B4="")),($E4="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N4" s="3">
+        <f>IF(OR(AND(NOT(($B4="")),($E4=""))),2,0)</f>
         <v/>
       </c>
     </row>
@@ -664,31 +685,39 @@
         </is>
       </c>
       <c r="F5" s="3">
-        <f>IF($A5="","",IFERROR(VLOOKUP($B5,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A5=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B5)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B5)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B5)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G5" s="3">
-        <f>IF($A5="","",IF(($C5="Conf"),IFERROR(VLOOKUP($B5,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B5,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A5=""),"",IF(EXACT($C5,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B5)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B5)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B5)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B5)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B5)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B5)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H5" s="3">
-        <f>IF($A5="","",IFERROR(VLOOKUP($E5,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A5=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E5)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E5)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E5)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I5" s="3">
-        <f>IF($A5="","",IF(OR(($E5=""),($B5="")),"",($E5&amp;"|"&amp;$B5)))</f>
+        <f>IF(AND($A5=""),"",IF(OR(($E5=""),($B5="")),"",(IF(ISNUMBER($E5),IF($E5=0,"0",ROUND($E5,9-INT(LOG10(ABS($E5))))&amp;""),$E5&amp;"")&amp;"|"&amp;IF(ISNUMBER($B5),IF($B5=0,"0",ROUND($B5,9-INT(LOG10(ABS($B5))))&amp;""),$B5&amp;""))))</f>
         <v/>
       </c>
       <c r="J5" s="3">
-        <f>IF($A5="","",($B5&amp;" "&amp;$C5&amp;" "&amp;$D5))</f>
+        <f>IF(AND($A5=""),"",(IF(ISNUMBER($B5),IF($B5=0,"0",ROUND($B5,9-INT(LOG10(ABS($B5))))&amp;""),$B5&amp;"")&amp;" "&amp;IF(ISNUMBER($C5),IF($C5=0,"0",ROUND($C5,9-INT(LOG10(ABS($C5))))&amp;""),$C5&amp;"")&amp;" "&amp;IF(ISNUMBER($D5),IF($D5=0,"0",ROUND($D5,9-INT(LOG10(ABS($D5))))&amp;""),$D5&amp;"")))</f>
         <v/>
       </c>
       <c r="K5" s="3">
-        <f>IF($A5="","",IF(($I5=""),"",IFERROR(VLOOKUP($I5,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A5=""),"",IF(EXACT($I5,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I5)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I5)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I5)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L5" s="3">
-        <f>IF($A5="","",IF(AND(NOT(($I5="")),($K5=$J5)),1,0))</f>
+        <f>IF(AND($A5=""),"",IF(AND(NOT(EXACT($I5,"")),EXACT($K5,$J5)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M5" s="3">
+        <f>IF(AND($A5=""),"",MID(IF(AND(NOT(($B5="")),($E5="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N5" s="3">
+        <f>IF(OR(AND(NOT(($B5="")),($E5=""))),2,0)</f>
         <v/>
       </c>
     </row>
@@ -717,31 +746,39 @@
         </is>
       </c>
       <c r="F6" s="3">
-        <f>IF($A6="","",IFERROR(VLOOKUP($B6,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A6=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B6)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B6)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B6)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G6" s="3">
-        <f>IF($A6="","",IF(($C6="Conf"),IFERROR(VLOOKUP($B6,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B6,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A6=""),"",IF(EXACT($C6,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B6)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B6)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B6)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B6)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B6)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B6)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H6" s="3">
-        <f>IF($A6="","",IFERROR(VLOOKUP($E6,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A6=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E6)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E6)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E6)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I6" s="3">
-        <f>IF($A6="","",IF(OR(($E6=""),($B6="")),"",($E6&amp;"|"&amp;$B6)))</f>
+        <f>IF(AND($A6=""),"",IF(OR(($E6=""),($B6="")),"",(IF(ISNUMBER($E6),IF($E6=0,"0",ROUND($E6,9-INT(LOG10(ABS($E6))))&amp;""),$E6&amp;"")&amp;"|"&amp;IF(ISNUMBER($B6),IF($B6=0,"0",ROUND($B6,9-INT(LOG10(ABS($B6))))&amp;""),$B6&amp;""))))</f>
         <v/>
       </c>
       <c r="J6" s="3">
-        <f>IF($A6="","",($B6&amp;" "&amp;$C6&amp;" "&amp;$D6))</f>
+        <f>IF(AND($A6=""),"",(IF(ISNUMBER($B6),IF($B6=0,"0",ROUND($B6,9-INT(LOG10(ABS($B6))))&amp;""),$B6&amp;"")&amp;" "&amp;IF(ISNUMBER($C6),IF($C6=0,"0",ROUND($C6,9-INT(LOG10(ABS($C6))))&amp;""),$C6&amp;"")&amp;" "&amp;IF(ISNUMBER($D6),IF($D6=0,"0",ROUND($D6,9-INT(LOG10(ABS($D6))))&amp;""),$D6&amp;"")))</f>
         <v/>
       </c>
       <c r="K6" s="3">
-        <f>IF($A6="","",IF(($I6=""),"",IFERROR(VLOOKUP($I6,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A6=""),"",IF(EXACT($I6,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I6)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I6)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I6)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L6" s="3">
-        <f>IF($A6="","",IF(AND(NOT(($I6="")),($K6=$J6)),1,0))</f>
+        <f>IF(AND($A6=""),"",IF(AND(NOT(EXACT($I6,"")),EXACT($K6,$J6)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M6" s="3">
+        <f>IF(AND($A6=""),"",MID(IF(AND(NOT(($B6="")),($E6="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N6" s="3">
+        <f>IF(OR(AND(NOT(($B6="")),($E6=""))),2,0)</f>
         <v/>
       </c>
     </row>
@@ -766,31 +803,39 @@
         </is>
       </c>
       <c r="F7" s="3">
-        <f>IF($A7="","",IFERROR(VLOOKUP($B7,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A7=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B7)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B7)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B7)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G7" s="3">
-        <f>IF($A7="","",IF(($C7="Conf"),IFERROR(VLOOKUP($B7,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B7,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A7=""),"",IF(EXACT($C7,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B7)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B7)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B7)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B7)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B7)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B7)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H7" s="3">
-        <f>IF($A7="","",IFERROR(VLOOKUP($E7,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A7=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E7)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E7)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E7)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I7" s="3">
-        <f>IF($A7="","",IF(OR(($E7=""),($B7="")),"",($E7&amp;"|"&amp;$B7)))</f>
+        <f>IF(AND($A7=""),"",IF(OR(($E7=""),($B7="")),"",(IF(ISNUMBER($E7),IF($E7=0,"0",ROUND($E7,9-INT(LOG10(ABS($E7))))&amp;""),$E7&amp;"")&amp;"|"&amp;IF(ISNUMBER($B7),IF($B7=0,"0",ROUND($B7,9-INT(LOG10(ABS($B7))))&amp;""),$B7&amp;""))))</f>
         <v/>
       </c>
       <c r="J7" s="3">
-        <f>IF($A7="","",($B7&amp;" "&amp;$C7&amp;" "&amp;$D7))</f>
+        <f>IF(AND($A7=""),"",(IF(ISNUMBER($B7),IF($B7=0,"0",ROUND($B7,9-INT(LOG10(ABS($B7))))&amp;""),$B7&amp;"")&amp;" "&amp;IF(ISNUMBER($C7),IF($C7=0,"0",ROUND($C7,9-INT(LOG10(ABS($C7))))&amp;""),$C7&amp;"")&amp;" "&amp;IF(ISNUMBER($D7),IF($D7=0,"0",ROUND($D7,9-INT(LOG10(ABS($D7))))&amp;""),$D7&amp;"")))</f>
         <v/>
       </c>
       <c r="K7" s="3">
-        <f>IF($A7="","",IF(($I7=""),"",IFERROR(VLOOKUP($I7,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A7=""),"",IF(EXACT($I7,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I7)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I7)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I7)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L7" s="3">
-        <f>IF($A7="","",IF(AND(NOT(($I7="")),($K7=$J7)),1,0))</f>
+        <f>IF(AND($A7=""),"",IF(AND(NOT(EXACT($I7,"")),EXACT($K7,$J7)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M7" s="3">
+        <f>IF(AND($A7=""),"",MID(IF(AND(NOT(($B7="")),($E7="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N7" s="3">
+        <f>IF(OR(AND(NOT(($B7="")),($E7=""))),2,0)</f>
         <v/>
       </c>
     </row>
@@ -819,31 +864,39 @@
         </is>
       </c>
       <c r="F8" s="3">
-        <f>IF($A8="","",IFERROR(VLOOKUP($B8,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A8=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B8)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B8)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B8)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G8" s="3">
-        <f>IF($A8="","",IF(($C8="Conf"),IFERROR(VLOOKUP($B8,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B8,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A8=""),"",IF(EXACT($C8,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B8)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B8)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B8)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B8)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B8)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B8)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H8" s="3">
-        <f>IF($A8="","",IFERROR(VLOOKUP($E8,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A8=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E8)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E8)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E8)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I8" s="3">
-        <f>IF($A8="","",IF(OR(($E8=""),($B8="")),"",($E8&amp;"|"&amp;$B8)))</f>
+        <f>IF(AND($A8=""),"",IF(OR(($E8=""),($B8="")),"",(IF(ISNUMBER($E8),IF($E8=0,"0",ROUND($E8,9-INT(LOG10(ABS($E8))))&amp;""),$E8&amp;"")&amp;"|"&amp;IF(ISNUMBER($B8),IF($B8=0,"0",ROUND($B8,9-INT(LOG10(ABS($B8))))&amp;""),$B8&amp;""))))</f>
         <v/>
       </c>
       <c r="J8" s="3">
-        <f>IF($A8="","",($B8&amp;" "&amp;$C8&amp;" "&amp;$D8))</f>
+        <f>IF(AND($A8=""),"",(IF(ISNUMBER($B8),IF($B8=0,"0",ROUND($B8,9-INT(LOG10(ABS($B8))))&amp;""),$B8&amp;"")&amp;" "&amp;IF(ISNUMBER($C8),IF($C8=0,"0",ROUND($C8,9-INT(LOG10(ABS($C8))))&amp;""),$C8&amp;"")&amp;" "&amp;IF(ISNUMBER($D8),IF($D8=0,"0",ROUND($D8,9-INT(LOG10(ABS($D8))))&amp;""),$D8&amp;"")))</f>
         <v/>
       </c>
       <c r="K8" s="3">
-        <f>IF($A8="","",IF(($I8=""),"",IFERROR(VLOOKUP($I8,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A8=""),"",IF(EXACT($I8,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I8)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I8)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I8)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L8" s="3">
-        <f>IF($A8="","",IF(AND(NOT(($I8="")),($K8=$J8)),1,0))</f>
+        <f>IF(AND($A8=""),"",IF(AND(NOT(EXACT($I8,"")),EXACT($K8,$J8)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M8" s="3">
+        <f>IF(AND($A8=""),"",MID(IF(AND(NOT(($B8="")),($E8="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N8" s="3">
+        <f>IF(OR(AND(NOT(($B8="")),($E8=""))),2,0)</f>
         <v/>
       </c>
     </row>
@@ -868,31 +921,39 @@
         </is>
       </c>
       <c r="F9" s="3">
-        <f>IF($A9="","",IFERROR(VLOOKUP($B9,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A9=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B9)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B9)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B9)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G9" s="3">
-        <f>IF($A9="","",IF(($C9="Conf"),IFERROR(VLOOKUP($B9,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B9,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A9=""),"",IF(EXACT($C9,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B9)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B9)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B9)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B9)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B9)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B9)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H9" s="3">
-        <f>IF($A9="","",IFERROR(VLOOKUP($E9,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A9=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E9)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E9)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E9)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I9" s="3">
-        <f>IF($A9="","",IF(OR(($E9=""),($B9="")),"",($E9&amp;"|"&amp;$B9)))</f>
+        <f>IF(AND($A9=""),"",IF(OR(($E9=""),($B9="")),"",(IF(ISNUMBER($E9),IF($E9=0,"0",ROUND($E9,9-INT(LOG10(ABS($E9))))&amp;""),$E9&amp;"")&amp;"|"&amp;IF(ISNUMBER($B9),IF($B9=0,"0",ROUND($B9,9-INT(LOG10(ABS($B9))))&amp;""),$B9&amp;""))))</f>
         <v/>
       </c>
       <c r="J9" s="3">
-        <f>IF($A9="","",($B9&amp;" "&amp;$C9&amp;" "&amp;$D9))</f>
+        <f>IF(AND($A9=""),"",(IF(ISNUMBER($B9),IF($B9=0,"0",ROUND($B9,9-INT(LOG10(ABS($B9))))&amp;""),$B9&amp;"")&amp;" "&amp;IF(ISNUMBER($C9),IF($C9=0,"0",ROUND($C9,9-INT(LOG10(ABS($C9))))&amp;""),$C9&amp;"")&amp;" "&amp;IF(ISNUMBER($D9),IF($D9=0,"0",ROUND($D9,9-INT(LOG10(ABS($D9))))&amp;""),$D9&amp;"")))</f>
         <v/>
       </c>
       <c r="K9" s="3">
-        <f>IF($A9="","",IF(($I9=""),"",IFERROR(VLOOKUP($I9,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A9=""),"",IF(EXACT($I9,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I9)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I9)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I9)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L9" s="3">
-        <f>IF($A9="","",IF(AND(NOT(($I9="")),($K9=$J9)),1,0))</f>
+        <f>IF(AND($A9=""),"",IF(AND(NOT(EXACT($I9,"")),EXACT($K9,$J9)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M9" s="3">
+        <f>IF(AND($A9=""),"",MID(IF(AND(NOT(($B9="")),($E9="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N9" s="3">
+        <f>IF(OR(AND(NOT(($B9="")),($E9=""))),2,0)</f>
         <v/>
       </c>
     </row>
@@ -921,31 +982,39 @@
         </is>
       </c>
       <c r="F10" s="3">
-        <f>IF($A10="","",IFERROR(VLOOKUP($B10,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A10=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B10)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B10)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B10)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G10" s="3">
-        <f>IF($A10="","",IF(($C10="Conf"),IFERROR(VLOOKUP($B10,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B10,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A10=""),"",IF(EXACT($C10,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B10)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B10)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B10)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B10)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B10)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B10)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H10" s="3">
-        <f>IF($A10="","",IFERROR(VLOOKUP($E10,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A10=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E10)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E10)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E10)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I10" s="3">
-        <f>IF($A10="","",IF(OR(($E10=""),($B10="")),"",($E10&amp;"|"&amp;$B10)))</f>
+        <f>IF(AND($A10=""),"",IF(OR(($E10=""),($B10="")),"",(IF(ISNUMBER($E10),IF($E10=0,"0",ROUND($E10,9-INT(LOG10(ABS($E10))))&amp;""),$E10&amp;"")&amp;"|"&amp;IF(ISNUMBER($B10),IF($B10=0,"0",ROUND($B10,9-INT(LOG10(ABS($B10))))&amp;""),$B10&amp;""))))</f>
         <v/>
       </c>
       <c r="J10" s="3">
-        <f>IF($A10="","",($B10&amp;" "&amp;$C10&amp;" "&amp;$D10))</f>
+        <f>IF(AND($A10=""),"",(IF(ISNUMBER($B10),IF($B10=0,"0",ROUND($B10,9-INT(LOG10(ABS($B10))))&amp;""),$B10&amp;"")&amp;" "&amp;IF(ISNUMBER($C10),IF($C10=0,"0",ROUND($C10,9-INT(LOG10(ABS($C10))))&amp;""),$C10&amp;"")&amp;" "&amp;IF(ISNUMBER($D10),IF($D10=0,"0",ROUND($D10,9-INT(LOG10(ABS($D10))))&amp;""),$D10&amp;"")))</f>
         <v/>
       </c>
       <c r="K10" s="3">
-        <f>IF($A10="","",IF(($I10=""),"",IFERROR(VLOOKUP($I10,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A10=""),"",IF(EXACT($I10,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I10)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I10)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I10)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L10" s="3">
-        <f>IF($A10="","",IF(AND(NOT(($I10="")),($K10=$J10)),1,0))</f>
+        <f>IF(AND($A10=""),"",IF(AND(NOT(EXACT($I10,"")),EXACT($K10,$J10)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M10" s="3">
+        <f>IF(AND($A10=""),"",MID(IF(AND(NOT(($B10="")),($E10="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N10" s="3">
+        <f>IF(OR(AND(NOT(($B10="")),($E10=""))),2,0)</f>
         <v/>
       </c>
     </row>
@@ -970,31 +1039,39 @@
       </c>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="3">
-        <f>IF($A11="","",IFERROR(VLOOKUP($B11,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A11=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B11)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B11)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B11)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G11" s="3">
-        <f>IF($A11="","",IF(($C11="Conf"),IFERROR(VLOOKUP($B11,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B11,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A11=""),"",IF(EXACT($C11,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B11)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B11)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B11)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B11)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B11)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B11)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H11" s="3">
-        <f>IF($A11="","",IFERROR(VLOOKUP($E11,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A11=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E11)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E11)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E11)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I11" s="3">
-        <f>IF($A11="","",IF(OR(($E11=""),($B11="")),"",($E11&amp;"|"&amp;$B11)))</f>
+        <f>IF(AND($A11=""),"",IF(OR(($E11=""),($B11="")),"",(IF(ISNUMBER($E11),IF($E11=0,"0",ROUND($E11,9-INT(LOG10(ABS($E11))))&amp;""),$E11&amp;"")&amp;"|"&amp;IF(ISNUMBER($B11),IF($B11=0,"0",ROUND($B11,9-INT(LOG10(ABS($B11))))&amp;""),$B11&amp;""))))</f>
         <v/>
       </c>
       <c r="J11" s="3">
-        <f>IF($A11="","",($B11&amp;" "&amp;$C11&amp;" "&amp;$D11))</f>
+        <f>IF(AND($A11=""),"",(IF(ISNUMBER($B11),IF($B11=0,"0",ROUND($B11,9-INT(LOG10(ABS($B11))))&amp;""),$B11&amp;"")&amp;" "&amp;IF(ISNUMBER($C11),IF($C11=0,"0",ROUND($C11,9-INT(LOG10(ABS($C11))))&amp;""),$C11&amp;"")&amp;" "&amp;IF(ISNUMBER($D11),IF($D11=0,"0",ROUND($D11,9-INT(LOG10(ABS($D11))))&amp;""),$D11&amp;"")))</f>
         <v/>
       </c>
       <c r="K11" s="3">
-        <f>IF($A11="","",IF(($I11=""),"",IFERROR(VLOOKUP($I11,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A11=""),"",IF(EXACT($I11,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I11)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I11)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I11)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L11" s="3">
-        <f>IF($A11="","",IF(AND(NOT(($I11="")),($K11=$J11)),1,0))</f>
+        <f>IF(AND($A11=""),"",IF(AND(NOT(EXACT($I11,"")),EXACT($K11,$J11)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M11" s="3">
+        <f>IF(AND($A11=""),"",MID(IF(AND(NOT(($B11="")),($E11="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N11" s="3">
+        <f>IF(OR(AND(NOT(($B11="")),($E11=""))),2,0)</f>
         <v/>
       </c>
     </row>
@@ -1019,31 +1096,39 @@
         </is>
       </c>
       <c r="F12" s="3">
-        <f>IF($A12="","",IFERROR(VLOOKUP($B12,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A12=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B12)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B12)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B12)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G12" s="3">
-        <f>IF($A12="","",IF(($C12="Conf"),IFERROR(VLOOKUP($B12,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B12,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A12=""),"",IF(EXACT($C12,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B12)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B12)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B12)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B12)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B12)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B12)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H12" s="3">
-        <f>IF($A12="","",IFERROR(VLOOKUP($E12,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A12=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E12)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E12)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E12)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I12" s="3">
-        <f>IF($A12="","",IF(OR(($E12=""),($B12="")),"",($E12&amp;"|"&amp;$B12)))</f>
+        <f>IF(AND($A12=""),"",IF(OR(($E12=""),($B12="")),"",(IF(ISNUMBER($E12),IF($E12=0,"0",ROUND($E12,9-INT(LOG10(ABS($E12))))&amp;""),$E12&amp;"")&amp;"|"&amp;IF(ISNUMBER($B12),IF($B12=0,"0",ROUND($B12,9-INT(LOG10(ABS($B12))))&amp;""),$B12&amp;""))))</f>
         <v/>
       </c>
       <c r="J12" s="3">
-        <f>IF($A12="","",($B12&amp;" "&amp;$C12&amp;" "&amp;$D12))</f>
+        <f>IF(AND($A12=""),"",(IF(ISNUMBER($B12),IF($B12=0,"0",ROUND($B12,9-INT(LOG10(ABS($B12))))&amp;""),$B12&amp;"")&amp;" "&amp;IF(ISNUMBER($C12),IF($C12=0,"0",ROUND($C12,9-INT(LOG10(ABS($C12))))&amp;""),$C12&amp;"")&amp;" "&amp;IF(ISNUMBER($D12),IF($D12=0,"0",ROUND($D12,9-INT(LOG10(ABS($D12))))&amp;""),$D12&amp;"")))</f>
         <v/>
       </c>
       <c r="K12" s="3">
-        <f>IF($A12="","",IF(($I12=""),"",IFERROR(VLOOKUP($I12,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A12=""),"",IF(EXACT($I12,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I12)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I12)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I12)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L12" s="3">
-        <f>IF($A12="","",IF(AND(NOT(($I12="")),($K12=$J12)),1,0))</f>
+        <f>IF(AND($A12=""),"",IF(AND(NOT(EXACT($I12,"")),EXACT($K12,$J12)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M12" s="3">
+        <f>IF(AND($A12=""),"",MID(IF(AND(NOT(($B12="")),($E12="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N12" s="3">
+        <f>IF(OR(AND(NOT(($B12="")),($E12=""))),2,0)</f>
         <v/>
       </c>
     </row>
@@ -1056,31 +1141,39 @@
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="3">
-        <f>IF($A13="","",IFERROR(VLOOKUP($B13,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A13=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B13)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B13)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B13)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G13" s="3">
-        <f>IF($A13="","",IF(($C13="Conf"),IFERROR(VLOOKUP($B13,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B13,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A13=""),"",IF(EXACT($C13,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B13)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B13)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B13)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B13)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B13)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B13)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H13" s="3">
-        <f>IF($A13="","",IFERROR(VLOOKUP($E13,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A13=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E13)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E13)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E13)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I13" s="3">
-        <f>IF($A13="","",IF(OR(($E13=""),($B13="")),"",($E13&amp;"|"&amp;$B13)))</f>
+        <f>IF(AND($A13=""),"",IF(OR(($E13=""),($B13="")),"",(IF(ISNUMBER($E13),IF($E13=0,"0",ROUND($E13,9-INT(LOG10(ABS($E13))))&amp;""),$E13&amp;"")&amp;"|"&amp;IF(ISNUMBER($B13),IF($B13=0,"0",ROUND($B13,9-INT(LOG10(ABS($B13))))&amp;""),$B13&amp;""))))</f>
         <v/>
       </c>
       <c r="J13" s="3">
-        <f>IF($A13="","",($B13&amp;" "&amp;$C13&amp;" "&amp;$D13))</f>
+        <f>IF(AND($A13=""),"",(IF(ISNUMBER($B13),IF($B13=0,"0",ROUND($B13,9-INT(LOG10(ABS($B13))))&amp;""),$B13&amp;"")&amp;" "&amp;IF(ISNUMBER($C13),IF($C13=0,"0",ROUND($C13,9-INT(LOG10(ABS($C13))))&amp;""),$C13&amp;"")&amp;" "&amp;IF(ISNUMBER($D13),IF($D13=0,"0",ROUND($D13,9-INT(LOG10(ABS($D13))))&amp;""),$D13&amp;"")))</f>
         <v/>
       </c>
       <c r="K13" s="3">
-        <f>IF($A13="","",IF(($I13=""),"",IFERROR(VLOOKUP($I13,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A13=""),"",IF(EXACT($I13,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I13)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I13)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I13)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L13" s="3">
-        <f>IF($A13="","",IF(AND(NOT(($I13="")),($K13=$J13)),1,0))</f>
+        <f>IF(AND($A13=""),"",IF(AND(NOT(EXACT($I13,"")),EXACT($K13,$J13)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M13" s="3">
+        <f>IF(AND($A13=""),"",MID(IF(AND(NOT(($B13="")),($E13="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N13" s="3">
+        <f>IF(OR(AND(NOT(($B13="")),($E13=""))),2,0)</f>
         <v/>
       </c>
     </row>
@@ -1093,731 +1186,899 @@
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="3">
-        <f>IF($A14="","",IFERROR(VLOOKUP($B14,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A14=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B14)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B14)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B14)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G14" s="3">
-        <f>IF($A14="","",IF(($C14="Conf"),IFERROR(VLOOKUP($B14,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B14,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A14=""),"",IF(EXACT($C14,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B14)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B14)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B14)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B14)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B14)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B14)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H14" s="3">
-        <f>IF($A14="","",IFERROR(VLOOKUP($E14,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A14=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E14)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E14)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E14)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I14" s="3">
-        <f>IF($A14="","",IF(OR(($E14=""),($B14="")),"",($E14&amp;"|"&amp;$B14)))</f>
+        <f>IF(AND($A14=""),"",IF(OR(($E14=""),($B14="")),"",(IF(ISNUMBER($E14),IF($E14=0,"0",ROUND($E14,9-INT(LOG10(ABS($E14))))&amp;""),$E14&amp;"")&amp;"|"&amp;IF(ISNUMBER($B14),IF($B14=0,"0",ROUND($B14,9-INT(LOG10(ABS($B14))))&amp;""),$B14&amp;""))))</f>
         <v/>
       </c>
       <c r="J14" s="3">
-        <f>IF($A14="","",($B14&amp;" "&amp;$C14&amp;" "&amp;$D14))</f>
+        <f>IF(AND($A14=""),"",(IF(ISNUMBER($B14),IF($B14=0,"0",ROUND($B14,9-INT(LOG10(ABS($B14))))&amp;""),$B14&amp;"")&amp;" "&amp;IF(ISNUMBER($C14),IF($C14=0,"0",ROUND($C14,9-INT(LOG10(ABS($C14))))&amp;""),$C14&amp;"")&amp;" "&amp;IF(ISNUMBER($D14),IF($D14=0,"0",ROUND($D14,9-INT(LOG10(ABS($D14))))&amp;""),$D14&amp;"")))</f>
         <v/>
       </c>
       <c r="K14" s="3">
-        <f>IF($A14="","",IF(($I14=""),"",IFERROR(VLOOKUP($I14,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A14=""),"",IF(EXACT($I14,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I14)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I14)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I14)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L14" s="3">
-        <f>IF($A14="","",IF(AND(NOT(($I14="")),($K14=$J14)),1,0))</f>
+        <f>IF(AND($A14=""),"",IF(AND(NOT(EXACT($I14,"")),EXACT($K14,$J14)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M14" s="3">
+        <f>IF(AND($A14=""),"",MID(IF(AND(NOT(($B14="")),($E14="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N14" s="3">
+        <f>IF(OR(AND(NOT(($B14="")),($E14=""))),2,0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n"/>
+      <c r="A15" s="4" t="n"/>
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="4" t="n"/>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="3">
-        <f>IF($A15="","",IFERROR(VLOOKUP($B15,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A15=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B15)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B15)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B15)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G15" s="3">
-        <f>IF($A15="","",IF(($C15="Conf"),IFERROR(VLOOKUP($B15,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B15,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A15=""),"",IF(EXACT($C15,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B15)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B15)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B15)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B15)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B15)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B15)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H15" s="3">
-        <f>IF($A15="","",IFERROR(VLOOKUP($E15,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A15=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E15)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E15)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E15)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I15" s="3">
-        <f>IF($A15="","",IF(OR(($E15=""),($B15="")),"",($E15&amp;"|"&amp;$B15)))</f>
+        <f>IF(AND($A15=""),"",IF(OR(($E15=""),($B15="")),"",(IF(ISNUMBER($E15),IF($E15=0,"0",ROUND($E15,9-INT(LOG10(ABS($E15))))&amp;""),$E15&amp;"")&amp;"|"&amp;IF(ISNUMBER($B15),IF($B15=0,"0",ROUND($B15,9-INT(LOG10(ABS($B15))))&amp;""),$B15&amp;""))))</f>
         <v/>
       </c>
       <c r="J15" s="3">
-        <f>IF($A15="","",($B15&amp;" "&amp;$C15&amp;" "&amp;$D15))</f>
+        <f>IF(AND($A15=""),"",(IF(ISNUMBER($B15),IF($B15=0,"0",ROUND($B15,9-INT(LOG10(ABS($B15))))&amp;""),$B15&amp;"")&amp;" "&amp;IF(ISNUMBER($C15),IF($C15=0,"0",ROUND($C15,9-INT(LOG10(ABS($C15))))&amp;""),$C15&amp;"")&amp;" "&amp;IF(ISNUMBER($D15),IF($D15=0,"0",ROUND($D15,9-INT(LOG10(ABS($D15))))&amp;""),$D15&amp;"")))</f>
         <v/>
       </c>
       <c r="K15" s="3">
-        <f>IF($A15="","",IF(($I15=""),"",IFERROR(VLOOKUP($I15,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A15=""),"",IF(EXACT($I15,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I15)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I15)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I15)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L15" s="3">
-        <f>IF($A15="","",IF(AND(NOT(($I15="")),($K15=$J15)),1,0))</f>
+        <f>IF(AND($A15=""),"",IF(AND(NOT(EXACT($I15,"")),EXACT($K15,$J15)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M15" s="3">
+        <f>IF(AND($A15=""),"",MID(IF(AND(NOT(($B15="")),($E15="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N15" s="3">
+        <f>IF(OR(AND(NOT(($B15="")),($E15=""))),2,0)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n"/>
+      <c r="A16" s="4" t="n"/>
       <c r="B16" s="4" t="n"/>
       <c r="C16" s="4" t="n"/>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="3">
-        <f>IF($A16="","",IFERROR(VLOOKUP($B16,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A16=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B16)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B16)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B16)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G16" s="3">
-        <f>IF($A16="","",IF(($C16="Conf"),IFERROR(VLOOKUP($B16,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B16,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A16=""),"",IF(EXACT($C16,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B16)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B16)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B16)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B16)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B16)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B16)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H16" s="3">
-        <f>IF($A16="","",IFERROR(VLOOKUP($E16,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A16=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E16)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E16)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E16)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I16" s="3">
-        <f>IF($A16="","",IF(OR(($E16=""),($B16="")),"",($E16&amp;"|"&amp;$B16)))</f>
+        <f>IF(AND($A16=""),"",IF(OR(($E16=""),($B16="")),"",(IF(ISNUMBER($E16),IF($E16=0,"0",ROUND($E16,9-INT(LOG10(ABS($E16))))&amp;""),$E16&amp;"")&amp;"|"&amp;IF(ISNUMBER($B16),IF($B16=0,"0",ROUND($B16,9-INT(LOG10(ABS($B16))))&amp;""),$B16&amp;""))))</f>
         <v/>
       </c>
       <c r="J16" s="3">
-        <f>IF($A16="","",($B16&amp;" "&amp;$C16&amp;" "&amp;$D16))</f>
+        <f>IF(AND($A16=""),"",(IF(ISNUMBER($B16),IF($B16=0,"0",ROUND($B16,9-INT(LOG10(ABS($B16))))&amp;""),$B16&amp;"")&amp;" "&amp;IF(ISNUMBER($C16),IF($C16=0,"0",ROUND($C16,9-INT(LOG10(ABS($C16))))&amp;""),$C16&amp;"")&amp;" "&amp;IF(ISNUMBER($D16),IF($D16=0,"0",ROUND($D16,9-INT(LOG10(ABS($D16))))&amp;""),$D16&amp;"")))</f>
         <v/>
       </c>
       <c r="K16" s="3">
-        <f>IF($A16="","",IF(($I16=""),"",IFERROR(VLOOKUP($I16,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A16=""),"",IF(EXACT($I16,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I16)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I16)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I16)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L16" s="3">
-        <f>IF($A16="","",IF(AND(NOT(($I16="")),($K16=$J16)),1,0))</f>
+        <f>IF(AND($A16=""),"",IF(AND(NOT(EXACT($I16,"")),EXACT($K16,$J16)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M16" s="3">
+        <f>IF(AND($A16=""),"",MID(IF(AND(NOT(($B16="")),($E16="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N16" s="3">
+        <f>IF(OR(AND(NOT(($B16="")),($E16=""))),2,0)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n"/>
+      <c r="A17" s="4" t="n"/>
       <c r="B17" s="4" t="n"/>
       <c r="C17" s="4" t="n"/>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="3">
-        <f>IF($A17="","",IFERROR(VLOOKUP($B17,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A17=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B17)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B17)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B17)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G17" s="3">
-        <f>IF($A17="","",IF(($C17="Conf"),IFERROR(VLOOKUP($B17,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B17,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A17=""),"",IF(EXACT($C17,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B17)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B17)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B17)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B17)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B17)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B17)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H17" s="3">
-        <f>IF($A17="","",IFERROR(VLOOKUP($E17,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A17=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E17)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E17)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E17)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I17" s="3">
-        <f>IF($A17="","",IF(OR(($E17=""),($B17="")),"",($E17&amp;"|"&amp;$B17)))</f>
+        <f>IF(AND($A17=""),"",IF(OR(($E17=""),($B17="")),"",(IF(ISNUMBER($E17),IF($E17=0,"0",ROUND($E17,9-INT(LOG10(ABS($E17))))&amp;""),$E17&amp;"")&amp;"|"&amp;IF(ISNUMBER($B17),IF($B17=0,"0",ROUND($B17,9-INT(LOG10(ABS($B17))))&amp;""),$B17&amp;""))))</f>
         <v/>
       </c>
       <c r="J17" s="3">
-        <f>IF($A17="","",($B17&amp;" "&amp;$C17&amp;" "&amp;$D17))</f>
+        <f>IF(AND($A17=""),"",(IF(ISNUMBER($B17),IF($B17=0,"0",ROUND($B17,9-INT(LOG10(ABS($B17))))&amp;""),$B17&amp;"")&amp;" "&amp;IF(ISNUMBER($C17),IF($C17=0,"0",ROUND($C17,9-INT(LOG10(ABS($C17))))&amp;""),$C17&amp;"")&amp;" "&amp;IF(ISNUMBER($D17),IF($D17=0,"0",ROUND($D17,9-INT(LOG10(ABS($D17))))&amp;""),$D17&amp;"")))</f>
         <v/>
       </c>
       <c r="K17" s="3">
-        <f>IF($A17="","",IF(($I17=""),"",IFERROR(VLOOKUP($I17,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A17=""),"",IF(EXACT($I17,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I17)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I17)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I17)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L17" s="3">
-        <f>IF($A17="","",IF(AND(NOT(($I17="")),($K17=$J17)),1,0))</f>
+        <f>IF(AND($A17=""),"",IF(AND(NOT(EXACT($I17,"")),EXACT($K17,$J17)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M17" s="3">
+        <f>IF(AND($A17=""),"",MID(IF(AND(NOT(($B17="")),($E17="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N17" s="3">
+        <f>IF(OR(AND(NOT(($B17="")),($E17=""))),2,0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n"/>
+      <c r="A18" s="4" t="n"/>
       <c r="B18" s="4" t="n"/>
       <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="3">
-        <f>IF($A18="","",IFERROR(VLOOKUP($B18,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A18=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B18)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B18)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B18)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G18" s="3">
-        <f>IF($A18="","",IF(($C18="Conf"),IFERROR(VLOOKUP($B18,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B18,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A18=""),"",IF(EXACT($C18,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B18)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B18)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B18)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B18)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B18)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B18)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H18" s="3">
-        <f>IF($A18="","",IFERROR(VLOOKUP($E18,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A18=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E18)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E18)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E18)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I18" s="3">
-        <f>IF($A18="","",IF(OR(($E18=""),($B18="")),"",($E18&amp;"|"&amp;$B18)))</f>
+        <f>IF(AND($A18=""),"",IF(OR(($E18=""),($B18="")),"",(IF(ISNUMBER($E18),IF($E18=0,"0",ROUND($E18,9-INT(LOG10(ABS($E18))))&amp;""),$E18&amp;"")&amp;"|"&amp;IF(ISNUMBER($B18),IF($B18=0,"0",ROUND($B18,9-INT(LOG10(ABS($B18))))&amp;""),$B18&amp;""))))</f>
         <v/>
       </c>
       <c r="J18" s="3">
-        <f>IF($A18="","",($B18&amp;" "&amp;$C18&amp;" "&amp;$D18))</f>
+        <f>IF(AND($A18=""),"",(IF(ISNUMBER($B18),IF($B18=0,"0",ROUND($B18,9-INT(LOG10(ABS($B18))))&amp;""),$B18&amp;"")&amp;" "&amp;IF(ISNUMBER($C18),IF($C18=0,"0",ROUND($C18,9-INT(LOG10(ABS($C18))))&amp;""),$C18&amp;"")&amp;" "&amp;IF(ISNUMBER($D18),IF($D18=0,"0",ROUND($D18,9-INT(LOG10(ABS($D18))))&amp;""),$D18&amp;"")))</f>
         <v/>
       </c>
       <c r="K18" s="3">
-        <f>IF($A18="","",IF(($I18=""),"",IFERROR(VLOOKUP($I18,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A18=""),"",IF(EXACT($I18,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I18)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I18)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I18)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L18" s="3">
-        <f>IF($A18="","",IF(AND(NOT(($I18="")),($K18=$J18)),1,0))</f>
+        <f>IF(AND($A18=""),"",IF(AND(NOT(EXACT($I18,"")),EXACT($K18,$J18)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M18" s="3">
+        <f>IF(AND($A18=""),"",MID(IF(AND(NOT(($B18="")),($E18="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N18" s="3">
+        <f>IF(OR(AND(NOT(($B18="")),($E18=""))),2,0)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n"/>
+      <c r="A19" s="4" t="n"/>
       <c r="B19" s="4" t="n"/>
       <c r="C19" s="4" t="n"/>
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="3">
-        <f>IF($A19="","",IFERROR(VLOOKUP($B19,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A19=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B19)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B19)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B19)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G19" s="3">
-        <f>IF($A19="","",IF(($C19="Conf"),IFERROR(VLOOKUP($B19,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B19,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A19=""),"",IF(EXACT($C19,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B19)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B19)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B19)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B19)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B19)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B19)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H19" s="3">
-        <f>IF($A19="","",IFERROR(VLOOKUP($E19,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A19=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E19)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E19)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E19)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I19" s="3">
-        <f>IF($A19="","",IF(OR(($E19=""),($B19="")),"",($E19&amp;"|"&amp;$B19)))</f>
+        <f>IF(AND($A19=""),"",IF(OR(($E19=""),($B19="")),"",(IF(ISNUMBER($E19),IF($E19=0,"0",ROUND($E19,9-INT(LOG10(ABS($E19))))&amp;""),$E19&amp;"")&amp;"|"&amp;IF(ISNUMBER($B19),IF($B19=0,"0",ROUND($B19,9-INT(LOG10(ABS($B19))))&amp;""),$B19&amp;""))))</f>
         <v/>
       </c>
       <c r="J19" s="3">
-        <f>IF($A19="","",($B19&amp;" "&amp;$C19&amp;" "&amp;$D19))</f>
+        <f>IF(AND($A19=""),"",(IF(ISNUMBER($B19),IF($B19=0,"0",ROUND($B19,9-INT(LOG10(ABS($B19))))&amp;""),$B19&amp;"")&amp;" "&amp;IF(ISNUMBER($C19),IF($C19=0,"0",ROUND($C19,9-INT(LOG10(ABS($C19))))&amp;""),$C19&amp;"")&amp;" "&amp;IF(ISNUMBER($D19),IF($D19=0,"0",ROUND($D19,9-INT(LOG10(ABS($D19))))&amp;""),$D19&amp;"")))</f>
         <v/>
       </c>
       <c r="K19" s="3">
-        <f>IF($A19="","",IF(($I19=""),"",IFERROR(VLOOKUP($I19,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A19=""),"",IF(EXACT($I19,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I19)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I19)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I19)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L19" s="3">
-        <f>IF($A19="","",IF(AND(NOT(($I19="")),($K19=$J19)),1,0))</f>
+        <f>IF(AND($A19=""),"",IF(AND(NOT(EXACT($I19,"")),EXACT($K19,$J19)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M19" s="3">
+        <f>IF(AND($A19=""),"",MID(IF(AND(NOT(($B19="")),($E19="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N19" s="3">
+        <f>IF(OR(AND(NOT(($B19="")),($E19=""))),2,0)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n"/>
+      <c r="A20" s="4" t="n"/>
       <c r="B20" s="4" t="n"/>
       <c r="C20" s="4" t="n"/>
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="3">
-        <f>IF($A20="","",IFERROR(VLOOKUP($B20,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A20=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B20)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B20)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B20)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G20" s="3">
-        <f>IF($A20="","",IF(($C20="Conf"),IFERROR(VLOOKUP($B20,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B20,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A20=""),"",IF(EXACT($C20,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B20)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B20)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B20)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B20)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B20)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B20)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H20" s="3">
-        <f>IF($A20="","",IFERROR(VLOOKUP($E20,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A20=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E20)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E20)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E20)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I20" s="3">
-        <f>IF($A20="","",IF(OR(($E20=""),($B20="")),"",($E20&amp;"|"&amp;$B20)))</f>
+        <f>IF(AND($A20=""),"",IF(OR(($E20=""),($B20="")),"",(IF(ISNUMBER($E20),IF($E20=0,"0",ROUND($E20,9-INT(LOG10(ABS($E20))))&amp;""),$E20&amp;"")&amp;"|"&amp;IF(ISNUMBER($B20),IF($B20=0,"0",ROUND($B20,9-INT(LOG10(ABS($B20))))&amp;""),$B20&amp;""))))</f>
         <v/>
       </c>
       <c r="J20" s="3">
-        <f>IF($A20="","",($B20&amp;" "&amp;$C20&amp;" "&amp;$D20))</f>
+        <f>IF(AND($A20=""),"",(IF(ISNUMBER($B20),IF($B20=0,"0",ROUND($B20,9-INT(LOG10(ABS($B20))))&amp;""),$B20&amp;"")&amp;" "&amp;IF(ISNUMBER($C20),IF($C20=0,"0",ROUND($C20,9-INT(LOG10(ABS($C20))))&amp;""),$C20&amp;"")&amp;" "&amp;IF(ISNUMBER($D20),IF($D20=0,"0",ROUND($D20,9-INT(LOG10(ABS($D20))))&amp;""),$D20&amp;"")))</f>
         <v/>
       </c>
       <c r="K20" s="3">
-        <f>IF($A20="","",IF(($I20=""),"",IFERROR(VLOOKUP($I20,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A20=""),"",IF(EXACT($I20,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I20)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I20)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I20)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L20" s="3">
-        <f>IF($A20="","",IF(AND(NOT(($I20="")),($K20=$J20)),1,0))</f>
+        <f>IF(AND($A20=""),"",IF(AND(NOT(EXACT($I20,"")),EXACT($K20,$J20)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M20" s="3">
+        <f>IF(AND($A20=""),"",MID(IF(AND(NOT(($B20="")),($E20="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N20" s="3">
+        <f>IF(OR(AND(NOT(($B20="")),($E20=""))),2,0)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n"/>
+      <c r="A21" s="4" t="n"/>
       <c r="B21" s="4" t="n"/>
       <c r="C21" s="4" t="n"/>
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="3">
-        <f>IF($A21="","",IFERROR(VLOOKUP($B21,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A21=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B21)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B21)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B21)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G21" s="3">
-        <f>IF($A21="","",IF(($C21="Conf"),IFERROR(VLOOKUP($B21,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B21,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A21=""),"",IF(EXACT($C21,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B21)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B21)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B21)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B21)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B21)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B21)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H21" s="3">
-        <f>IF($A21="","",IFERROR(VLOOKUP($E21,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A21=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E21)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E21)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E21)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I21" s="3">
-        <f>IF($A21="","",IF(OR(($E21=""),($B21="")),"",($E21&amp;"|"&amp;$B21)))</f>
+        <f>IF(AND($A21=""),"",IF(OR(($E21=""),($B21="")),"",(IF(ISNUMBER($E21),IF($E21=0,"0",ROUND($E21,9-INT(LOG10(ABS($E21))))&amp;""),$E21&amp;"")&amp;"|"&amp;IF(ISNUMBER($B21),IF($B21=0,"0",ROUND($B21,9-INT(LOG10(ABS($B21))))&amp;""),$B21&amp;""))))</f>
         <v/>
       </c>
       <c r="J21" s="3">
-        <f>IF($A21="","",($B21&amp;" "&amp;$C21&amp;" "&amp;$D21))</f>
+        <f>IF(AND($A21=""),"",(IF(ISNUMBER($B21),IF($B21=0,"0",ROUND($B21,9-INT(LOG10(ABS($B21))))&amp;""),$B21&amp;"")&amp;" "&amp;IF(ISNUMBER($C21),IF($C21=0,"0",ROUND($C21,9-INT(LOG10(ABS($C21))))&amp;""),$C21&amp;"")&amp;" "&amp;IF(ISNUMBER($D21),IF($D21=0,"0",ROUND($D21,9-INT(LOG10(ABS($D21))))&amp;""),$D21&amp;"")))</f>
         <v/>
       </c>
       <c r="K21" s="3">
-        <f>IF($A21="","",IF(($I21=""),"",IFERROR(VLOOKUP($I21,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A21=""),"",IF(EXACT($I21,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I21)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I21)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I21)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L21" s="3">
-        <f>IF($A21="","",IF(AND(NOT(($I21="")),($K21=$J21)),1,0))</f>
+        <f>IF(AND($A21=""),"",IF(AND(NOT(EXACT($I21,"")),EXACT($K21,$J21)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M21" s="3">
+        <f>IF(AND($A21=""),"",MID(IF(AND(NOT(($B21="")),($E21="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N21" s="3">
+        <f>IF(OR(AND(NOT(($B21="")),($E21=""))),2,0)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n"/>
+      <c r="A22" s="4" t="n"/>
       <c r="B22" s="4" t="n"/>
       <c r="C22" s="4" t="n"/>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="3">
-        <f>IF($A22="","",IFERROR(VLOOKUP($B22,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A22=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B22)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B22)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B22)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G22" s="3">
-        <f>IF($A22="","",IF(($C22="Conf"),IFERROR(VLOOKUP($B22,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B22,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A22=""),"",IF(EXACT($C22,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B22)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B22)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B22)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B22)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B22)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B22)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H22" s="3">
-        <f>IF($A22="","",IFERROR(VLOOKUP($E22,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A22=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E22)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E22)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E22)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I22" s="3">
-        <f>IF($A22="","",IF(OR(($E22=""),($B22="")),"",($E22&amp;"|"&amp;$B22)))</f>
+        <f>IF(AND($A22=""),"",IF(OR(($E22=""),($B22="")),"",(IF(ISNUMBER($E22),IF($E22=0,"0",ROUND($E22,9-INT(LOG10(ABS($E22))))&amp;""),$E22&amp;"")&amp;"|"&amp;IF(ISNUMBER($B22),IF($B22=0,"0",ROUND($B22,9-INT(LOG10(ABS($B22))))&amp;""),$B22&amp;""))))</f>
         <v/>
       </c>
       <c r="J22" s="3">
-        <f>IF($A22="","",($B22&amp;" "&amp;$C22&amp;" "&amp;$D22))</f>
+        <f>IF(AND($A22=""),"",(IF(ISNUMBER($B22),IF($B22=0,"0",ROUND($B22,9-INT(LOG10(ABS($B22))))&amp;""),$B22&amp;"")&amp;" "&amp;IF(ISNUMBER($C22),IF($C22=0,"0",ROUND($C22,9-INT(LOG10(ABS($C22))))&amp;""),$C22&amp;"")&amp;" "&amp;IF(ISNUMBER($D22),IF($D22=0,"0",ROUND($D22,9-INT(LOG10(ABS($D22))))&amp;""),$D22&amp;"")))</f>
         <v/>
       </c>
       <c r="K22" s="3">
-        <f>IF($A22="","",IF(($I22=""),"",IFERROR(VLOOKUP($I22,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A22=""),"",IF(EXACT($I22,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I22)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I22)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I22)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L22" s="3">
-        <f>IF($A22="","",IF(AND(NOT(($I22="")),($K22=$J22)),1,0))</f>
+        <f>IF(AND($A22=""),"",IF(AND(NOT(EXACT($I22,"")),EXACT($K22,$J22)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M22" s="3">
+        <f>IF(AND($A22=""),"",MID(IF(AND(NOT(($B22="")),($E22="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N22" s="3">
+        <f>IF(OR(AND(NOT(($B22="")),($E22=""))),2,0)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n"/>
+      <c r="A23" s="4" t="n"/>
       <c r="B23" s="4" t="n"/>
       <c r="C23" s="4" t="n"/>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="3">
-        <f>IF($A23="","",IFERROR(VLOOKUP($B23,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A23=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B23)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B23)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B23)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G23" s="3">
-        <f>IF($A23="","",IF(($C23="Conf"),IFERROR(VLOOKUP($B23,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B23,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A23=""),"",IF(EXACT($C23,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B23)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B23)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B23)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B23)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B23)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B23)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H23" s="3">
-        <f>IF($A23="","",IFERROR(VLOOKUP($E23,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A23=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E23)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E23)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E23)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I23" s="3">
-        <f>IF($A23="","",IF(OR(($E23=""),($B23="")),"",($E23&amp;"|"&amp;$B23)))</f>
+        <f>IF(AND($A23=""),"",IF(OR(($E23=""),($B23="")),"",(IF(ISNUMBER($E23),IF($E23=0,"0",ROUND($E23,9-INT(LOG10(ABS($E23))))&amp;""),$E23&amp;"")&amp;"|"&amp;IF(ISNUMBER($B23),IF($B23=0,"0",ROUND($B23,9-INT(LOG10(ABS($B23))))&amp;""),$B23&amp;""))))</f>
         <v/>
       </c>
       <c r="J23" s="3">
-        <f>IF($A23="","",($B23&amp;" "&amp;$C23&amp;" "&amp;$D23))</f>
+        <f>IF(AND($A23=""),"",(IF(ISNUMBER($B23),IF($B23=0,"0",ROUND($B23,9-INT(LOG10(ABS($B23))))&amp;""),$B23&amp;"")&amp;" "&amp;IF(ISNUMBER($C23),IF($C23=0,"0",ROUND($C23,9-INT(LOG10(ABS($C23))))&amp;""),$C23&amp;"")&amp;" "&amp;IF(ISNUMBER($D23),IF($D23=0,"0",ROUND($D23,9-INT(LOG10(ABS($D23))))&amp;""),$D23&amp;"")))</f>
         <v/>
       </c>
       <c r="K23" s="3">
-        <f>IF($A23="","",IF(($I23=""),"",IFERROR(VLOOKUP($I23,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A23=""),"",IF(EXACT($I23,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I23)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I23)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I23)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L23" s="3">
-        <f>IF($A23="","",IF(AND(NOT(($I23="")),($K23=$J23)),1,0))</f>
+        <f>IF(AND($A23=""),"",IF(AND(NOT(EXACT($I23,"")),EXACT($K23,$J23)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M23" s="3">
+        <f>IF(AND($A23=""),"",MID(IF(AND(NOT(($B23="")),($E23="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N23" s="3">
+        <f>IF(OR(AND(NOT(($B23="")),($E23=""))),2,0)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n"/>
+      <c r="A24" s="4" t="n"/>
       <c r="B24" s="4" t="n"/>
       <c r="C24" s="4" t="n"/>
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="3">
-        <f>IF($A24="","",IFERROR(VLOOKUP($B24,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A24=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B24)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B24)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B24)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G24" s="3">
-        <f>IF($A24="","",IF(($C24="Conf"),IFERROR(VLOOKUP($B24,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B24,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A24=""),"",IF(EXACT($C24,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B24)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B24)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B24)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B24)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B24)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B24)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H24" s="3">
-        <f>IF($A24="","",IFERROR(VLOOKUP($E24,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A24=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E24)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E24)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E24)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I24" s="3">
-        <f>IF($A24="","",IF(OR(($E24=""),($B24="")),"",($E24&amp;"|"&amp;$B24)))</f>
+        <f>IF(AND($A24=""),"",IF(OR(($E24=""),($B24="")),"",(IF(ISNUMBER($E24),IF($E24=0,"0",ROUND($E24,9-INT(LOG10(ABS($E24))))&amp;""),$E24&amp;"")&amp;"|"&amp;IF(ISNUMBER($B24),IF($B24=0,"0",ROUND($B24,9-INT(LOG10(ABS($B24))))&amp;""),$B24&amp;""))))</f>
         <v/>
       </c>
       <c r="J24" s="3">
-        <f>IF($A24="","",($B24&amp;" "&amp;$C24&amp;" "&amp;$D24))</f>
+        <f>IF(AND($A24=""),"",(IF(ISNUMBER($B24),IF($B24=0,"0",ROUND($B24,9-INT(LOG10(ABS($B24))))&amp;""),$B24&amp;"")&amp;" "&amp;IF(ISNUMBER($C24),IF($C24=0,"0",ROUND($C24,9-INT(LOG10(ABS($C24))))&amp;""),$C24&amp;"")&amp;" "&amp;IF(ISNUMBER($D24),IF($D24=0,"0",ROUND($D24,9-INT(LOG10(ABS($D24))))&amp;""),$D24&amp;"")))</f>
         <v/>
       </c>
       <c r="K24" s="3">
-        <f>IF($A24="","",IF(($I24=""),"",IFERROR(VLOOKUP($I24,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A24=""),"",IF(EXACT($I24,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I24)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I24)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I24)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L24" s="3">
-        <f>IF($A24="","",IF(AND(NOT(($I24="")),($K24=$J24)),1,0))</f>
+        <f>IF(AND($A24=""),"",IF(AND(NOT(EXACT($I24,"")),EXACT($K24,$J24)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M24" s="3">
+        <f>IF(AND($A24=""),"",MID(IF(AND(NOT(($B24="")),($E24="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N24" s="3">
+        <f>IF(OR(AND(NOT(($B24="")),($E24=""))),2,0)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n"/>
+      <c r="A25" s="4" t="n"/>
       <c r="B25" s="4" t="n"/>
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="3">
-        <f>IF($A25="","",IFERROR(VLOOKUP($B25,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A25=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B25)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B25)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B25)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G25" s="3">
-        <f>IF($A25="","",IF(($C25="Conf"),IFERROR(VLOOKUP($B25,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B25,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A25=""),"",IF(EXACT($C25,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B25)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B25)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B25)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B25)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B25)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B25)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H25" s="3">
-        <f>IF($A25="","",IFERROR(VLOOKUP($E25,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A25=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E25)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E25)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E25)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I25" s="3">
-        <f>IF($A25="","",IF(OR(($E25=""),($B25="")),"",($E25&amp;"|"&amp;$B25)))</f>
+        <f>IF(AND($A25=""),"",IF(OR(($E25=""),($B25="")),"",(IF(ISNUMBER($E25),IF($E25=0,"0",ROUND($E25,9-INT(LOG10(ABS($E25))))&amp;""),$E25&amp;"")&amp;"|"&amp;IF(ISNUMBER($B25),IF($B25=0,"0",ROUND($B25,9-INT(LOG10(ABS($B25))))&amp;""),$B25&amp;""))))</f>
         <v/>
       </c>
       <c r="J25" s="3">
-        <f>IF($A25="","",($B25&amp;" "&amp;$C25&amp;" "&amp;$D25))</f>
+        <f>IF(AND($A25=""),"",(IF(ISNUMBER($B25),IF($B25=0,"0",ROUND($B25,9-INT(LOG10(ABS($B25))))&amp;""),$B25&amp;"")&amp;" "&amp;IF(ISNUMBER($C25),IF($C25=0,"0",ROUND($C25,9-INT(LOG10(ABS($C25))))&amp;""),$C25&amp;"")&amp;" "&amp;IF(ISNUMBER($D25),IF($D25=0,"0",ROUND($D25,9-INT(LOG10(ABS($D25))))&amp;""),$D25&amp;"")))</f>
         <v/>
       </c>
       <c r="K25" s="3">
-        <f>IF($A25="","",IF(($I25=""),"",IFERROR(VLOOKUP($I25,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A25=""),"",IF(EXACT($I25,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I25)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I25)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I25)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L25" s="3">
-        <f>IF($A25="","",IF(AND(NOT(($I25="")),($K25=$J25)),1,0))</f>
+        <f>IF(AND($A25=""),"",IF(AND(NOT(EXACT($I25,"")),EXACT($K25,$J25)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M25" s="3">
+        <f>IF(AND($A25=""),"",MID(IF(AND(NOT(($B25="")),($E25="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N25" s="3">
+        <f>IF(OR(AND(NOT(($B25="")),($E25=""))),2,0)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n"/>
+      <c r="A26" s="4" t="n"/>
       <c r="B26" s="4" t="n"/>
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="3">
-        <f>IF($A26="","",IFERROR(VLOOKUP($B26,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A26=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B26)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B26)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B26)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G26" s="3">
-        <f>IF($A26="","",IF(($C26="Conf"),IFERROR(VLOOKUP($B26,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B26,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A26=""),"",IF(EXACT($C26,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B26)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B26)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B26)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B26)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B26)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B26)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H26" s="3">
-        <f>IF($A26="","",IFERROR(VLOOKUP($E26,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A26=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E26)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E26)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E26)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I26" s="3">
-        <f>IF($A26="","",IF(OR(($E26=""),($B26="")),"",($E26&amp;"|"&amp;$B26)))</f>
+        <f>IF(AND($A26=""),"",IF(OR(($E26=""),($B26="")),"",(IF(ISNUMBER($E26),IF($E26=0,"0",ROUND($E26,9-INT(LOG10(ABS($E26))))&amp;""),$E26&amp;"")&amp;"|"&amp;IF(ISNUMBER($B26),IF($B26=0,"0",ROUND($B26,9-INT(LOG10(ABS($B26))))&amp;""),$B26&amp;""))))</f>
         <v/>
       </c>
       <c r="J26" s="3">
-        <f>IF($A26="","",($B26&amp;" "&amp;$C26&amp;" "&amp;$D26))</f>
+        <f>IF(AND($A26=""),"",(IF(ISNUMBER($B26),IF($B26=0,"0",ROUND($B26,9-INT(LOG10(ABS($B26))))&amp;""),$B26&amp;"")&amp;" "&amp;IF(ISNUMBER($C26),IF($C26=0,"0",ROUND($C26,9-INT(LOG10(ABS($C26))))&amp;""),$C26&amp;"")&amp;" "&amp;IF(ISNUMBER($D26),IF($D26=0,"0",ROUND($D26,9-INT(LOG10(ABS($D26))))&amp;""),$D26&amp;"")))</f>
         <v/>
       </c>
       <c r="K26" s="3">
-        <f>IF($A26="","",IF(($I26=""),"",IFERROR(VLOOKUP($I26,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A26=""),"",IF(EXACT($I26,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I26)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I26)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I26)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L26" s="3">
-        <f>IF($A26="","",IF(AND(NOT(($I26="")),($K26=$J26)),1,0))</f>
+        <f>IF(AND($A26=""),"",IF(AND(NOT(EXACT($I26,"")),EXACT($K26,$J26)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M26" s="3">
+        <f>IF(AND($A26=""),"",MID(IF(AND(NOT(($B26="")),($E26="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N26" s="3">
+        <f>IF(OR(AND(NOT(($B26="")),($E26=""))),2,0)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n"/>
+      <c r="A27" s="4" t="n"/>
       <c r="B27" s="4" t="n"/>
       <c r="C27" s="4" t="n"/>
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="3">
-        <f>IF($A27="","",IFERROR(VLOOKUP($B27,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A27=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B27)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B27)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B27)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G27" s="3">
-        <f>IF($A27="","",IF(($C27="Conf"),IFERROR(VLOOKUP($B27,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B27,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A27=""),"",IF(EXACT($C27,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B27)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B27)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B27)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B27)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B27)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B27)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H27" s="3">
-        <f>IF($A27="","",IFERROR(VLOOKUP($E27,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A27=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E27)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E27)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E27)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I27" s="3">
-        <f>IF($A27="","",IF(OR(($E27=""),($B27="")),"",($E27&amp;"|"&amp;$B27)))</f>
+        <f>IF(AND($A27=""),"",IF(OR(($E27=""),($B27="")),"",(IF(ISNUMBER($E27),IF($E27=0,"0",ROUND($E27,9-INT(LOG10(ABS($E27))))&amp;""),$E27&amp;"")&amp;"|"&amp;IF(ISNUMBER($B27),IF($B27=0,"0",ROUND($B27,9-INT(LOG10(ABS($B27))))&amp;""),$B27&amp;""))))</f>
         <v/>
       </c>
       <c r="J27" s="3">
-        <f>IF($A27="","",($B27&amp;" "&amp;$C27&amp;" "&amp;$D27))</f>
+        <f>IF(AND($A27=""),"",(IF(ISNUMBER($B27),IF($B27=0,"0",ROUND($B27,9-INT(LOG10(ABS($B27))))&amp;""),$B27&amp;"")&amp;" "&amp;IF(ISNUMBER($C27),IF($C27=0,"0",ROUND($C27,9-INT(LOG10(ABS($C27))))&amp;""),$C27&amp;"")&amp;" "&amp;IF(ISNUMBER($D27),IF($D27=0,"0",ROUND($D27,9-INT(LOG10(ABS($D27))))&amp;""),$D27&amp;"")))</f>
         <v/>
       </c>
       <c r="K27" s="3">
-        <f>IF($A27="","",IF(($I27=""),"",IFERROR(VLOOKUP($I27,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A27=""),"",IF(EXACT($I27,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I27)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I27)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I27)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L27" s="3">
-        <f>IF($A27="","",IF(AND(NOT(($I27="")),($K27=$J27)),1,0))</f>
+        <f>IF(AND($A27=""),"",IF(AND(NOT(EXACT($I27,"")),EXACT($K27,$J27)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M27" s="3">
+        <f>IF(AND($A27=""),"",MID(IF(AND(NOT(($B27="")),($E27="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N27" s="3">
+        <f>IF(OR(AND(NOT(($B27="")),($E27=""))),2,0)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n"/>
+      <c r="A28" s="4" t="n"/>
       <c r="B28" s="4" t="n"/>
       <c r="C28" s="4" t="n"/>
       <c r="D28" s="4" t="n"/>
       <c r="E28" s="4" t="n"/>
       <c r="F28" s="3">
-        <f>IF($A28="","",IFERROR(VLOOKUP($B28,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A28=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B28)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B28)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B28)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G28" s="3">
-        <f>IF($A28="","",IF(($C28="Conf"),IFERROR(VLOOKUP($B28,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B28,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A28=""),"",IF(EXACT($C28,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B28)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B28)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B28)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B28)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B28)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B28)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H28" s="3">
-        <f>IF($A28="","",IFERROR(VLOOKUP($E28,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A28=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E28)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E28)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E28)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I28" s="3">
-        <f>IF($A28="","",IF(OR(($E28=""),($B28="")),"",($E28&amp;"|"&amp;$B28)))</f>
+        <f>IF(AND($A28=""),"",IF(OR(($E28=""),($B28="")),"",(IF(ISNUMBER($E28),IF($E28=0,"0",ROUND($E28,9-INT(LOG10(ABS($E28))))&amp;""),$E28&amp;"")&amp;"|"&amp;IF(ISNUMBER($B28),IF($B28=0,"0",ROUND($B28,9-INT(LOG10(ABS($B28))))&amp;""),$B28&amp;""))))</f>
         <v/>
       </c>
       <c r="J28" s="3">
-        <f>IF($A28="","",($B28&amp;" "&amp;$C28&amp;" "&amp;$D28))</f>
+        <f>IF(AND($A28=""),"",(IF(ISNUMBER($B28),IF($B28=0,"0",ROUND($B28,9-INT(LOG10(ABS($B28))))&amp;""),$B28&amp;"")&amp;" "&amp;IF(ISNUMBER($C28),IF($C28=0,"0",ROUND($C28,9-INT(LOG10(ABS($C28))))&amp;""),$C28&amp;"")&amp;" "&amp;IF(ISNUMBER($D28),IF($D28=0,"0",ROUND($D28,9-INT(LOG10(ABS($D28))))&amp;""),$D28&amp;"")))</f>
         <v/>
       </c>
       <c r="K28" s="3">
-        <f>IF($A28="","",IF(($I28=""),"",IFERROR(VLOOKUP($I28,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A28=""),"",IF(EXACT($I28,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I28)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I28)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I28)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L28" s="3">
-        <f>IF($A28="","",IF(AND(NOT(($I28="")),($K28=$J28)),1,0))</f>
+        <f>IF(AND($A28=""),"",IF(AND(NOT(EXACT($I28,"")),EXACT($K28,$J28)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M28" s="3">
+        <f>IF(AND($A28=""),"",MID(IF(AND(NOT(($B28="")),($E28="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N28" s="3">
+        <f>IF(OR(AND(NOT(($B28="")),($E28=""))),2,0)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n"/>
+      <c r="A29" s="4" t="n"/>
       <c r="B29" s="4" t="n"/>
       <c r="C29" s="4" t="n"/>
       <c r="D29" s="4" t="n"/>
       <c r="E29" s="4" t="n"/>
       <c r="F29" s="3">
-        <f>IF($A29="","",IFERROR(VLOOKUP($B29,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A29=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B29)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B29)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B29)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G29" s="3">
-        <f>IF($A29="","",IF(($C29="Conf"),IFERROR(VLOOKUP($B29,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B29,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A29=""),"",IF(EXACT($C29,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B29)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B29)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B29)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B29)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B29)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B29)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H29" s="3">
-        <f>IF($A29="","",IFERROR(VLOOKUP($E29,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A29=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E29)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E29)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E29)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I29" s="3">
-        <f>IF($A29="","",IF(OR(($E29=""),($B29="")),"",($E29&amp;"|"&amp;$B29)))</f>
+        <f>IF(AND($A29=""),"",IF(OR(($E29=""),($B29="")),"",(IF(ISNUMBER($E29),IF($E29=0,"0",ROUND($E29,9-INT(LOG10(ABS($E29))))&amp;""),$E29&amp;"")&amp;"|"&amp;IF(ISNUMBER($B29),IF($B29=0,"0",ROUND($B29,9-INT(LOG10(ABS($B29))))&amp;""),$B29&amp;""))))</f>
         <v/>
       </c>
       <c r="J29" s="3">
-        <f>IF($A29="","",($B29&amp;" "&amp;$C29&amp;" "&amp;$D29))</f>
+        <f>IF(AND($A29=""),"",(IF(ISNUMBER($B29),IF($B29=0,"0",ROUND($B29,9-INT(LOG10(ABS($B29))))&amp;""),$B29&amp;"")&amp;" "&amp;IF(ISNUMBER($C29),IF($C29=0,"0",ROUND($C29,9-INT(LOG10(ABS($C29))))&amp;""),$C29&amp;"")&amp;" "&amp;IF(ISNUMBER($D29),IF($D29=0,"0",ROUND($D29,9-INT(LOG10(ABS($D29))))&amp;""),$D29&amp;"")))</f>
         <v/>
       </c>
       <c r="K29" s="3">
-        <f>IF($A29="","",IF(($I29=""),"",IFERROR(VLOOKUP($I29,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A29=""),"",IF(EXACT($I29,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I29)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I29)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I29)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L29" s="3">
-        <f>IF($A29="","",IF(AND(NOT(($I29="")),($K29=$J29)),1,0))</f>
+        <f>IF(AND($A29=""),"",IF(AND(NOT(EXACT($I29,"")),EXACT($K29,$J29)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M29" s="3">
+        <f>IF(AND($A29=""),"",MID(IF(AND(NOT(($B29="")),($E29="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N29" s="3">
+        <f>IF(OR(AND(NOT(($B29="")),($E29=""))),2,0)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n"/>
+      <c r="A30" s="4" t="n"/>
       <c r="B30" s="4" t="n"/>
       <c r="C30" s="4" t="n"/>
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="3">
-        <f>IF($A30="","",IFERROR(VLOOKUP($B30,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A30=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B30)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B30)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B30)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G30" s="3">
-        <f>IF($A30="","",IF(($C30="Conf"),IFERROR(VLOOKUP($B30,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B30,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A30=""),"",IF(EXACT($C30,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B30)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B30)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B30)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B30)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B30)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B30)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H30" s="3">
-        <f>IF($A30="","",IFERROR(VLOOKUP($E30,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A30=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E30)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E30)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E30)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I30" s="3">
-        <f>IF($A30="","",IF(OR(($E30=""),($B30="")),"",($E30&amp;"|"&amp;$B30)))</f>
+        <f>IF(AND($A30=""),"",IF(OR(($E30=""),($B30="")),"",(IF(ISNUMBER($E30),IF($E30=0,"0",ROUND($E30,9-INT(LOG10(ABS($E30))))&amp;""),$E30&amp;"")&amp;"|"&amp;IF(ISNUMBER($B30),IF($B30=0,"0",ROUND($B30,9-INT(LOG10(ABS($B30))))&amp;""),$B30&amp;""))))</f>
         <v/>
       </c>
       <c r="J30" s="3">
-        <f>IF($A30="","",($B30&amp;" "&amp;$C30&amp;" "&amp;$D30))</f>
+        <f>IF(AND($A30=""),"",(IF(ISNUMBER($B30),IF($B30=0,"0",ROUND($B30,9-INT(LOG10(ABS($B30))))&amp;""),$B30&amp;"")&amp;" "&amp;IF(ISNUMBER($C30),IF($C30=0,"0",ROUND($C30,9-INT(LOG10(ABS($C30))))&amp;""),$C30&amp;"")&amp;" "&amp;IF(ISNUMBER($D30),IF($D30=0,"0",ROUND($D30,9-INT(LOG10(ABS($D30))))&amp;""),$D30&amp;"")))</f>
         <v/>
       </c>
       <c r="K30" s="3">
-        <f>IF($A30="","",IF(($I30=""),"",IFERROR(VLOOKUP($I30,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A30=""),"",IF(EXACT($I30,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I30)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I30)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I30)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L30" s="3">
-        <f>IF($A30="","",IF(AND(NOT(($I30="")),($K30=$J30)),1,0))</f>
+        <f>IF(AND($A30=""),"",IF(AND(NOT(EXACT($I30,"")),EXACT($K30,$J30)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M30" s="3">
+        <f>IF(AND($A30=""),"",MID(IF(AND(NOT(($B30="")),($E30="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N30" s="3">
+        <f>IF(OR(AND(NOT(($B30="")),($E30=""))),2,0)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n"/>
+      <c r="A31" s="4" t="n"/>
       <c r="B31" s="4" t="n"/>
       <c r="C31" s="4" t="n"/>
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="3">
-        <f>IF($A31="","",IFERROR(VLOOKUP($B31,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A31=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B31)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B31)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B31)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G31" s="3">
-        <f>IF($A31="","",IF(($C31="Conf"),IFERROR(VLOOKUP($B31,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B31,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A31=""),"",IF(EXACT($C31,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B31)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B31)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B31)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B31)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B31)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B31)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H31" s="3">
-        <f>IF($A31="","",IFERROR(VLOOKUP($E31,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A31=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E31)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E31)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E31)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I31" s="3">
-        <f>IF($A31="","",IF(OR(($E31=""),($B31="")),"",($E31&amp;"|"&amp;$B31)))</f>
+        <f>IF(AND($A31=""),"",IF(OR(($E31=""),($B31="")),"",(IF(ISNUMBER($E31),IF($E31=0,"0",ROUND($E31,9-INT(LOG10(ABS($E31))))&amp;""),$E31&amp;"")&amp;"|"&amp;IF(ISNUMBER($B31),IF($B31=0,"0",ROUND($B31,9-INT(LOG10(ABS($B31))))&amp;""),$B31&amp;""))))</f>
         <v/>
       </c>
       <c r="J31" s="3">
-        <f>IF($A31="","",($B31&amp;" "&amp;$C31&amp;" "&amp;$D31))</f>
+        <f>IF(AND($A31=""),"",(IF(ISNUMBER($B31),IF($B31=0,"0",ROUND($B31,9-INT(LOG10(ABS($B31))))&amp;""),$B31&amp;"")&amp;" "&amp;IF(ISNUMBER($C31),IF($C31=0,"0",ROUND($C31,9-INT(LOG10(ABS($C31))))&amp;""),$C31&amp;"")&amp;" "&amp;IF(ISNUMBER($D31),IF($D31=0,"0",ROUND($D31,9-INT(LOG10(ABS($D31))))&amp;""),$D31&amp;"")))</f>
         <v/>
       </c>
       <c r="K31" s="3">
-        <f>IF($A31="","",IF(($I31=""),"",IFERROR(VLOOKUP($I31,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A31=""),"",IF(EXACT($I31,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I31)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I31)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I31)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L31" s="3">
-        <f>IF($A31="","",IF(AND(NOT(($I31="")),($K31=$J31)),1,0))</f>
+        <f>IF(AND($A31=""),"",IF(AND(NOT(EXACT($I31,"")),EXACT($K31,$J31)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M31" s="3">
+        <f>IF(AND($A31=""),"",MID(IF(AND(NOT(($B31="")),($E31="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N31" s="3">
+        <f>IF(OR(AND(NOT(($B31="")),($E31=""))),2,0)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n"/>
+      <c r="A32" s="4" t="n"/>
       <c r="B32" s="4" t="n"/>
       <c r="C32" s="4" t="n"/>
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="n"/>
       <c r="F32" s="3">
-        <f>IF($A32="","",IFERROR(VLOOKUP($B32,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A32=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B32)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B32)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B32)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G32" s="3">
-        <f>IF($A32="","",IF(($C32="Conf"),IFERROR(VLOOKUP($B32,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B32,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A32=""),"",IF(EXACT($C32,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B32)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B32)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B32)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B32)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B32)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B32)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H32" s="3">
-        <f>IF($A32="","",IFERROR(VLOOKUP($E32,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A32=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E32)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E32)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E32)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I32" s="3">
-        <f>IF($A32="","",IF(OR(($E32=""),($B32="")),"",($E32&amp;"|"&amp;$B32)))</f>
+        <f>IF(AND($A32=""),"",IF(OR(($E32=""),($B32="")),"",(IF(ISNUMBER($E32),IF($E32=0,"0",ROUND($E32,9-INT(LOG10(ABS($E32))))&amp;""),$E32&amp;"")&amp;"|"&amp;IF(ISNUMBER($B32),IF($B32=0,"0",ROUND($B32,9-INT(LOG10(ABS($B32))))&amp;""),$B32&amp;""))))</f>
         <v/>
       </c>
       <c r="J32" s="3">
-        <f>IF($A32="","",($B32&amp;" "&amp;$C32&amp;" "&amp;$D32))</f>
+        <f>IF(AND($A32=""),"",(IF(ISNUMBER($B32),IF($B32=0,"0",ROUND($B32,9-INT(LOG10(ABS($B32))))&amp;""),$B32&amp;"")&amp;" "&amp;IF(ISNUMBER($C32),IF($C32=0,"0",ROUND($C32,9-INT(LOG10(ABS($C32))))&amp;""),$C32&amp;"")&amp;" "&amp;IF(ISNUMBER($D32),IF($D32=0,"0",ROUND($D32,9-INT(LOG10(ABS($D32))))&amp;""),$D32&amp;"")))</f>
         <v/>
       </c>
       <c r="K32" s="3">
-        <f>IF($A32="","",IF(($I32=""),"",IFERROR(VLOOKUP($I32,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A32=""),"",IF(EXACT($I32,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I32)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I32)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I32)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L32" s="3">
-        <f>IF($A32="","",IF(AND(NOT(($I32="")),($K32=$J32)),1,0))</f>
+        <f>IF(AND($A32=""),"",IF(AND(NOT(EXACT($I32,"")),EXACT($K32,$J32)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M32" s="3">
+        <f>IF(AND($A32=""),"",MID(IF(AND(NOT(($B32="")),($E32="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N32" s="3">
+        <f>IF(OR(AND(NOT(($B32="")),($E32=""))),2,0)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n"/>
+      <c r="A33" s="4" t="n"/>
       <c r="B33" s="4" t="n"/>
       <c r="C33" s="4" t="n"/>
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="3">
-        <f>IF($A33="","",IFERROR(VLOOKUP($B33,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A33=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B33)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B33)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B33)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G33" s="3">
-        <f>IF($A33="","",IF(($C33="Conf"),IFERROR(VLOOKUP($B33,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B33,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A33=""),"",IF(EXACT($C33,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B33)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B33)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B33)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B33)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B33)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B33)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H33" s="3">
-        <f>IF($A33="","",IFERROR(VLOOKUP($E33,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A33=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E33)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E33)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E33)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I33" s="3">
-        <f>IF($A33="","",IF(OR(($E33=""),($B33="")),"",($E33&amp;"|"&amp;$B33)))</f>
+        <f>IF(AND($A33=""),"",IF(OR(($E33=""),($B33="")),"",(IF(ISNUMBER($E33),IF($E33=0,"0",ROUND($E33,9-INT(LOG10(ABS($E33))))&amp;""),$E33&amp;"")&amp;"|"&amp;IF(ISNUMBER($B33),IF($B33=0,"0",ROUND($B33,9-INT(LOG10(ABS($B33))))&amp;""),$B33&amp;""))))</f>
         <v/>
       </c>
       <c r="J33" s="3">
-        <f>IF($A33="","",($B33&amp;" "&amp;$C33&amp;" "&amp;$D33))</f>
+        <f>IF(AND($A33=""),"",(IF(ISNUMBER($B33),IF($B33=0,"0",ROUND($B33,9-INT(LOG10(ABS($B33))))&amp;""),$B33&amp;"")&amp;" "&amp;IF(ISNUMBER($C33),IF($C33=0,"0",ROUND($C33,9-INT(LOG10(ABS($C33))))&amp;""),$C33&amp;"")&amp;" "&amp;IF(ISNUMBER($D33),IF($D33=0,"0",ROUND($D33,9-INT(LOG10(ABS($D33))))&amp;""),$D33&amp;"")))</f>
         <v/>
       </c>
       <c r="K33" s="3">
-        <f>IF($A33="","",IF(($I33=""),"",IFERROR(VLOOKUP($I33,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A33=""),"",IF(EXACT($I33,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I33)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I33)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I33)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L33" s="3">
-        <f>IF($A33="","",IF(AND(NOT(($I33="")),($K33=$J33)),1,0))</f>
+        <f>IF(AND($A33=""),"",IF(AND(NOT(EXACT($I33,"")),EXACT($K33,$J33)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M33" s="3">
+        <f>IF(AND($A33=""),"",MID(IF(AND(NOT(($B33="")),($E33="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N33" s="3">
+        <f>IF(OR(AND(NOT(($B33="")),($E33=""))),2,0)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n"/>
+      <c r="A34" s="4" t="n"/>
       <c r="B34" s="4" t="n"/>
       <c r="C34" s="4" t="n"/>
       <c r="D34" s="4" t="n"/>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="3">
-        <f>IF($A34="","",IFERROR(VLOOKUP($B34,Asignaturas!$A$4:$L$27,2,FALSE),""))</f>
+        <f>IF(AND($A34=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B34)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B34)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B34)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="G34" s="3">
-        <f>IF($A34="","",IF(($C34="Conf"),IFERROR(VLOOKUP($B34,Asignaturas!$A$4:$L$27,4,FALSE),0),IFERROR(VLOOKUP($B34,Asignaturas!$A$4:$L$27,5,FALSE),0)))</f>
+        <f>IF(AND($A34=""),"",IF(EXACT($C34,"Conf"),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B34)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B34)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$D$4:$D$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B34)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))),IF(ISNA(MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B34)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),0,IF(ISBLANK(INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B34)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Cobertura por asignatura'!$E$4:$E$27,MATCH(1,INDEX(EXACT('Cobertura por asignatura'!$A$4:$A$27,$B34)*1*((('Cobertura por asignatura'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="H34" s="3">
-        <f>IF($A34="","",IFERROR(VLOOKUP($E34,Profesores!$A$4:$G$27,2,FALSE),""))</f>
+        <f>IF(AND($A34=""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E34)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E34)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0))),"",INDEX('Carga por profesor'!$B$4:$B$27,MATCH(1,INDEX(EXACT('Carga por profesor'!$A$4:$A$27,$E34)*1*((('Carga por profesor'!$A$4:$A$27&lt;&gt;""))&gt;0),0),0)))))</f>
         <v/>
       </c>
       <c r="I34" s="3">
-        <f>IF($A34="","",IF(OR(($E34=""),($B34="")),"",($E34&amp;"|"&amp;$B34)))</f>
+        <f>IF(AND($A34=""),"",IF(OR(($E34=""),($B34="")),"",(IF(ISNUMBER($E34),IF($E34=0,"0",ROUND($E34,9-INT(LOG10(ABS($E34))))&amp;""),$E34&amp;"")&amp;"|"&amp;IF(ISNUMBER($B34),IF($B34=0,"0",ROUND($B34,9-INT(LOG10(ABS($B34))))&amp;""),$B34&amp;""))))</f>
         <v/>
       </c>
       <c r="J34" s="3">
-        <f>IF($A34="","",($B34&amp;" "&amp;$C34&amp;" "&amp;$D34))</f>
+        <f>IF(AND($A34=""),"",(IF(ISNUMBER($B34),IF($B34=0,"0",ROUND($B34,9-INT(LOG10(ABS($B34))))&amp;""),$B34&amp;"")&amp;" "&amp;IF(ISNUMBER($C34),IF($C34=0,"0",ROUND($C34,9-INT(LOG10(ABS($C34))))&amp;""),$C34&amp;"")&amp;" "&amp;IF(ISNUMBER($D34),IF($D34=0,"0",ROUND($D34,9-INT(LOG10(ABS($D34))))&amp;""),$D34&amp;"")))</f>
         <v/>
       </c>
       <c r="K34" s="3">
-        <f>IF($A34="","",IF(($I34=""),"",IFERROR(VLOOKUP($I34,Asignacion!$I$4:$L$34,2,FALSE),"")))</f>
+        <f>IF(AND($A34=""),"",IF(EXACT($I34,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I34)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I34)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I34)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
         <v/>
       </c>
       <c r="L34" s="3">
-        <f>IF($A34="","",IF(AND(NOT(($I34="")),($K34=$J34)),1,0))</f>
+        <f>IF(AND($A34=""),"",IF(AND(NOT(EXACT($I34,"")),EXACT($K34,$J34)),1,0))</f>
+        <v/>
+      </c>
+      <c r="M34" s="3">
+        <f>IF(AND($A34=""),"",MID(IF(AND(NOT(($B34="")),($E34="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N34" s="3">
+        <f>IF(OR(AND(NOT(($B34="")),($E34=""))),2,0)</f>
         <v/>
       </c>
     </row>
@@ -1832,7 +2093,7 @@
       <c r="A37" s="6" t="n"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>falta profesor</t>
+          <t>Esta fila de carga todavia no tiene profesor</t>
         </is>
       </c>
     </row>
@@ -1845,16 +2106,17 @@
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation sqref="B4:B34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fuera del dominio" error="Ese valor no esta en la lista." type="list" errorStyle="information">
-      <formula1>"EST-CC,EST-MAT,PROB,MNUM"</formula1>
+      <formula1>'Listas'!$A$4:$A$7</formula1>
     </dataValidation>
     <dataValidation sqref="C4:C34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fuera del dominio" error="Ese valor no esta en la lista." type="list" errorStyle="information">
-      <formula1>"Conf,CP"</formula1>
+      <formula1>'Listas'!$B$4:$B$5</formula1>
     </dataValidation>
     <dataValidation sqref="E4:E34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fuera del dominio" error="Ese valor no esta en la lista." type="list" errorStyle="information">
-      <formula1>"PIAD,MARA,LUGO,ROTO"</formula1>
+      <formula1>'Listas'!$C$4:$C$7</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1863,24 +2125,26 @@
   <sheetPr>
     <tabColor rgb="008EA9DB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col hidden="1" width="24" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profesores</t>
+          <t>Carga por profesor</t>
         </is>
       </c>
     </row>
@@ -1920,6 +2184,16 @@
           <t>Lo que imparte</t>
         </is>
       </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>(nivel de las marcas)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1941,15 +2215,23 @@
         <v>160</v>
       </c>
       <c r="E4" s="3">
-        <f>IF($A4="","",SUMIF(Asignacion!$E$4:$E$34,$A4,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A4=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A4)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F4" s="3">
-        <f>IF($A4="","",SUMIF(Asignacion!$E$4:$E$34,$A4,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A4=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A4)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G4" s="3">
-        <f>IF($A4="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A4&amp;"#*"))</f>
+        <f>IF(AND($A4=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A4&amp;CHAR(30)))),($A4&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H4" s="3">
+        <f>IF(AND($A4=""),"",MID(IF((IFERROR(VALUE($E4&amp;""),0)&gt;IFERROR(VALUE($D4&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0))),IF((IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0))))))&amp;""),(IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0))),IF((IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0))))))&amp;""),(IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0))),IF((IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0))))))&amp;""),(IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0))),IF((IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0))))))&amp;""),(IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0))),IF((IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0))))))&amp;""),(IFERROR(VALUE($E4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I4" s="3">
+        <f>IF(OR((IFERROR(VALUE($E4&amp;""),0)&gt;IFERROR(VALUE($D4&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
@@ -1973,15 +2255,23 @@
         <v>80</v>
       </c>
       <c r="E5" s="3">
-        <f>IF($A5="","",SUMIF(Asignacion!$E$4:$E$34,$A5,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A5=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A5)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F5" s="3">
-        <f>IF($A5="","",SUMIF(Asignacion!$E$4:$E$34,$A5,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A5=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A5)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G5" s="3">
-        <f>IF($A5="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A5&amp;"#*"))</f>
+        <f>IF(AND($A5=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A5&amp;CHAR(30)))),($A5&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H5" s="3">
+        <f>IF(AND($A5=""),"",MID(IF((IFERROR(VALUE($E5&amp;""),0)&gt;IFERROR(VALUE($D5&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0))),IF((IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0))))))&amp;""),(IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0))),IF((IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0))))))&amp;""),(IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0))),IF((IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0))))))&amp;""),(IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0))),IF((IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0))))))&amp;""),(IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0))),IF((IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0))))))&amp;""),(IFERROR(VALUE($E5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I5" s="3">
+        <f>IF(OR((IFERROR(VALUE($E5&amp;""),0)&gt;IFERROR(VALUE($D5&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
@@ -2005,15 +2295,23 @@
         <v>160</v>
       </c>
       <c r="E6" s="3">
-        <f>IF($A6="","",SUMIF(Asignacion!$E$4:$E$34,$A6,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A6=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A6)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F6" s="3">
-        <f>IF($A6="","",SUMIF(Asignacion!$E$4:$E$34,$A6,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A6=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A6)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G6" s="3">
-        <f>IF($A6="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A6&amp;"#*"))</f>
+        <f>IF(AND($A6=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A6&amp;CHAR(30)))),($A6&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H6" s="3">
+        <f>IF(AND($A6=""),"",MID(IF((IFERROR(VALUE($E6&amp;""),0)&gt;IFERROR(VALUE($D6&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0))),IF((IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0))))))&amp;""),(IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0))),IF((IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0))))))&amp;""),(IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0))),IF((IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0))))))&amp;""),(IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0))),IF((IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0))))))&amp;""),(IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0))),IF((IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0))))))&amp;""),(IFERROR(VALUE($E6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I6" s="3">
+        <f>IF(OR((IFERROR(VALUE($E6&amp;""),0)&gt;IFERROR(VALUE($D6&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
@@ -2037,375 +2335,543 @@
         <v>160</v>
       </c>
       <c r="E7" s="3">
-        <f>IF($A7="","",SUMIF(Asignacion!$E$4:$E$34,$A7,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A7=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A7)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F7" s="3">
-        <f>IF($A7="","",SUMIF(Asignacion!$E$4:$E$34,$A7,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A7=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A7)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G7" s="3">
-        <f>IF($A7="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A7&amp;"#*"))</f>
+        <f>IF(AND($A7=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A7&amp;CHAR(30)))),($A7&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="3">
+        <f>IF(AND($A7=""),"",MID(IF((IFERROR(VALUE($E7&amp;""),0)&gt;IFERROR(VALUE($D7&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0))),IF((IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0))))))&amp;""),(IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0))),IF((IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0))))))&amp;""),(IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0))),IF((IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0))))))&amp;""),(IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0))),IF((IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0))))))&amp;""),(IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0))),IF((IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0))))))&amp;""),(IFERROR(VALUE($E7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I7" s="3">
+        <f>IF(OR((IFERROR(VALUE($E7&amp;""),0)&gt;IFERROR(VALUE($D7&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
       <c r="E8" s="3">
-        <f>IF($A8="","",SUMIF(Asignacion!$E$4:$E$34,$A8,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A8=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A8)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F8" s="3">
-        <f>IF($A8="","",SUMIF(Asignacion!$E$4:$E$34,$A8,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A8=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A8)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G8" s="3">
-        <f>IF($A8="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A8&amp;"#*"))</f>
+        <f>IF(AND($A8=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A8&amp;CHAR(30)))),($A8&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="3">
+        <f>IF(AND($A8=""),"",MID(IF((IFERROR(VALUE($E8&amp;""),0)&gt;IFERROR(VALUE($D8&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0))),IF((IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0))))))&amp;""),(IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0))),IF((IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0))))))&amp;""),(IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0))),IF((IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0))))))&amp;""),(IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0))),IF((IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0))))))&amp;""),(IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0))),IF((IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0))))))&amp;""),(IFERROR(VALUE($E8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I8" s="3">
+        <f>IF(OR((IFERROR(VALUE($E8&amp;""),0)&gt;IFERROR(VALUE($D8&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
       <c r="E9" s="3">
-        <f>IF($A9="","",SUMIF(Asignacion!$E$4:$E$34,$A9,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A9=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A9)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F9" s="3">
-        <f>IF($A9="","",SUMIF(Asignacion!$E$4:$E$34,$A9,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A9=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A9)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G9" s="3">
-        <f>IF($A9="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A9&amp;"#*"))</f>
+        <f>IF(AND($A9=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A9&amp;CHAR(30)))),($A9&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="3">
+        <f>IF(AND($A9=""),"",MID(IF((IFERROR(VALUE($E9&amp;""),0)&gt;IFERROR(VALUE($D9&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0))),IF((IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0))))))&amp;""),(IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0))),IF((IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0))))))&amp;""),(IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0))),IF((IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0))))))&amp;""),(IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0))),IF((IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0))))))&amp;""),(IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0))),IF((IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0))))))&amp;""),(IFERROR(VALUE($E9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I9" s="3">
+        <f>IF(OR((IFERROR(VALUE($E9&amp;""),0)&gt;IFERROR(VALUE($D9&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
       <c r="E10" s="3">
-        <f>IF($A10="","",SUMIF(Asignacion!$E$4:$E$34,$A10,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A10=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A10)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F10" s="3">
-        <f>IF($A10="","",SUMIF(Asignacion!$E$4:$E$34,$A10,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A10=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A10)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G10" s="3">
-        <f>IF($A10="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A10&amp;"#*"))</f>
+        <f>IF(AND($A10=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A10&amp;CHAR(30)))),($A10&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="3">
+        <f>IF(AND($A10=""),"",MID(IF((IFERROR(VALUE($E10&amp;""),0)&gt;IFERROR(VALUE($D10&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0))),IF((IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0))))))&amp;""),(IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0))),IF((IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0))))))&amp;""),(IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0))),IF((IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0))))))&amp;""),(IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0))),IF((IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0))))))&amp;""),(IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0))),IF((IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0))))))&amp;""),(IFERROR(VALUE($E10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I10" s="3">
+        <f>IF(OR((IFERROR(VALUE($E10&amp;""),0)&gt;IFERROR(VALUE($D10&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
       <c r="E11" s="3">
-        <f>IF($A11="","",SUMIF(Asignacion!$E$4:$E$34,$A11,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A11=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A11)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F11" s="3">
-        <f>IF($A11="","",SUMIF(Asignacion!$E$4:$E$34,$A11,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A11=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A11)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G11" s="3">
-        <f>IF($A11="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A11&amp;"#*"))</f>
+        <f>IF(AND($A11=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A11&amp;CHAR(30)))),($A11&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="3">
+        <f>IF(AND($A11=""),"",MID(IF((IFERROR(VALUE($E11&amp;""),0)&gt;IFERROR(VALUE($D11&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0))),IF((IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0))))))&amp;""),(IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0))),IF((IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0))))))&amp;""),(IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0))),IF((IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0))))))&amp;""),(IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0))),IF((IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0))))))&amp;""),(IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0))),IF((IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0))))))&amp;""),(IFERROR(VALUE($E11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I11" s="3">
+        <f>IF(OR((IFERROR(VALUE($E11&amp;""),0)&gt;IFERROR(VALUE($D11&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
       <c r="E12" s="3">
-        <f>IF($A12="","",SUMIF(Asignacion!$E$4:$E$34,$A12,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A12=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A12)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F12" s="3">
-        <f>IF($A12="","",SUMIF(Asignacion!$E$4:$E$34,$A12,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A12=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A12)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G12" s="3">
-        <f>IF($A12="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A12&amp;"#*"))</f>
+        <f>IF(AND($A12=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A12&amp;CHAR(30)))),($A12&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="3">
+        <f>IF(AND($A12=""),"",MID(IF((IFERROR(VALUE($E12&amp;""),0)&gt;IFERROR(VALUE($D12&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0))),IF((IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0))))))&amp;""),(IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0))),IF((IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0))))))&amp;""),(IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0))),IF((IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0))))))&amp;""),(IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0))),IF((IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0))))))&amp;""),(IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0))),IF((IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0))))))&amp;""),(IFERROR(VALUE($E12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I12" s="3">
+        <f>IF(OR((IFERROR(VALUE($E12&amp;""),0)&gt;IFERROR(VALUE($D12&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n"/>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
       <c r="E13" s="3">
-        <f>IF($A13="","",SUMIF(Asignacion!$E$4:$E$34,$A13,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A13=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A13)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F13" s="3">
-        <f>IF($A13="","",SUMIF(Asignacion!$E$4:$E$34,$A13,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A13=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A13)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G13" s="3">
-        <f>IF($A13="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A13&amp;"#*"))</f>
+        <f>IF(AND($A13=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A13&amp;CHAR(30)))),($A13&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="3">
+        <f>IF(AND($A13=""),"",MID(IF((IFERROR(VALUE($E13&amp;""),0)&gt;IFERROR(VALUE($D13&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0))),IF((IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0))))))&amp;""),(IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0))),IF((IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0))))))&amp;""),(IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0))),IF((IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0))))))&amp;""),(IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0))),IF((IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0))))))&amp;""),(IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0))),IF((IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0))))))&amp;""),(IFERROR(VALUE($E13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I13" s="3">
+        <f>IF(OR((IFERROR(VALUE($E13&amp;""),0)&gt;IFERROR(VALUE($D13&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
       <c r="E14" s="3">
-        <f>IF($A14="","",SUMIF(Asignacion!$E$4:$E$34,$A14,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A14=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A14)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F14" s="3">
-        <f>IF($A14="","",SUMIF(Asignacion!$E$4:$E$34,$A14,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A14=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A14)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G14" s="3">
-        <f>IF($A14="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A14&amp;"#*"))</f>
+        <f>IF(AND($A14=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A14&amp;CHAR(30)))),($A14&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="3">
+        <f>IF(AND($A14=""),"",MID(IF((IFERROR(VALUE($E14&amp;""),0)&gt;IFERROR(VALUE($D14&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0))),IF((IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0))))))&amp;""),(IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0))),IF((IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0))))))&amp;""),(IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0))),IF((IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0))))))&amp;""),(IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0))),IF((IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0))))))&amp;""),(IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0))),IF((IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0))))))&amp;""),(IFERROR(VALUE($E14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I14" s="3">
+        <f>IF(OR((IFERROR(VALUE($E14&amp;""),0)&gt;IFERROR(VALUE($D14&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
       <c r="E15" s="3">
-        <f>IF($A15="","",SUMIF(Asignacion!$E$4:$E$34,$A15,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A15=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A15)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F15" s="3">
-        <f>IF($A15="","",SUMIF(Asignacion!$E$4:$E$34,$A15,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A15=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A15)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G15" s="3">
-        <f>IF($A15="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A15&amp;"#*"))</f>
+        <f>IF(AND($A15=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A15&amp;CHAR(30)))),($A15&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="3">
+        <f>IF(AND($A15=""),"",MID(IF((IFERROR(VALUE($E15&amp;""),0)&gt;IFERROR(VALUE($D15&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0))),IF((IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0))))))&amp;""),(IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0))),IF((IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0))))))&amp;""),(IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0))),IF((IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0))))))&amp;""),(IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0))),IF((IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0))))))&amp;""),(IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0))),IF((IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0))))))&amp;""),(IFERROR(VALUE($E15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I15" s="3">
+        <f>IF(OR((IFERROR(VALUE($E15&amp;""),0)&gt;IFERROR(VALUE($D15&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n"/>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
       <c r="E16" s="3">
-        <f>IF($A16="","",SUMIF(Asignacion!$E$4:$E$34,$A16,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A16=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A16)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F16" s="3">
-        <f>IF($A16="","",SUMIF(Asignacion!$E$4:$E$34,$A16,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A16=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A16)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G16" s="3">
-        <f>IF($A16="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A16&amp;"#*"))</f>
+        <f>IF(AND($A16=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A16&amp;CHAR(30)))),($A16&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="3">
+        <f>IF(AND($A16=""),"",MID(IF((IFERROR(VALUE($E16&amp;""),0)&gt;IFERROR(VALUE($D16&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0))),IF((IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0))))))&amp;""),(IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0))),IF((IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0))))))&amp;""),(IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0))),IF((IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0))))))&amp;""),(IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0))),IF((IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0))))))&amp;""),(IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0))),IF((IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0))))))&amp;""),(IFERROR(VALUE($E16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I16" s="3">
+        <f>IF(OR((IFERROR(VALUE($E16&amp;""),0)&gt;IFERROR(VALUE($D16&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
       <c r="E17" s="3">
-        <f>IF($A17="","",SUMIF(Asignacion!$E$4:$E$34,$A17,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A17=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A17)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F17" s="3">
-        <f>IF($A17="","",SUMIF(Asignacion!$E$4:$E$34,$A17,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A17=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A17)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G17" s="3">
-        <f>IF($A17="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A17&amp;"#*"))</f>
+        <f>IF(AND($A17=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A17&amp;CHAR(30)))),($A17&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="3">
+        <f>IF(AND($A17=""),"",MID(IF((IFERROR(VALUE($E17&amp;""),0)&gt;IFERROR(VALUE($D17&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0))),IF((IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0))))))&amp;""),(IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0))),IF((IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0))))))&amp;""),(IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0))),IF((IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0))))))&amp;""),(IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0))),IF((IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0))))))&amp;""),(IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0))),IF((IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0))))))&amp;""),(IFERROR(VALUE($E17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I17" s="3">
+        <f>IF(OR((IFERROR(VALUE($E17&amp;""),0)&gt;IFERROR(VALUE($D17&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n"/>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
       <c r="E18" s="3">
-        <f>IF($A18="","",SUMIF(Asignacion!$E$4:$E$34,$A18,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A18=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A18)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F18" s="3">
-        <f>IF($A18="","",SUMIF(Asignacion!$E$4:$E$34,$A18,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A18=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A18)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G18" s="3">
-        <f>IF($A18="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A18&amp;"#*"))</f>
+        <f>IF(AND($A18=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A18&amp;CHAR(30)))),($A18&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="3">
+        <f>IF(AND($A18=""),"",MID(IF((IFERROR(VALUE($E18&amp;""),0)&gt;IFERROR(VALUE($D18&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0))),IF((IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0))))))&amp;""),(IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0))),IF((IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0))))))&amp;""),(IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0))),IF((IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0))))))&amp;""),(IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0))),IF((IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0))))))&amp;""),(IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0))),IF((IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0))))))&amp;""),(IFERROR(VALUE($E18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I18" s="3">
+        <f>IF(OR((IFERROR(VALUE($E18&amp;""),0)&gt;IFERROR(VALUE($D18&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
       <c r="E19" s="3">
-        <f>IF($A19="","",SUMIF(Asignacion!$E$4:$E$34,$A19,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A19=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A19)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F19" s="3">
-        <f>IF($A19="","",SUMIF(Asignacion!$E$4:$E$34,$A19,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A19=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A19)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G19" s="3">
-        <f>IF($A19="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A19&amp;"#*"))</f>
+        <f>IF(AND($A19=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A19&amp;CHAR(30)))),($A19&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="3">
+        <f>IF(AND($A19=""),"",MID(IF((IFERROR(VALUE($E19&amp;""),0)&gt;IFERROR(VALUE($D19&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0))),IF((IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0))))))&amp;""),(IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0))),IF((IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0))))))&amp;""),(IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0))),IF((IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0))))))&amp;""),(IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0))),IF((IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0))))))&amp;""),(IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0))),IF((IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0))))))&amp;""),(IFERROR(VALUE($E19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I19" s="3">
+        <f>IF(OR((IFERROR(VALUE($E19&amp;""),0)&gt;IFERROR(VALUE($D19&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n"/>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
       <c r="E20" s="3">
-        <f>IF($A20="","",SUMIF(Asignacion!$E$4:$E$34,$A20,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A20=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A20)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F20" s="3">
-        <f>IF($A20="","",SUMIF(Asignacion!$E$4:$E$34,$A20,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A20=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A20)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G20" s="3">
-        <f>IF($A20="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A20&amp;"#*"))</f>
+        <f>IF(AND($A20=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A20&amp;CHAR(30)))),($A20&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="3">
+        <f>IF(AND($A20=""),"",MID(IF((IFERROR(VALUE($E20&amp;""),0)&gt;IFERROR(VALUE($D20&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0))),IF((IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0))))))&amp;""),(IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0))),IF((IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0))))))&amp;""),(IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0))),IF((IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0))))))&amp;""),(IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0))),IF((IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0))))))&amp;""),(IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0))),IF((IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0))))))&amp;""),(IFERROR(VALUE($E20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I20" s="3">
+        <f>IF(OR((IFERROR(VALUE($E20&amp;""),0)&gt;IFERROR(VALUE($D20&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n"/>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
       <c r="E21" s="3">
-        <f>IF($A21="","",SUMIF(Asignacion!$E$4:$E$34,$A21,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A21=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A21)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F21" s="3">
-        <f>IF($A21="","",SUMIF(Asignacion!$E$4:$E$34,$A21,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A21=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A21)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G21" s="3">
-        <f>IF($A21="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A21&amp;"#*"))</f>
+        <f>IF(AND($A21=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A21&amp;CHAR(30)))),($A21&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="3">
+        <f>IF(AND($A21=""),"",MID(IF((IFERROR(VALUE($E21&amp;""),0)&gt;IFERROR(VALUE($D21&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0))),IF((IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0))))))&amp;""),(IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0))),IF((IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0))))))&amp;""),(IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0))),IF((IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0))))))&amp;""),(IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0))),IF((IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0))))))&amp;""),(IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0))),IF((IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0))))))&amp;""),(IFERROR(VALUE($E21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I21" s="3">
+        <f>IF(OR((IFERROR(VALUE($E21&amp;""),0)&gt;IFERROR(VALUE($D21&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n"/>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
       <c r="E22" s="3">
-        <f>IF($A22="","",SUMIF(Asignacion!$E$4:$E$34,$A22,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A22=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A22)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F22" s="3">
-        <f>IF($A22="","",SUMIF(Asignacion!$E$4:$E$34,$A22,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A22=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A22)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G22" s="3">
-        <f>IF($A22="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A22&amp;"#*"))</f>
+        <f>IF(AND($A22=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A22&amp;CHAR(30)))),($A22&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="3">
+        <f>IF(AND($A22=""),"",MID(IF((IFERROR(VALUE($E22&amp;""),0)&gt;IFERROR(VALUE($D22&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0))),IF((IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0))))))&amp;""),(IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0))),IF((IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0))))))&amp;""),(IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0))),IF((IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0))))))&amp;""),(IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0))),IF((IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0))))))&amp;""),(IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0))),IF((IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0))))))&amp;""),(IFERROR(VALUE($E22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I22" s="3">
+        <f>IF(OR((IFERROR(VALUE($E22&amp;""),0)&gt;IFERROR(VALUE($D22&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n"/>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
       <c r="E23" s="3">
-        <f>IF($A23="","",SUMIF(Asignacion!$E$4:$E$34,$A23,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A23=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A23)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F23" s="3">
-        <f>IF($A23="","",SUMIF(Asignacion!$E$4:$E$34,$A23,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A23=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A23)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G23" s="3">
-        <f>IF($A23="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A23&amp;"#*"))</f>
+        <f>IF(AND($A23=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A23&amp;CHAR(30)))),($A23&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="3">
+        <f>IF(AND($A23=""),"",MID(IF((IFERROR(VALUE($E23&amp;""),0)&gt;IFERROR(VALUE($D23&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0))),IF((IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0))))))&amp;""),(IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0))),IF((IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0))))))&amp;""),(IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0))),IF((IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0))))))&amp;""),(IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0))),IF((IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0))))))&amp;""),(IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0))),IF((IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0))))))&amp;""),(IFERROR(VALUE($E23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I23" s="3">
+        <f>IF(OR((IFERROR(VALUE($E23&amp;""),0)&gt;IFERROR(VALUE($D23&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n"/>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
       <c r="E24" s="3">
-        <f>IF($A24="","",SUMIF(Asignacion!$E$4:$E$34,$A24,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A24=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A24)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F24" s="3">
-        <f>IF($A24="","",SUMIF(Asignacion!$E$4:$E$34,$A24,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A24=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A24)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G24" s="3">
-        <f>IF($A24="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A24&amp;"#*"))</f>
+        <f>IF(AND($A24=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A24&amp;CHAR(30)))),($A24&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="3">
+        <f>IF(AND($A24=""),"",MID(IF((IFERROR(VALUE($E24&amp;""),0)&gt;IFERROR(VALUE($D24&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0))),IF((IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0))))))&amp;""),(IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0))),IF((IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0))))))&amp;""),(IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0))),IF((IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0))))))&amp;""),(IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0))),IF((IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0))))))&amp;""),(IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0))),IF((IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0))))))&amp;""),(IFERROR(VALUE($E24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I24" s="3">
+        <f>IF(OR((IFERROR(VALUE($E24&amp;""),0)&gt;IFERROR(VALUE($D24&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n"/>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
       <c r="E25" s="3">
-        <f>IF($A25="","",SUMIF(Asignacion!$E$4:$E$34,$A25,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A25=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A25)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F25" s="3">
-        <f>IF($A25="","",SUMIF(Asignacion!$E$4:$E$34,$A25,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A25=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A25)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G25" s="3">
-        <f>IF($A25="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A25&amp;"#*"))</f>
+        <f>IF(AND($A25=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A25&amp;CHAR(30)))),($A25&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="3">
+        <f>IF(AND($A25=""),"",MID(IF((IFERROR(VALUE($E25&amp;""),0)&gt;IFERROR(VALUE($D25&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0))),IF((IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0))))))&amp;""),(IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0))),IF((IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0))))))&amp;""),(IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0))),IF((IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0))))))&amp;""),(IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0))),IF((IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0))))))&amp;""),(IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0))),IF((IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0))))))&amp;""),(IFERROR(VALUE($E25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I25" s="3">
+        <f>IF(OR((IFERROR(VALUE($E25&amp;""),0)&gt;IFERROR(VALUE($D25&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
       <c r="E26" s="3">
-        <f>IF($A26="","",SUMIF(Asignacion!$E$4:$E$34,$A26,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A26=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A26)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F26" s="3">
-        <f>IF($A26="","",SUMIF(Asignacion!$E$4:$E$34,$A26,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A26=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A26)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G26" s="3">
-        <f>IF($A26="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A26&amp;"#*"))</f>
+        <f>IF(AND($A26=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A26&amp;CHAR(30)))),($A26&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="3">
+        <f>IF(AND($A26=""),"",MID(IF((IFERROR(VALUE($E26&amp;""),0)&gt;IFERROR(VALUE($D26&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0))),IF((IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0))))))&amp;""),(IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0))),IF((IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0))))))&amp;""),(IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0))),IF((IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0))))))&amp;""),(IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0))),IF((IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0))))))&amp;""),(IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0))),IF((IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0))))))&amp;""),(IFERROR(VALUE($E26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I26" s="3">
+        <f>IF(OR((IFERROR(VALUE($E26&amp;""),0)&gt;IFERROR(VALUE($D26&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n"/>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
       <c r="E27" s="3">
-        <f>IF($A27="","",SUMIF(Asignacion!$E$4:$E$34,$A27,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A27=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A27)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="F27" s="3">
-        <f>IF($A27="","",SUMIF(Asignacion!$E$4:$E$34,$A27,Asignacion!$L$4:$L$34))</f>
+        <f>IF(AND($A27=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A27)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G27" s="3">
-        <f>IF($A27="","",COUNTIF('Detalle - Lo que imparte'!$A$4:$A$11,$A27&amp;"#*"))</f>
+        <f>IF(AND($A27=""),"",SUMPRODUCT(1*EXACT(LEFT('Detalle - Lo que imparte'!$A$4:$A$11,LEN(($A27&amp;CHAR(30)))),($A27&amp;CHAR(30)))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="3">
+        <f>IF(AND($A27=""),"",MID(IF((IFERROR(VALUE($E27&amp;""),0)&gt;IFERROR(VALUE($D27&amp;""),0)),"; "&amp;IF(ISNUMBER(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0))),IF((IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0))))))&amp;""),(IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0))&amp;"")&amp;" horas")),IF(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0))),IF((IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0))))))&amp;""),(IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0))&amp;"")&amp;" horas")=0,"0",ROUND(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0))),IF((IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0))))))&amp;""),(IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0))&amp;"")&amp;" horas"),9-INT(LOG10(ABS(("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0))),IF((IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0))))))&amp;""),(IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0))&amp;"")&amp;" horas")))))&amp;""),("Pasa del tope en "&amp;IF(ISNUMBER((IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0))),IF((IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0))))))&amp;""),(IFERROR(VALUE($E27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0))&amp;"")&amp;" horas")&amp;""),""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="I27" s="3">
+        <f>IF(OR((IFERROR(VALUE($E27&amp;""),0)&gt;IFERROR(VALUE($D27&amp;""),0))),3,0)</f>
         <v/>
       </c>
     </row>
@@ -2428,15 +2894,16 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <conditionalFormatting sqref="E4:E27">
     <cfRule type="expression" priority="1" dxfId="1" stopIfTrue="0">
-      <formula>($E4&gt;$D4)</formula>
+      <formula>(IFERROR(VALUE($E4&amp;""),0)&gt;IFERROR(VALUE($D4&amp;""),0))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D27">
     <cfRule type="expression" priority="1" dxfId="1" stopIfTrue="0">
-      <formula>($E4&gt;$D4)</formula>
+      <formula>(IFERROR(VALUE($E4&amp;""),0)&gt;IFERROR(VALUE($D4&amp;""),0))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2445,29 +2912,31 @@
   <sheetPr>
     <tabColor rgb="008EA9DB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="37" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="42" customWidth="1" min="9" max="9"/>
-    <col width="42" customWidth="1" min="10" max="10"/>
-    <col width="42" customWidth="1" min="11" max="11"/>
-    <col width="42" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col hidden="1" width="24" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Asignaturas</t>
+          <t>Cobertura por asignatura</t>
         </is>
       </c>
     </row>
@@ -2532,6 +3001,16 @@
           <t>Cobertura</t>
         </is>
       </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>(nivel de las marcas)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -2559,27 +3038,35 @@
         <v>2</v>
       </c>
       <c r="G4" s="3">
-        <f>IF($A4="","",($D4+($E4*$F4)))</f>
+        <f>IF(AND($A4=""),"",(IFERROR(VALUE($D4&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E4&amp;""),0)*IFERROR(VALUE($F4&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H4" s="3">
-        <f>IF($A4="","",COUNTIF(Asignacion!$B$4:$B$34,$A4))</f>
+        <f>IF(AND($A4=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A4)))))</f>
         <v/>
       </c>
       <c r="I4" s="3">
-        <f>IF($A4="","",SUMIF(Asignacion!$B$4:$B$34,$A4,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A4=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A4)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J4" s="3">
-        <f>IF($A4="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A4,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A4=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A4)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K4" s="3">
-        <f>IF($A4="","",COUNTIFS(Asignacion!$B$4:$B$34,$A4,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A4=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A4)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L4" s="3">
-        <f>IF($A4="","",IF(($H4=0),"Sin filas de carga",IF(($I4&lt;$G4),(IF(($G4-$I4)=1,"Falta","Faltan")&amp;" "&amp;($G4-$I4)&amp;" horas de carga"),IF(($K4&gt;0),(IF($K4=1,"Falta","Faltan")&amp;" "&amp;$K4&amp;" "&amp;IF($K4=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A4=""),"",IF(EXACT($H4,0),"Sin filas de carga",IF((IFERROR(VALUE($I4&amp;""),0)&lt;IFERROR(VALUE($G4&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G4&amp;""),0)-IFERROR(VALUE($I4&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G4&amp;""),0)-IFERROR(VALUE($I4&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G4&amp;""),0)-IFERROR(VALUE($I4&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G4&amp;""),0)-IFERROR(VALUE($I4&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G4&amp;""),0)-IFERROR(VALUE($I4&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G4&amp;""),0)-IFERROR(VALUE($I4&amp;""),0))),IF((IFERROR(VALUE($G4&amp;""),0)-IFERROR(VALUE($I4&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G4&amp;""),0)-IFERROR(VALUE($I4&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G4&amp;""),0)-IFERROR(VALUE($I4&amp;""),0))))))&amp;""),(IFERROR(VALUE($G4&amp;""),0)-IFERROR(VALUE($I4&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K4&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K4&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K4&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K4&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K4&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K4&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K4),IF($K4=0,"0",ROUND($K4,9-INT(LOG10(ABS($K4))))&amp;""),$K4&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K4&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K4&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K4&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K4&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K4&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M4" s="3">
+        <f>IF(AND($A4=""),"",MID(IF(AND(NOT(($A4="")),NOT(EXACT($L4,"Completa"))),"; "&amp;IF(ISNUMBER($L4),IF($L4=0,"0",ROUND($L4,9-INT(LOG10(ABS($L4))))&amp;""),$L4&amp;""),"")&amp;IF(AND(NOT(($A4="")),EXACT($L4,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N4" s="3">
+        <f>IF(OR(AND(NOT(($A4="")),NOT(EXACT($L4,"Completa")))),2,IF(OR(AND(NOT(($A4="")),EXACT($L4,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2609,27 +3096,35 @@
         <v>1</v>
       </c>
       <c r="G5" s="3">
-        <f>IF($A5="","",($D5+($E5*$F5)))</f>
+        <f>IF(AND($A5=""),"",(IFERROR(VALUE($D5&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E5&amp;""),0)*IFERROR(VALUE($F5&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H5" s="3">
-        <f>IF($A5="","",COUNTIF(Asignacion!$B$4:$B$34,$A5))</f>
+        <f>IF(AND($A5=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A5)))))</f>
         <v/>
       </c>
       <c r="I5" s="3">
-        <f>IF($A5="","",SUMIF(Asignacion!$B$4:$B$34,$A5,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A5=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A5)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J5" s="3">
-        <f>IF($A5="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A5,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A5=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A5)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K5" s="3">
-        <f>IF($A5="","",COUNTIFS(Asignacion!$B$4:$B$34,$A5,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A5=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A5)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L5" s="3">
-        <f>IF($A5="","",IF(($H5=0),"Sin filas de carga",IF(($I5&lt;$G5),(IF(($G5-$I5)=1,"Falta","Faltan")&amp;" "&amp;($G5-$I5)&amp;" horas de carga"),IF(($K5&gt;0),(IF($K5=1,"Falta","Faltan")&amp;" "&amp;$K5&amp;" "&amp;IF($K5=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A5=""),"",IF(EXACT($H5,0),"Sin filas de carga",IF((IFERROR(VALUE($I5&amp;""),0)&lt;IFERROR(VALUE($G5&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G5&amp;""),0)-IFERROR(VALUE($I5&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G5&amp;""),0)-IFERROR(VALUE($I5&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G5&amp;""),0)-IFERROR(VALUE($I5&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G5&amp;""),0)-IFERROR(VALUE($I5&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G5&amp;""),0)-IFERROR(VALUE($I5&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G5&amp;""),0)-IFERROR(VALUE($I5&amp;""),0))),IF((IFERROR(VALUE($G5&amp;""),0)-IFERROR(VALUE($I5&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G5&amp;""),0)-IFERROR(VALUE($I5&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G5&amp;""),0)-IFERROR(VALUE($I5&amp;""),0))))))&amp;""),(IFERROR(VALUE($G5&amp;""),0)-IFERROR(VALUE($I5&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K5&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K5&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K5&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K5&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K5&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K5&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K5),IF($K5=0,"0",ROUND($K5,9-INT(LOG10(ABS($K5))))&amp;""),$K5&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K5&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K5&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K5&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K5&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K5&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M5" s="3">
+        <f>IF(AND($A5=""),"",MID(IF(AND(NOT(($A5="")),NOT(EXACT($L5,"Completa"))),"; "&amp;IF(ISNUMBER($L5),IF($L5=0,"0",ROUND($L5,9-INT(LOG10(ABS($L5))))&amp;""),$L5&amp;""),"")&amp;IF(AND(NOT(($A5="")),EXACT($L5,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N5" s="3">
+        <f>IF(OR(AND(NOT(($A5="")),NOT(EXACT($L5,"Completa")))),2,IF(OR(AND(NOT(($A5="")),EXACT($L5,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2659,27 +3154,35 @@
         <v>2</v>
       </c>
       <c r="G6" s="3">
-        <f>IF($A6="","",($D6+($E6*$F6)))</f>
+        <f>IF(AND($A6=""),"",(IFERROR(VALUE($D6&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E6&amp;""),0)*IFERROR(VALUE($F6&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H6" s="3">
-        <f>IF($A6="","",COUNTIF(Asignacion!$B$4:$B$34,$A6))</f>
+        <f>IF(AND($A6=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A6)))))</f>
         <v/>
       </c>
       <c r="I6" s="3">
-        <f>IF($A6="","",SUMIF(Asignacion!$B$4:$B$34,$A6,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A6=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A6)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J6" s="3">
-        <f>IF($A6="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A6,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A6=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A6)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K6" s="3">
-        <f>IF($A6="","",COUNTIFS(Asignacion!$B$4:$B$34,$A6,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A6=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A6)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L6" s="3">
-        <f>IF($A6="","",IF(($H6=0),"Sin filas de carga",IF(($I6&lt;$G6),(IF(($G6-$I6)=1,"Falta","Faltan")&amp;" "&amp;($G6-$I6)&amp;" horas de carga"),IF(($K6&gt;0),(IF($K6=1,"Falta","Faltan")&amp;" "&amp;$K6&amp;" "&amp;IF($K6=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A6=""),"",IF(EXACT($H6,0),"Sin filas de carga",IF((IFERROR(VALUE($I6&amp;""),0)&lt;IFERROR(VALUE($G6&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G6&amp;""),0)-IFERROR(VALUE($I6&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G6&amp;""),0)-IFERROR(VALUE($I6&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G6&amp;""),0)-IFERROR(VALUE($I6&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G6&amp;""),0)-IFERROR(VALUE($I6&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G6&amp;""),0)-IFERROR(VALUE($I6&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G6&amp;""),0)-IFERROR(VALUE($I6&amp;""),0))),IF((IFERROR(VALUE($G6&amp;""),0)-IFERROR(VALUE($I6&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G6&amp;""),0)-IFERROR(VALUE($I6&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G6&amp;""),0)-IFERROR(VALUE($I6&amp;""),0))))))&amp;""),(IFERROR(VALUE($G6&amp;""),0)-IFERROR(VALUE($I6&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K6&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K6&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K6&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K6&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K6&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K6&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K6),IF($K6=0,"0",ROUND($K6,9-INT(LOG10(ABS($K6))))&amp;""),$K6&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K6&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K6&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K6&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K6&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K6&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M6" s="3">
+        <f>IF(AND($A6=""),"",MID(IF(AND(NOT(($A6="")),NOT(EXACT($L6,"Completa"))),"; "&amp;IF(ISNUMBER($L6),IF($L6=0,"0",ROUND($L6,9-INT(LOG10(ABS($L6))))&amp;""),$L6&amp;""),"")&amp;IF(AND(NOT(($A6="")),EXACT($L6,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N6" s="3">
+        <f>IF(OR(AND(NOT(($A6="")),NOT(EXACT($L6,"Completa")))),2,IF(OR(AND(NOT(($A6="")),EXACT($L6,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
@@ -2709,667 +3212,835 @@
         <v>1</v>
       </c>
       <c r="G7" s="3">
-        <f>IF($A7="","",($D7+($E7*$F7)))</f>
+        <f>IF(AND($A7=""),"",(IFERROR(VALUE($D7&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E7&amp;""),0)*IFERROR(VALUE($F7&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H7" s="3">
-        <f>IF($A7="","",COUNTIF(Asignacion!$B$4:$B$34,$A7))</f>
+        <f>IF(AND($A7=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A7)))))</f>
         <v/>
       </c>
       <c r="I7" s="3">
-        <f>IF($A7="","",SUMIF(Asignacion!$B$4:$B$34,$A7,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A7=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A7)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J7" s="3">
-        <f>IF($A7="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A7,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A7=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A7)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K7" s="3">
-        <f>IF($A7="","",COUNTIFS(Asignacion!$B$4:$B$34,$A7,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A7=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A7)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L7" s="3">
-        <f>IF($A7="","",IF(($H7=0),"Sin filas de carga",IF(($I7&lt;$G7),(IF(($G7-$I7)=1,"Falta","Faltan")&amp;" "&amp;($G7-$I7)&amp;" horas de carga"),IF(($K7&gt;0),(IF($K7=1,"Falta","Faltan")&amp;" "&amp;$K7&amp;" "&amp;IF($K7=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A7=""),"",IF(EXACT($H7,0),"Sin filas de carga",IF((IFERROR(VALUE($I7&amp;""),0)&lt;IFERROR(VALUE($G7&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G7&amp;""),0)-IFERROR(VALUE($I7&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G7&amp;""),0)-IFERROR(VALUE($I7&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G7&amp;""),0)-IFERROR(VALUE($I7&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G7&amp;""),0)-IFERROR(VALUE($I7&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G7&amp;""),0)-IFERROR(VALUE($I7&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G7&amp;""),0)-IFERROR(VALUE($I7&amp;""),0))),IF((IFERROR(VALUE($G7&amp;""),0)-IFERROR(VALUE($I7&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G7&amp;""),0)-IFERROR(VALUE($I7&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G7&amp;""),0)-IFERROR(VALUE($I7&amp;""),0))))))&amp;""),(IFERROR(VALUE($G7&amp;""),0)-IFERROR(VALUE($I7&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K7&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K7&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K7&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K7&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K7&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K7&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K7),IF($K7=0,"0",ROUND($K7,9-INT(LOG10(ABS($K7))))&amp;""),$K7&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K7&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K7&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K7&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K7&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K7&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M7" s="3">
+        <f>IF(AND($A7=""),"",MID(IF(AND(NOT(($A7="")),NOT(EXACT($L7,"Completa"))),"; "&amp;IF(ISNUMBER($L7),IF($L7=0,"0",ROUND($L7,9-INT(LOG10(ABS($L7))))&amp;""),$L7&amp;""),"")&amp;IF(AND(NOT(($A7="")),EXACT($L7,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N7" s="3">
+        <f>IF(OR(AND(NOT(($A7="")),NOT(EXACT($L7,"Completa")))),2,IF(OR(AND(NOT(($A7="")),EXACT($L7,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
       <c r="G8" s="3">
-        <f>IF($A8="","",($D8+($E8*$F8)))</f>
+        <f>IF(AND($A8=""),"",(IFERROR(VALUE($D8&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E8&amp;""),0)*IFERROR(VALUE($F8&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H8" s="3">
-        <f>IF($A8="","",COUNTIF(Asignacion!$B$4:$B$34,$A8))</f>
+        <f>IF(AND($A8=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A8)))))</f>
         <v/>
       </c>
       <c r="I8" s="3">
-        <f>IF($A8="","",SUMIF(Asignacion!$B$4:$B$34,$A8,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A8=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A8)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J8" s="3">
-        <f>IF($A8="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A8,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A8=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A8)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K8" s="3">
-        <f>IF($A8="","",COUNTIFS(Asignacion!$B$4:$B$34,$A8,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A8=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A8)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L8" s="3">
-        <f>IF($A8="","",IF(($H8=0),"Sin filas de carga",IF(($I8&lt;$G8),(IF(($G8-$I8)=1,"Falta","Faltan")&amp;" "&amp;($G8-$I8)&amp;" horas de carga"),IF(($K8&gt;0),(IF($K8=1,"Falta","Faltan")&amp;" "&amp;$K8&amp;" "&amp;IF($K8=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A8=""),"",IF(EXACT($H8,0),"Sin filas de carga",IF((IFERROR(VALUE($I8&amp;""),0)&lt;IFERROR(VALUE($G8&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G8&amp;""),0)-IFERROR(VALUE($I8&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G8&amp;""),0)-IFERROR(VALUE($I8&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G8&amp;""),0)-IFERROR(VALUE($I8&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G8&amp;""),0)-IFERROR(VALUE($I8&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G8&amp;""),0)-IFERROR(VALUE($I8&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G8&amp;""),0)-IFERROR(VALUE($I8&amp;""),0))),IF((IFERROR(VALUE($G8&amp;""),0)-IFERROR(VALUE($I8&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G8&amp;""),0)-IFERROR(VALUE($I8&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G8&amp;""),0)-IFERROR(VALUE($I8&amp;""),0))))))&amp;""),(IFERROR(VALUE($G8&amp;""),0)-IFERROR(VALUE($I8&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K8&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K8&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K8&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K8&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K8&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K8&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K8),IF($K8=0,"0",ROUND($K8,9-INT(LOG10(ABS($K8))))&amp;""),$K8&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K8&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K8&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K8&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K8&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K8&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M8" s="3">
+        <f>IF(AND($A8=""),"",MID(IF(AND(NOT(($A8="")),NOT(EXACT($L8,"Completa"))),"; "&amp;IF(ISNUMBER($L8),IF($L8=0,"0",ROUND($L8,9-INT(LOG10(ABS($L8))))&amp;""),$L8&amp;""),"")&amp;IF(AND(NOT(($A8="")),EXACT($L8,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N8" s="3">
+        <f>IF(OR(AND(NOT(($A8="")),NOT(EXACT($L8,"Completa")))),2,IF(OR(AND(NOT(($A8="")),EXACT($L8,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
       <c r="G9" s="3">
-        <f>IF($A9="","",($D9+($E9*$F9)))</f>
+        <f>IF(AND($A9=""),"",(IFERROR(VALUE($D9&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E9&amp;""),0)*IFERROR(VALUE($F9&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H9" s="3">
-        <f>IF($A9="","",COUNTIF(Asignacion!$B$4:$B$34,$A9))</f>
+        <f>IF(AND($A9=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A9)))))</f>
         <v/>
       </c>
       <c r="I9" s="3">
-        <f>IF($A9="","",SUMIF(Asignacion!$B$4:$B$34,$A9,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A9=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A9)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J9" s="3">
-        <f>IF($A9="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A9,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A9=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A9)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K9" s="3">
-        <f>IF($A9="","",COUNTIFS(Asignacion!$B$4:$B$34,$A9,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A9=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A9)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L9" s="3">
-        <f>IF($A9="","",IF(($H9=0),"Sin filas de carga",IF(($I9&lt;$G9),(IF(($G9-$I9)=1,"Falta","Faltan")&amp;" "&amp;($G9-$I9)&amp;" horas de carga"),IF(($K9&gt;0),(IF($K9=1,"Falta","Faltan")&amp;" "&amp;$K9&amp;" "&amp;IF($K9=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A9=""),"",IF(EXACT($H9,0),"Sin filas de carga",IF((IFERROR(VALUE($I9&amp;""),0)&lt;IFERROR(VALUE($G9&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G9&amp;""),0)-IFERROR(VALUE($I9&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G9&amp;""),0)-IFERROR(VALUE($I9&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G9&amp;""),0)-IFERROR(VALUE($I9&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G9&amp;""),0)-IFERROR(VALUE($I9&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G9&amp;""),0)-IFERROR(VALUE($I9&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G9&amp;""),0)-IFERROR(VALUE($I9&amp;""),0))),IF((IFERROR(VALUE($G9&amp;""),0)-IFERROR(VALUE($I9&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G9&amp;""),0)-IFERROR(VALUE($I9&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G9&amp;""),0)-IFERROR(VALUE($I9&amp;""),0))))))&amp;""),(IFERROR(VALUE($G9&amp;""),0)-IFERROR(VALUE($I9&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K9&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K9&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K9&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K9&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K9&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K9&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K9),IF($K9=0,"0",ROUND($K9,9-INT(LOG10(ABS($K9))))&amp;""),$K9&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K9&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K9&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K9&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K9&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K9&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M9" s="3">
+        <f>IF(AND($A9=""),"",MID(IF(AND(NOT(($A9="")),NOT(EXACT($L9,"Completa"))),"; "&amp;IF(ISNUMBER($L9),IF($L9=0,"0",ROUND($L9,9-INT(LOG10(ABS($L9))))&amp;""),$L9&amp;""),"")&amp;IF(AND(NOT(($A9="")),EXACT($L9,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N9" s="3">
+        <f>IF(OR(AND(NOT(($A9="")),NOT(EXACT($L9,"Completa")))),2,IF(OR(AND(NOT(($A9="")),EXACT($L9,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
       <c r="G10" s="3">
-        <f>IF($A10="","",($D10+($E10*$F10)))</f>
+        <f>IF(AND($A10=""),"",(IFERROR(VALUE($D10&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E10&amp;""),0)*IFERROR(VALUE($F10&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H10" s="3">
-        <f>IF($A10="","",COUNTIF(Asignacion!$B$4:$B$34,$A10))</f>
+        <f>IF(AND($A10=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A10)))))</f>
         <v/>
       </c>
       <c r="I10" s="3">
-        <f>IF($A10="","",SUMIF(Asignacion!$B$4:$B$34,$A10,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A10=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A10)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J10" s="3">
-        <f>IF($A10="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A10,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A10=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A10)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K10" s="3">
-        <f>IF($A10="","",COUNTIFS(Asignacion!$B$4:$B$34,$A10,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A10=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A10)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L10" s="3">
-        <f>IF($A10="","",IF(($H10=0),"Sin filas de carga",IF(($I10&lt;$G10),(IF(($G10-$I10)=1,"Falta","Faltan")&amp;" "&amp;($G10-$I10)&amp;" horas de carga"),IF(($K10&gt;0),(IF($K10=1,"Falta","Faltan")&amp;" "&amp;$K10&amp;" "&amp;IF($K10=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A10=""),"",IF(EXACT($H10,0),"Sin filas de carga",IF((IFERROR(VALUE($I10&amp;""),0)&lt;IFERROR(VALUE($G10&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G10&amp;""),0)-IFERROR(VALUE($I10&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G10&amp;""),0)-IFERROR(VALUE($I10&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G10&amp;""),0)-IFERROR(VALUE($I10&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G10&amp;""),0)-IFERROR(VALUE($I10&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G10&amp;""),0)-IFERROR(VALUE($I10&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G10&amp;""),0)-IFERROR(VALUE($I10&amp;""),0))),IF((IFERROR(VALUE($G10&amp;""),0)-IFERROR(VALUE($I10&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G10&amp;""),0)-IFERROR(VALUE($I10&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G10&amp;""),0)-IFERROR(VALUE($I10&amp;""),0))))))&amp;""),(IFERROR(VALUE($G10&amp;""),0)-IFERROR(VALUE($I10&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K10&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K10&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K10&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K10&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K10&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K10&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K10),IF($K10=0,"0",ROUND($K10,9-INT(LOG10(ABS($K10))))&amp;""),$K10&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K10&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K10&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K10&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K10&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K10&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M10" s="3">
+        <f>IF(AND($A10=""),"",MID(IF(AND(NOT(($A10="")),NOT(EXACT($L10,"Completa"))),"; "&amp;IF(ISNUMBER($L10),IF($L10=0,"0",ROUND($L10,9-INT(LOG10(ABS($L10))))&amp;""),$L10&amp;""),"")&amp;IF(AND(NOT(($A10="")),EXACT($L10,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N10" s="3">
+        <f>IF(OR(AND(NOT(($A10="")),NOT(EXACT($L10,"Completa")))),2,IF(OR(AND(NOT(($A10="")),EXACT($L10,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
       <c r="G11" s="3">
-        <f>IF($A11="","",($D11+($E11*$F11)))</f>
+        <f>IF(AND($A11=""),"",(IFERROR(VALUE($D11&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E11&amp;""),0)*IFERROR(VALUE($F11&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H11" s="3">
-        <f>IF($A11="","",COUNTIF(Asignacion!$B$4:$B$34,$A11))</f>
+        <f>IF(AND($A11=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A11)))))</f>
         <v/>
       </c>
       <c r="I11" s="3">
-        <f>IF($A11="","",SUMIF(Asignacion!$B$4:$B$34,$A11,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A11=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A11)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J11" s="3">
-        <f>IF($A11="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A11,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A11=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A11)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K11" s="3">
-        <f>IF($A11="","",COUNTIFS(Asignacion!$B$4:$B$34,$A11,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A11=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A11)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L11" s="3">
-        <f>IF($A11="","",IF(($H11=0),"Sin filas de carga",IF(($I11&lt;$G11),(IF(($G11-$I11)=1,"Falta","Faltan")&amp;" "&amp;($G11-$I11)&amp;" horas de carga"),IF(($K11&gt;0),(IF($K11=1,"Falta","Faltan")&amp;" "&amp;$K11&amp;" "&amp;IF($K11=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A11=""),"",IF(EXACT($H11,0),"Sin filas de carga",IF((IFERROR(VALUE($I11&amp;""),0)&lt;IFERROR(VALUE($G11&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G11&amp;""),0)-IFERROR(VALUE($I11&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G11&amp;""),0)-IFERROR(VALUE($I11&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G11&amp;""),0)-IFERROR(VALUE($I11&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G11&amp;""),0)-IFERROR(VALUE($I11&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G11&amp;""),0)-IFERROR(VALUE($I11&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G11&amp;""),0)-IFERROR(VALUE($I11&amp;""),0))),IF((IFERROR(VALUE($G11&amp;""),0)-IFERROR(VALUE($I11&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G11&amp;""),0)-IFERROR(VALUE($I11&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G11&amp;""),0)-IFERROR(VALUE($I11&amp;""),0))))))&amp;""),(IFERROR(VALUE($G11&amp;""),0)-IFERROR(VALUE($I11&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K11&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K11&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K11&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K11&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K11&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K11&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K11),IF($K11=0,"0",ROUND($K11,9-INT(LOG10(ABS($K11))))&amp;""),$K11&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K11&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K11&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K11&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K11&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K11&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M11" s="3">
+        <f>IF(AND($A11=""),"",MID(IF(AND(NOT(($A11="")),NOT(EXACT($L11,"Completa"))),"; "&amp;IF(ISNUMBER($L11),IF($L11=0,"0",ROUND($L11,9-INT(LOG10(ABS($L11))))&amp;""),$L11&amp;""),"")&amp;IF(AND(NOT(($A11="")),EXACT($L11,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N11" s="3">
+        <f>IF(OR(AND(NOT(($A11="")),NOT(EXACT($L11,"Completa")))),2,IF(OR(AND(NOT(($A11="")),EXACT($L11,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
       <c r="G12" s="3">
-        <f>IF($A12="","",($D12+($E12*$F12)))</f>
+        <f>IF(AND($A12=""),"",(IFERROR(VALUE($D12&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E12&amp;""),0)*IFERROR(VALUE($F12&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H12" s="3">
-        <f>IF($A12="","",COUNTIF(Asignacion!$B$4:$B$34,$A12))</f>
+        <f>IF(AND($A12=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A12)))))</f>
         <v/>
       </c>
       <c r="I12" s="3">
-        <f>IF($A12="","",SUMIF(Asignacion!$B$4:$B$34,$A12,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A12=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A12)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J12" s="3">
-        <f>IF($A12="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A12,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A12=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A12)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K12" s="3">
-        <f>IF($A12="","",COUNTIFS(Asignacion!$B$4:$B$34,$A12,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A12=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A12)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L12" s="3">
-        <f>IF($A12="","",IF(($H12=0),"Sin filas de carga",IF(($I12&lt;$G12),(IF(($G12-$I12)=1,"Falta","Faltan")&amp;" "&amp;($G12-$I12)&amp;" horas de carga"),IF(($K12&gt;0),(IF($K12=1,"Falta","Faltan")&amp;" "&amp;$K12&amp;" "&amp;IF($K12=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A12=""),"",IF(EXACT($H12,0),"Sin filas de carga",IF((IFERROR(VALUE($I12&amp;""),0)&lt;IFERROR(VALUE($G12&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G12&amp;""),0)-IFERROR(VALUE($I12&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G12&amp;""),0)-IFERROR(VALUE($I12&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G12&amp;""),0)-IFERROR(VALUE($I12&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G12&amp;""),0)-IFERROR(VALUE($I12&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G12&amp;""),0)-IFERROR(VALUE($I12&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G12&amp;""),0)-IFERROR(VALUE($I12&amp;""),0))),IF((IFERROR(VALUE($G12&amp;""),0)-IFERROR(VALUE($I12&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G12&amp;""),0)-IFERROR(VALUE($I12&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G12&amp;""),0)-IFERROR(VALUE($I12&amp;""),0))))))&amp;""),(IFERROR(VALUE($G12&amp;""),0)-IFERROR(VALUE($I12&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K12&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K12&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K12&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K12&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K12&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K12&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K12),IF($K12=0,"0",ROUND($K12,9-INT(LOG10(ABS($K12))))&amp;""),$K12&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K12&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K12&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K12&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K12&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K12&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M12" s="3">
+        <f>IF(AND($A12=""),"",MID(IF(AND(NOT(($A12="")),NOT(EXACT($L12,"Completa"))),"; "&amp;IF(ISNUMBER($L12),IF($L12=0,"0",ROUND($L12,9-INT(LOG10(ABS($L12))))&amp;""),$L12&amp;""),"")&amp;IF(AND(NOT(($A12="")),EXACT($L12,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N12" s="3">
+        <f>IF(OR(AND(NOT(($A12="")),NOT(EXACT($L12,"Completa")))),2,IF(OR(AND(NOT(($A12="")),EXACT($L12,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n"/>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
       <c r="G13" s="3">
-        <f>IF($A13="","",($D13+($E13*$F13)))</f>
+        <f>IF(AND($A13=""),"",(IFERROR(VALUE($D13&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E13&amp;""),0)*IFERROR(VALUE($F13&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H13" s="3">
-        <f>IF($A13="","",COUNTIF(Asignacion!$B$4:$B$34,$A13))</f>
+        <f>IF(AND($A13=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A13)))))</f>
         <v/>
       </c>
       <c r="I13" s="3">
-        <f>IF($A13="","",SUMIF(Asignacion!$B$4:$B$34,$A13,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A13=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A13)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J13" s="3">
-        <f>IF($A13="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A13,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A13=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A13)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K13" s="3">
-        <f>IF($A13="","",COUNTIFS(Asignacion!$B$4:$B$34,$A13,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A13=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A13)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L13" s="3">
-        <f>IF($A13="","",IF(($H13=0),"Sin filas de carga",IF(($I13&lt;$G13),(IF(($G13-$I13)=1,"Falta","Faltan")&amp;" "&amp;($G13-$I13)&amp;" horas de carga"),IF(($K13&gt;0),(IF($K13=1,"Falta","Faltan")&amp;" "&amp;$K13&amp;" "&amp;IF($K13=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A13=""),"",IF(EXACT($H13,0),"Sin filas de carga",IF((IFERROR(VALUE($I13&amp;""),0)&lt;IFERROR(VALUE($G13&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G13&amp;""),0)-IFERROR(VALUE($I13&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G13&amp;""),0)-IFERROR(VALUE($I13&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G13&amp;""),0)-IFERROR(VALUE($I13&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G13&amp;""),0)-IFERROR(VALUE($I13&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G13&amp;""),0)-IFERROR(VALUE($I13&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G13&amp;""),0)-IFERROR(VALUE($I13&amp;""),0))),IF((IFERROR(VALUE($G13&amp;""),0)-IFERROR(VALUE($I13&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G13&amp;""),0)-IFERROR(VALUE($I13&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G13&amp;""),0)-IFERROR(VALUE($I13&amp;""),0))))))&amp;""),(IFERROR(VALUE($G13&amp;""),0)-IFERROR(VALUE($I13&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K13&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K13&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K13&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K13&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K13&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K13&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K13),IF($K13=0,"0",ROUND($K13,9-INT(LOG10(ABS($K13))))&amp;""),$K13&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K13&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K13&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K13&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K13&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K13&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M13" s="3">
+        <f>IF(AND($A13=""),"",MID(IF(AND(NOT(($A13="")),NOT(EXACT($L13,"Completa"))),"; "&amp;IF(ISNUMBER($L13),IF($L13=0,"0",ROUND($L13,9-INT(LOG10(ABS($L13))))&amp;""),$L13&amp;""),"")&amp;IF(AND(NOT(($A13="")),EXACT($L13,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N13" s="3">
+        <f>IF(OR(AND(NOT(($A13="")),NOT(EXACT($L13,"Completa")))),2,IF(OR(AND(NOT(($A13="")),EXACT($L13,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
       <c r="G14" s="3">
-        <f>IF($A14="","",($D14+($E14*$F14)))</f>
+        <f>IF(AND($A14=""),"",(IFERROR(VALUE($D14&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E14&amp;""),0)*IFERROR(VALUE($F14&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H14" s="3">
-        <f>IF($A14="","",COUNTIF(Asignacion!$B$4:$B$34,$A14))</f>
+        <f>IF(AND($A14=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A14)))))</f>
         <v/>
       </c>
       <c r="I14" s="3">
-        <f>IF($A14="","",SUMIF(Asignacion!$B$4:$B$34,$A14,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A14=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A14)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J14" s="3">
-        <f>IF($A14="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A14,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A14=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A14)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K14" s="3">
-        <f>IF($A14="","",COUNTIFS(Asignacion!$B$4:$B$34,$A14,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A14=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A14)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L14" s="3">
-        <f>IF($A14="","",IF(($H14=0),"Sin filas de carga",IF(($I14&lt;$G14),(IF(($G14-$I14)=1,"Falta","Faltan")&amp;" "&amp;($G14-$I14)&amp;" horas de carga"),IF(($K14&gt;0),(IF($K14=1,"Falta","Faltan")&amp;" "&amp;$K14&amp;" "&amp;IF($K14=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A14=""),"",IF(EXACT($H14,0),"Sin filas de carga",IF((IFERROR(VALUE($I14&amp;""),0)&lt;IFERROR(VALUE($G14&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G14&amp;""),0)-IFERROR(VALUE($I14&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G14&amp;""),0)-IFERROR(VALUE($I14&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G14&amp;""),0)-IFERROR(VALUE($I14&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G14&amp;""),0)-IFERROR(VALUE($I14&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G14&amp;""),0)-IFERROR(VALUE($I14&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G14&amp;""),0)-IFERROR(VALUE($I14&amp;""),0))),IF((IFERROR(VALUE($G14&amp;""),0)-IFERROR(VALUE($I14&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G14&amp;""),0)-IFERROR(VALUE($I14&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G14&amp;""),0)-IFERROR(VALUE($I14&amp;""),0))))))&amp;""),(IFERROR(VALUE($G14&amp;""),0)-IFERROR(VALUE($I14&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K14&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K14&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K14&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K14&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K14&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K14&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K14),IF($K14=0,"0",ROUND($K14,9-INT(LOG10(ABS($K14))))&amp;""),$K14&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K14&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K14&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K14&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K14&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K14&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M14" s="3">
+        <f>IF(AND($A14=""),"",MID(IF(AND(NOT(($A14="")),NOT(EXACT($L14,"Completa"))),"; "&amp;IF(ISNUMBER($L14),IF($L14=0,"0",ROUND($L14,9-INT(LOG10(ABS($L14))))&amp;""),$L14&amp;""),"")&amp;IF(AND(NOT(($A14="")),EXACT($L14,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N14" s="3">
+        <f>IF(OR(AND(NOT(($A14="")),NOT(EXACT($L14,"Completa")))),2,IF(OR(AND(NOT(($A14="")),EXACT($L14,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
       <c r="G15" s="3">
-        <f>IF($A15="","",($D15+($E15*$F15)))</f>
+        <f>IF(AND($A15=""),"",(IFERROR(VALUE($D15&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E15&amp;""),0)*IFERROR(VALUE($F15&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H15" s="3">
-        <f>IF($A15="","",COUNTIF(Asignacion!$B$4:$B$34,$A15))</f>
+        <f>IF(AND($A15=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A15)))))</f>
         <v/>
       </c>
       <c r="I15" s="3">
-        <f>IF($A15="","",SUMIF(Asignacion!$B$4:$B$34,$A15,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A15=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A15)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J15" s="3">
-        <f>IF($A15="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A15,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A15=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A15)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K15" s="3">
-        <f>IF($A15="","",COUNTIFS(Asignacion!$B$4:$B$34,$A15,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A15=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A15)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L15" s="3">
-        <f>IF($A15="","",IF(($H15=0),"Sin filas de carga",IF(($I15&lt;$G15),(IF(($G15-$I15)=1,"Falta","Faltan")&amp;" "&amp;($G15-$I15)&amp;" horas de carga"),IF(($K15&gt;0),(IF($K15=1,"Falta","Faltan")&amp;" "&amp;$K15&amp;" "&amp;IF($K15=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A15=""),"",IF(EXACT($H15,0),"Sin filas de carga",IF((IFERROR(VALUE($I15&amp;""),0)&lt;IFERROR(VALUE($G15&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G15&amp;""),0)-IFERROR(VALUE($I15&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G15&amp;""),0)-IFERROR(VALUE($I15&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G15&amp;""),0)-IFERROR(VALUE($I15&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G15&amp;""),0)-IFERROR(VALUE($I15&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G15&amp;""),0)-IFERROR(VALUE($I15&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G15&amp;""),0)-IFERROR(VALUE($I15&amp;""),0))),IF((IFERROR(VALUE($G15&amp;""),0)-IFERROR(VALUE($I15&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G15&amp;""),0)-IFERROR(VALUE($I15&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G15&amp;""),0)-IFERROR(VALUE($I15&amp;""),0))))))&amp;""),(IFERROR(VALUE($G15&amp;""),0)-IFERROR(VALUE($I15&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K15&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K15&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K15&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K15&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K15&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K15&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K15),IF($K15=0,"0",ROUND($K15,9-INT(LOG10(ABS($K15))))&amp;""),$K15&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K15&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K15&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K15&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K15&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K15&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M15" s="3">
+        <f>IF(AND($A15=""),"",MID(IF(AND(NOT(($A15="")),NOT(EXACT($L15,"Completa"))),"; "&amp;IF(ISNUMBER($L15),IF($L15=0,"0",ROUND($L15,9-INT(LOG10(ABS($L15))))&amp;""),$L15&amp;""),"")&amp;IF(AND(NOT(($A15="")),EXACT($L15,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N15" s="3">
+        <f>IF(OR(AND(NOT(($A15="")),NOT(EXACT($L15,"Completa")))),2,IF(OR(AND(NOT(($A15="")),EXACT($L15,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n"/>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
       <c r="G16" s="3">
-        <f>IF($A16="","",($D16+($E16*$F16)))</f>
+        <f>IF(AND($A16=""),"",(IFERROR(VALUE($D16&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E16&amp;""),0)*IFERROR(VALUE($F16&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H16" s="3">
-        <f>IF($A16="","",COUNTIF(Asignacion!$B$4:$B$34,$A16))</f>
+        <f>IF(AND($A16=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A16)))))</f>
         <v/>
       </c>
       <c r="I16" s="3">
-        <f>IF($A16="","",SUMIF(Asignacion!$B$4:$B$34,$A16,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A16=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A16)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J16" s="3">
-        <f>IF($A16="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A16,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A16=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A16)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K16" s="3">
-        <f>IF($A16="","",COUNTIFS(Asignacion!$B$4:$B$34,$A16,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A16=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A16)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L16" s="3">
-        <f>IF($A16="","",IF(($H16=0),"Sin filas de carga",IF(($I16&lt;$G16),(IF(($G16-$I16)=1,"Falta","Faltan")&amp;" "&amp;($G16-$I16)&amp;" horas de carga"),IF(($K16&gt;0),(IF($K16=1,"Falta","Faltan")&amp;" "&amp;$K16&amp;" "&amp;IF($K16=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A16=""),"",IF(EXACT($H16,0),"Sin filas de carga",IF((IFERROR(VALUE($I16&amp;""),0)&lt;IFERROR(VALUE($G16&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G16&amp;""),0)-IFERROR(VALUE($I16&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G16&amp;""),0)-IFERROR(VALUE($I16&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G16&amp;""),0)-IFERROR(VALUE($I16&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G16&amp;""),0)-IFERROR(VALUE($I16&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G16&amp;""),0)-IFERROR(VALUE($I16&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G16&amp;""),0)-IFERROR(VALUE($I16&amp;""),0))),IF((IFERROR(VALUE($G16&amp;""),0)-IFERROR(VALUE($I16&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G16&amp;""),0)-IFERROR(VALUE($I16&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G16&amp;""),0)-IFERROR(VALUE($I16&amp;""),0))))))&amp;""),(IFERROR(VALUE($G16&amp;""),0)-IFERROR(VALUE($I16&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K16&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K16&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K16&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K16&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K16&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K16&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K16),IF($K16=0,"0",ROUND($K16,9-INT(LOG10(ABS($K16))))&amp;""),$K16&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K16&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K16&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K16&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K16&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K16&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M16" s="3">
+        <f>IF(AND($A16=""),"",MID(IF(AND(NOT(($A16="")),NOT(EXACT($L16,"Completa"))),"; "&amp;IF(ISNUMBER($L16),IF($L16=0,"0",ROUND($L16,9-INT(LOG10(ABS($L16))))&amp;""),$L16&amp;""),"")&amp;IF(AND(NOT(($A16="")),EXACT($L16,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N16" s="3">
+        <f>IF(OR(AND(NOT(($A16="")),NOT(EXACT($L16,"Completa")))),2,IF(OR(AND(NOT(($A16="")),EXACT($L16,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
       <c r="G17" s="3">
-        <f>IF($A17="","",($D17+($E17*$F17)))</f>
+        <f>IF(AND($A17=""),"",(IFERROR(VALUE($D17&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E17&amp;""),0)*IFERROR(VALUE($F17&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H17" s="3">
-        <f>IF($A17="","",COUNTIF(Asignacion!$B$4:$B$34,$A17))</f>
+        <f>IF(AND($A17=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A17)))))</f>
         <v/>
       </c>
       <c r="I17" s="3">
-        <f>IF($A17="","",SUMIF(Asignacion!$B$4:$B$34,$A17,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A17=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A17)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J17" s="3">
-        <f>IF($A17="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A17,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A17=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A17)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K17" s="3">
-        <f>IF($A17="","",COUNTIFS(Asignacion!$B$4:$B$34,$A17,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A17=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A17)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L17" s="3">
-        <f>IF($A17="","",IF(($H17=0),"Sin filas de carga",IF(($I17&lt;$G17),(IF(($G17-$I17)=1,"Falta","Faltan")&amp;" "&amp;($G17-$I17)&amp;" horas de carga"),IF(($K17&gt;0),(IF($K17=1,"Falta","Faltan")&amp;" "&amp;$K17&amp;" "&amp;IF($K17=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A17=""),"",IF(EXACT($H17,0),"Sin filas de carga",IF((IFERROR(VALUE($I17&amp;""),0)&lt;IFERROR(VALUE($G17&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G17&amp;""),0)-IFERROR(VALUE($I17&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G17&amp;""),0)-IFERROR(VALUE($I17&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G17&amp;""),0)-IFERROR(VALUE($I17&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G17&amp;""),0)-IFERROR(VALUE($I17&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G17&amp;""),0)-IFERROR(VALUE($I17&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G17&amp;""),0)-IFERROR(VALUE($I17&amp;""),0))),IF((IFERROR(VALUE($G17&amp;""),0)-IFERROR(VALUE($I17&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G17&amp;""),0)-IFERROR(VALUE($I17&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G17&amp;""),0)-IFERROR(VALUE($I17&amp;""),0))))))&amp;""),(IFERROR(VALUE($G17&amp;""),0)-IFERROR(VALUE($I17&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K17&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K17&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K17&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K17&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K17&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K17&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K17),IF($K17=0,"0",ROUND($K17,9-INT(LOG10(ABS($K17))))&amp;""),$K17&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K17&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K17&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K17&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K17&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K17&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M17" s="3">
+        <f>IF(AND($A17=""),"",MID(IF(AND(NOT(($A17="")),NOT(EXACT($L17,"Completa"))),"; "&amp;IF(ISNUMBER($L17),IF($L17=0,"0",ROUND($L17,9-INT(LOG10(ABS($L17))))&amp;""),$L17&amp;""),"")&amp;IF(AND(NOT(($A17="")),EXACT($L17,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N17" s="3">
+        <f>IF(OR(AND(NOT(($A17="")),NOT(EXACT($L17,"Completa")))),2,IF(OR(AND(NOT(($A17="")),EXACT($L17,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n"/>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
       <c r="G18" s="3">
-        <f>IF($A18="","",($D18+($E18*$F18)))</f>
+        <f>IF(AND($A18=""),"",(IFERROR(VALUE($D18&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E18&amp;""),0)*IFERROR(VALUE($F18&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H18" s="3">
-        <f>IF($A18="","",COUNTIF(Asignacion!$B$4:$B$34,$A18))</f>
+        <f>IF(AND($A18=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A18)))))</f>
         <v/>
       </c>
       <c r="I18" s="3">
-        <f>IF($A18="","",SUMIF(Asignacion!$B$4:$B$34,$A18,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A18=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A18)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J18" s="3">
-        <f>IF($A18="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A18,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A18=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A18)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K18" s="3">
-        <f>IF($A18="","",COUNTIFS(Asignacion!$B$4:$B$34,$A18,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A18=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A18)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L18" s="3">
-        <f>IF($A18="","",IF(($H18=0),"Sin filas de carga",IF(($I18&lt;$G18),(IF(($G18-$I18)=1,"Falta","Faltan")&amp;" "&amp;($G18-$I18)&amp;" horas de carga"),IF(($K18&gt;0),(IF($K18=1,"Falta","Faltan")&amp;" "&amp;$K18&amp;" "&amp;IF($K18=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A18=""),"",IF(EXACT($H18,0),"Sin filas de carga",IF((IFERROR(VALUE($I18&amp;""),0)&lt;IFERROR(VALUE($G18&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G18&amp;""),0)-IFERROR(VALUE($I18&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G18&amp;""),0)-IFERROR(VALUE($I18&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G18&amp;""),0)-IFERROR(VALUE($I18&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G18&amp;""),0)-IFERROR(VALUE($I18&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G18&amp;""),0)-IFERROR(VALUE($I18&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G18&amp;""),0)-IFERROR(VALUE($I18&amp;""),0))),IF((IFERROR(VALUE($G18&amp;""),0)-IFERROR(VALUE($I18&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G18&amp;""),0)-IFERROR(VALUE($I18&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G18&amp;""),0)-IFERROR(VALUE($I18&amp;""),0))))))&amp;""),(IFERROR(VALUE($G18&amp;""),0)-IFERROR(VALUE($I18&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K18&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K18&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K18&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K18&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K18&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K18&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K18),IF($K18=0,"0",ROUND($K18,9-INT(LOG10(ABS($K18))))&amp;""),$K18&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K18&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K18&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K18&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K18&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K18&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M18" s="3">
+        <f>IF(AND($A18=""),"",MID(IF(AND(NOT(($A18="")),NOT(EXACT($L18,"Completa"))),"; "&amp;IF(ISNUMBER($L18),IF($L18=0,"0",ROUND($L18,9-INT(LOG10(ABS($L18))))&amp;""),$L18&amp;""),"")&amp;IF(AND(NOT(($A18="")),EXACT($L18,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N18" s="3">
+        <f>IF(OR(AND(NOT(($A18="")),NOT(EXACT($L18,"Completa")))),2,IF(OR(AND(NOT(($A18="")),EXACT($L18,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
       <c r="G19" s="3">
-        <f>IF($A19="","",($D19+($E19*$F19)))</f>
+        <f>IF(AND($A19=""),"",(IFERROR(VALUE($D19&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E19&amp;""),0)*IFERROR(VALUE($F19&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H19" s="3">
-        <f>IF($A19="","",COUNTIF(Asignacion!$B$4:$B$34,$A19))</f>
+        <f>IF(AND($A19=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A19)))))</f>
         <v/>
       </c>
       <c r="I19" s="3">
-        <f>IF($A19="","",SUMIF(Asignacion!$B$4:$B$34,$A19,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A19=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A19)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J19" s="3">
-        <f>IF($A19="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A19,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A19=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A19)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K19" s="3">
-        <f>IF($A19="","",COUNTIFS(Asignacion!$B$4:$B$34,$A19,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A19=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A19)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L19" s="3">
-        <f>IF($A19="","",IF(($H19=0),"Sin filas de carga",IF(($I19&lt;$G19),(IF(($G19-$I19)=1,"Falta","Faltan")&amp;" "&amp;($G19-$I19)&amp;" horas de carga"),IF(($K19&gt;0),(IF($K19=1,"Falta","Faltan")&amp;" "&amp;$K19&amp;" "&amp;IF($K19=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A19=""),"",IF(EXACT($H19,0),"Sin filas de carga",IF((IFERROR(VALUE($I19&amp;""),0)&lt;IFERROR(VALUE($G19&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G19&amp;""),0)-IFERROR(VALUE($I19&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G19&amp;""),0)-IFERROR(VALUE($I19&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G19&amp;""),0)-IFERROR(VALUE($I19&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G19&amp;""),0)-IFERROR(VALUE($I19&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G19&amp;""),0)-IFERROR(VALUE($I19&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G19&amp;""),0)-IFERROR(VALUE($I19&amp;""),0))),IF((IFERROR(VALUE($G19&amp;""),0)-IFERROR(VALUE($I19&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G19&amp;""),0)-IFERROR(VALUE($I19&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G19&amp;""),0)-IFERROR(VALUE($I19&amp;""),0))))))&amp;""),(IFERROR(VALUE($G19&amp;""),0)-IFERROR(VALUE($I19&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K19&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K19&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K19&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K19&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K19&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K19&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K19),IF($K19=0,"0",ROUND($K19,9-INT(LOG10(ABS($K19))))&amp;""),$K19&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K19&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K19&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K19&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K19&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K19&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M19" s="3">
+        <f>IF(AND($A19=""),"",MID(IF(AND(NOT(($A19="")),NOT(EXACT($L19,"Completa"))),"; "&amp;IF(ISNUMBER($L19),IF($L19=0,"0",ROUND($L19,9-INT(LOG10(ABS($L19))))&amp;""),$L19&amp;""),"")&amp;IF(AND(NOT(($A19="")),EXACT($L19,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N19" s="3">
+        <f>IF(OR(AND(NOT(($A19="")),NOT(EXACT($L19,"Completa")))),2,IF(OR(AND(NOT(($A19="")),EXACT($L19,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n"/>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
       <c r="G20" s="3">
-        <f>IF($A20="","",($D20+($E20*$F20)))</f>
+        <f>IF(AND($A20=""),"",(IFERROR(VALUE($D20&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E20&amp;""),0)*IFERROR(VALUE($F20&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H20" s="3">
-        <f>IF($A20="","",COUNTIF(Asignacion!$B$4:$B$34,$A20))</f>
+        <f>IF(AND($A20=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A20)))))</f>
         <v/>
       </c>
       <c r="I20" s="3">
-        <f>IF($A20="","",SUMIF(Asignacion!$B$4:$B$34,$A20,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A20=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A20)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J20" s="3">
-        <f>IF($A20="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A20,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A20=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A20)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K20" s="3">
-        <f>IF($A20="","",COUNTIFS(Asignacion!$B$4:$B$34,$A20,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A20=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A20)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L20" s="3">
-        <f>IF($A20="","",IF(($H20=0),"Sin filas de carga",IF(($I20&lt;$G20),(IF(($G20-$I20)=1,"Falta","Faltan")&amp;" "&amp;($G20-$I20)&amp;" horas de carga"),IF(($K20&gt;0),(IF($K20=1,"Falta","Faltan")&amp;" "&amp;$K20&amp;" "&amp;IF($K20=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A20=""),"",IF(EXACT($H20,0),"Sin filas de carga",IF((IFERROR(VALUE($I20&amp;""),0)&lt;IFERROR(VALUE($G20&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G20&amp;""),0)-IFERROR(VALUE($I20&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G20&amp;""),0)-IFERROR(VALUE($I20&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G20&amp;""),0)-IFERROR(VALUE($I20&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G20&amp;""),0)-IFERROR(VALUE($I20&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G20&amp;""),0)-IFERROR(VALUE($I20&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G20&amp;""),0)-IFERROR(VALUE($I20&amp;""),0))),IF((IFERROR(VALUE($G20&amp;""),0)-IFERROR(VALUE($I20&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G20&amp;""),0)-IFERROR(VALUE($I20&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G20&amp;""),0)-IFERROR(VALUE($I20&amp;""),0))))))&amp;""),(IFERROR(VALUE($G20&amp;""),0)-IFERROR(VALUE($I20&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K20&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K20&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K20&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K20&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K20&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K20&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K20),IF($K20=0,"0",ROUND($K20,9-INT(LOG10(ABS($K20))))&amp;""),$K20&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K20&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K20&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K20&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K20&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K20&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M20" s="3">
+        <f>IF(AND($A20=""),"",MID(IF(AND(NOT(($A20="")),NOT(EXACT($L20,"Completa"))),"; "&amp;IF(ISNUMBER($L20),IF($L20=0,"0",ROUND($L20,9-INT(LOG10(ABS($L20))))&amp;""),$L20&amp;""),"")&amp;IF(AND(NOT(($A20="")),EXACT($L20,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N20" s="3">
+        <f>IF(OR(AND(NOT(($A20="")),NOT(EXACT($L20,"Completa")))),2,IF(OR(AND(NOT(($A20="")),EXACT($L20,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n"/>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
       <c r="G21" s="3">
-        <f>IF($A21="","",($D21+($E21*$F21)))</f>
+        <f>IF(AND($A21=""),"",(IFERROR(VALUE($D21&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E21&amp;""),0)*IFERROR(VALUE($F21&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H21" s="3">
-        <f>IF($A21="","",COUNTIF(Asignacion!$B$4:$B$34,$A21))</f>
+        <f>IF(AND($A21=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A21)))))</f>
         <v/>
       </c>
       <c r="I21" s="3">
-        <f>IF($A21="","",SUMIF(Asignacion!$B$4:$B$34,$A21,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A21=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A21)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J21" s="3">
-        <f>IF($A21="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A21,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A21=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A21)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K21" s="3">
-        <f>IF($A21="","",COUNTIFS(Asignacion!$B$4:$B$34,$A21,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A21=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A21)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L21" s="3">
-        <f>IF($A21="","",IF(($H21=0),"Sin filas de carga",IF(($I21&lt;$G21),(IF(($G21-$I21)=1,"Falta","Faltan")&amp;" "&amp;($G21-$I21)&amp;" horas de carga"),IF(($K21&gt;0),(IF($K21=1,"Falta","Faltan")&amp;" "&amp;$K21&amp;" "&amp;IF($K21=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A21=""),"",IF(EXACT($H21,0),"Sin filas de carga",IF((IFERROR(VALUE($I21&amp;""),0)&lt;IFERROR(VALUE($G21&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G21&amp;""),0)-IFERROR(VALUE($I21&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G21&amp;""),0)-IFERROR(VALUE($I21&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G21&amp;""),0)-IFERROR(VALUE($I21&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G21&amp;""),0)-IFERROR(VALUE($I21&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G21&amp;""),0)-IFERROR(VALUE($I21&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G21&amp;""),0)-IFERROR(VALUE($I21&amp;""),0))),IF((IFERROR(VALUE($G21&amp;""),0)-IFERROR(VALUE($I21&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G21&amp;""),0)-IFERROR(VALUE($I21&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G21&amp;""),0)-IFERROR(VALUE($I21&amp;""),0))))))&amp;""),(IFERROR(VALUE($G21&amp;""),0)-IFERROR(VALUE($I21&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K21&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K21&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K21&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K21&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K21&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K21&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K21),IF($K21=0,"0",ROUND($K21,9-INT(LOG10(ABS($K21))))&amp;""),$K21&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K21&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K21&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K21&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K21&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K21&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M21" s="3">
+        <f>IF(AND($A21=""),"",MID(IF(AND(NOT(($A21="")),NOT(EXACT($L21,"Completa"))),"; "&amp;IF(ISNUMBER($L21),IF($L21=0,"0",ROUND($L21,9-INT(LOG10(ABS($L21))))&amp;""),$L21&amp;""),"")&amp;IF(AND(NOT(($A21="")),EXACT($L21,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N21" s="3">
+        <f>IF(OR(AND(NOT(($A21="")),NOT(EXACT($L21,"Completa")))),2,IF(OR(AND(NOT(($A21="")),EXACT($L21,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n"/>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
       <c r="G22" s="3">
-        <f>IF($A22="","",($D22+($E22*$F22)))</f>
+        <f>IF(AND($A22=""),"",(IFERROR(VALUE($D22&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E22&amp;""),0)*IFERROR(VALUE($F22&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H22" s="3">
-        <f>IF($A22="","",COUNTIF(Asignacion!$B$4:$B$34,$A22))</f>
+        <f>IF(AND($A22=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A22)))))</f>
         <v/>
       </c>
       <c r="I22" s="3">
-        <f>IF($A22="","",SUMIF(Asignacion!$B$4:$B$34,$A22,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A22=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A22)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J22" s="3">
-        <f>IF($A22="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A22,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A22=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A22)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K22" s="3">
-        <f>IF($A22="","",COUNTIFS(Asignacion!$B$4:$B$34,$A22,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A22=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A22)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L22" s="3">
-        <f>IF($A22="","",IF(($H22=0),"Sin filas de carga",IF(($I22&lt;$G22),(IF(($G22-$I22)=1,"Falta","Faltan")&amp;" "&amp;($G22-$I22)&amp;" horas de carga"),IF(($K22&gt;0),(IF($K22=1,"Falta","Faltan")&amp;" "&amp;$K22&amp;" "&amp;IF($K22=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A22=""),"",IF(EXACT($H22,0),"Sin filas de carga",IF((IFERROR(VALUE($I22&amp;""),0)&lt;IFERROR(VALUE($G22&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G22&amp;""),0)-IFERROR(VALUE($I22&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G22&amp;""),0)-IFERROR(VALUE($I22&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G22&amp;""),0)-IFERROR(VALUE($I22&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G22&amp;""),0)-IFERROR(VALUE($I22&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G22&amp;""),0)-IFERROR(VALUE($I22&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G22&amp;""),0)-IFERROR(VALUE($I22&amp;""),0))),IF((IFERROR(VALUE($G22&amp;""),0)-IFERROR(VALUE($I22&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G22&amp;""),0)-IFERROR(VALUE($I22&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G22&amp;""),0)-IFERROR(VALUE($I22&amp;""),0))))))&amp;""),(IFERROR(VALUE($G22&amp;""),0)-IFERROR(VALUE($I22&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K22&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K22&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K22&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K22&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K22&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K22&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K22),IF($K22=0,"0",ROUND($K22,9-INT(LOG10(ABS($K22))))&amp;""),$K22&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K22&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K22&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K22&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K22&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K22&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M22" s="3">
+        <f>IF(AND($A22=""),"",MID(IF(AND(NOT(($A22="")),NOT(EXACT($L22,"Completa"))),"; "&amp;IF(ISNUMBER($L22),IF($L22=0,"0",ROUND($L22,9-INT(LOG10(ABS($L22))))&amp;""),$L22&amp;""),"")&amp;IF(AND(NOT(($A22="")),EXACT($L22,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N22" s="3">
+        <f>IF(OR(AND(NOT(($A22="")),NOT(EXACT($L22,"Completa")))),2,IF(OR(AND(NOT(($A22="")),EXACT($L22,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n"/>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
       <c r="G23" s="3">
-        <f>IF($A23="","",($D23+($E23*$F23)))</f>
+        <f>IF(AND($A23=""),"",(IFERROR(VALUE($D23&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E23&amp;""),0)*IFERROR(VALUE($F23&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H23" s="3">
-        <f>IF($A23="","",COUNTIF(Asignacion!$B$4:$B$34,$A23))</f>
+        <f>IF(AND($A23=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A23)))))</f>
         <v/>
       </c>
       <c r="I23" s="3">
-        <f>IF($A23="","",SUMIF(Asignacion!$B$4:$B$34,$A23,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A23=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A23)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J23" s="3">
-        <f>IF($A23="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A23,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A23=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A23)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K23" s="3">
-        <f>IF($A23="","",COUNTIFS(Asignacion!$B$4:$B$34,$A23,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A23=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A23)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L23" s="3">
-        <f>IF($A23="","",IF(($H23=0),"Sin filas de carga",IF(($I23&lt;$G23),(IF(($G23-$I23)=1,"Falta","Faltan")&amp;" "&amp;($G23-$I23)&amp;" horas de carga"),IF(($K23&gt;0),(IF($K23=1,"Falta","Faltan")&amp;" "&amp;$K23&amp;" "&amp;IF($K23=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A23=""),"",IF(EXACT($H23,0),"Sin filas de carga",IF((IFERROR(VALUE($I23&amp;""),0)&lt;IFERROR(VALUE($G23&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G23&amp;""),0)-IFERROR(VALUE($I23&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G23&amp;""),0)-IFERROR(VALUE($I23&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G23&amp;""),0)-IFERROR(VALUE($I23&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G23&amp;""),0)-IFERROR(VALUE($I23&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G23&amp;""),0)-IFERROR(VALUE($I23&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G23&amp;""),0)-IFERROR(VALUE($I23&amp;""),0))),IF((IFERROR(VALUE($G23&amp;""),0)-IFERROR(VALUE($I23&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G23&amp;""),0)-IFERROR(VALUE($I23&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G23&amp;""),0)-IFERROR(VALUE($I23&amp;""),0))))))&amp;""),(IFERROR(VALUE($G23&amp;""),0)-IFERROR(VALUE($I23&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K23&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K23&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K23&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K23&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K23&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K23&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K23),IF($K23=0,"0",ROUND($K23,9-INT(LOG10(ABS($K23))))&amp;""),$K23&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K23&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K23&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K23&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K23&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K23&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M23" s="3">
+        <f>IF(AND($A23=""),"",MID(IF(AND(NOT(($A23="")),NOT(EXACT($L23,"Completa"))),"; "&amp;IF(ISNUMBER($L23),IF($L23=0,"0",ROUND($L23,9-INT(LOG10(ABS($L23))))&amp;""),$L23&amp;""),"")&amp;IF(AND(NOT(($A23="")),EXACT($L23,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N23" s="3">
+        <f>IF(OR(AND(NOT(($A23="")),NOT(EXACT($L23,"Completa")))),2,IF(OR(AND(NOT(($A23="")),EXACT($L23,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n"/>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
       <c r="G24" s="3">
-        <f>IF($A24="","",($D24+($E24*$F24)))</f>
+        <f>IF(AND($A24=""),"",(IFERROR(VALUE($D24&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E24&amp;""),0)*IFERROR(VALUE($F24&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H24" s="3">
-        <f>IF($A24="","",COUNTIF(Asignacion!$B$4:$B$34,$A24))</f>
+        <f>IF(AND($A24=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A24)))))</f>
         <v/>
       </c>
       <c r="I24" s="3">
-        <f>IF($A24="","",SUMIF(Asignacion!$B$4:$B$34,$A24,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A24=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A24)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J24" s="3">
-        <f>IF($A24="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A24,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A24=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A24)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K24" s="3">
-        <f>IF($A24="","",COUNTIFS(Asignacion!$B$4:$B$34,$A24,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A24=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A24)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L24" s="3">
-        <f>IF($A24="","",IF(($H24=0),"Sin filas de carga",IF(($I24&lt;$G24),(IF(($G24-$I24)=1,"Falta","Faltan")&amp;" "&amp;($G24-$I24)&amp;" horas de carga"),IF(($K24&gt;0),(IF($K24=1,"Falta","Faltan")&amp;" "&amp;$K24&amp;" "&amp;IF($K24=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A24=""),"",IF(EXACT($H24,0),"Sin filas de carga",IF((IFERROR(VALUE($I24&amp;""),0)&lt;IFERROR(VALUE($G24&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G24&amp;""),0)-IFERROR(VALUE($I24&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G24&amp;""),0)-IFERROR(VALUE($I24&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G24&amp;""),0)-IFERROR(VALUE($I24&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G24&amp;""),0)-IFERROR(VALUE($I24&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G24&amp;""),0)-IFERROR(VALUE($I24&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G24&amp;""),0)-IFERROR(VALUE($I24&amp;""),0))),IF((IFERROR(VALUE($G24&amp;""),0)-IFERROR(VALUE($I24&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G24&amp;""),0)-IFERROR(VALUE($I24&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G24&amp;""),0)-IFERROR(VALUE($I24&amp;""),0))))))&amp;""),(IFERROR(VALUE($G24&amp;""),0)-IFERROR(VALUE($I24&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K24&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K24&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K24&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K24&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K24&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K24&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K24),IF($K24=0,"0",ROUND($K24,9-INT(LOG10(ABS($K24))))&amp;""),$K24&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K24&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K24&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K24&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K24&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K24&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M24" s="3">
+        <f>IF(AND($A24=""),"",MID(IF(AND(NOT(($A24="")),NOT(EXACT($L24,"Completa"))),"; "&amp;IF(ISNUMBER($L24),IF($L24=0,"0",ROUND($L24,9-INT(LOG10(ABS($L24))))&amp;""),$L24&amp;""),"")&amp;IF(AND(NOT(($A24="")),EXACT($L24,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N24" s="3">
+        <f>IF(OR(AND(NOT(($A24="")),NOT(EXACT($L24,"Completa")))),2,IF(OR(AND(NOT(($A24="")),EXACT($L24,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n"/>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
       <c r="G25" s="3">
-        <f>IF($A25="","",($D25+($E25*$F25)))</f>
+        <f>IF(AND($A25=""),"",(IFERROR(VALUE($D25&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E25&amp;""),0)*IFERROR(VALUE($F25&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H25" s="3">
-        <f>IF($A25="","",COUNTIF(Asignacion!$B$4:$B$34,$A25))</f>
+        <f>IF(AND($A25=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A25)))))</f>
         <v/>
       </c>
       <c r="I25" s="3">
-        <f>IF($A25="","",SUMIF(Asignacion!$B$4:$B$34,$A25,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A25=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A25)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J25" s="3">
-        <f>IF($A25="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A25,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A25=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A25)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K25" s="3">
-        <f>IF($A25="","",COUNTIFS(Asignacion!$B$4:$B$34,$A25,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A25=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A25)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L25" s="3">
-        <f>IF($A25="","",IF(($H25=0),"Sin filas de carga",IF(($I25&lt;$G25),(IF(($G25-$I25)=1,"Falta","Faltan")&amp;" "&amp;($G25-$I25)&amp;" horas de carga"),IF(($K25&gt;0),(IF($K25=1,"Falta","Faltan")&amp;" "&amp;$K25&amp;" "&amp;IF($K25=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A25=""),"",IF(EXACT($H25,0),"Sin filas de carga",IF((IFERROR(VALUE($I25&amp;""),0)&lt;IFERROR(VALUE($G25&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G25&amp;""),0)-IFERROR(VALUE($I25&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G25&amp;""),0)-IFERROR(VALUE($I25&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G25&amp;""),0)-IFERROR(VALUE($I25&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G25&amp;""),0)-IFERROR(VALUE($I25&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G25&amp;""),0)-IFERROR(VALUE($I25&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G25&amp;""),0)-IFERROR(VALUE($I25&amp;""),0))),IF((IFERROR(VALUE($G25&amp;""),0)-IFERROR(VALUE($I25&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G25&amp;""),0)-IFERROR(VALUE($I25&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G25&amp;""),0)-IFERROR(VALUE($I25&amp;""),0))))))&amp;""),(IFERROR(VALUE($G25&amp;""),0)-IFERROR(VALUE($I25&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K25&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K25&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K25&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K25&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K25&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K25&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K25),IF($K25=0,"0",ROUND($K25,9-INT(LOG10(ABS($K25))))&amp;""),$K25&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K25&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K25&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K25&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K25&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K25&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M25" s="3">
+        <f>IF(AND($A25=""),"",MID(IF(AND(NOT(($A25="")),NOT(EXACT($L25,"Completa"))),"; "&amp;IF(ISNUMBER($L25),IF($L25=0,"0",ROUND($L25,9-INT(LOG10(ABS($L25))))&amp;""),$L25&amp;""),"")&amp;IF(AND(NOT(($A25="")),EXACT($L25,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N25" s="3">
+        <f>IF(OR(AND(NOT(($A25="")),NOT(EXACT($L25,"Completa")))),2,IF(OR(AND(NOT(($A25="")),EXACT($L25,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
       <c r="G26" s="3">
-        <f>IF($A26="","",($D26+($E26*$F26)))</f>
+        <f>IF(AND($A26=""),"",(IFERROR(VALUE($D26&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E26&amp;""),0)*IFERROR(VALUE($F26&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H26" s="3">
-        <f>IF($A26="","",COUNTIF(Asignacion!$B$4:$B$34,$A26))</f>
+        <f>IF(AND($A26=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A26)))))</f>
         <v/>
       </c>
       <c r="I26" s="3">
-        <f>IF($A26="","",SUMIF(Asignacion!$B$4:$B$34,$A26,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A26=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A26)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J26" s="3">
-        <f>IF($A26="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A26,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A26=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A26)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K26" s="3">
-        <f>IF($A26="","",COUNTIFS(Asignacion!$B$4:$B$34,$A26,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A26=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A26)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L26" s="3">
-        <f>IF($A26="","",IF(($H26=0),"Sin filas de carga",IF(($I26&lt;$G26),(IF(($G26-$I26)=1,"Falta","Faltan")&amp;" "&amp;($G26-$I26)&amp;" horas de carga"),IF(($K26&gt;0),(IF($K26=1,"Falta","Faltan")&amp;" "&amp;$K26&amp;" "&amp;IF($K26=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A26=""),"",IF(EXACT($H26,0),"Sin filas de carga",IF((IFERROR(VALUE($I26&amp;""),0)&lt;IFERROR(VALUE($G26&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G26&amp;""),0)-IFERROR(VALUE($I26&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G26&amp;""),0)-IFERROR(VALUE($I26&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G26&amp;""),0)-IFERROR(VALUE($I26&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G26&amp;""),0)-IFERROR(VALUE($I26&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G26&amp;""),0)-IFERROR(VALUE($I26&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G26&amp;""),0)-IFERROR(VALUE($I26&amp;""),0))),IF((IFERROR(VALUE($G26&amp;""),0)-IFERROR(VALUE($I26&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G26&amp;""),0)-IFERROR(VALUE($I26&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G26&amp;""),0)-IFERROR(VALUE($I26&amp;""),0))))))&amp;""),(IFERROR(VALUE($G26&amp;""),0)-IFERROR(VALUE($I26&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K26&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K26&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K26&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K26&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K26&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K26&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K26),IF($K26=0,"0",ROUND($K26,9-INT(LOG10(ABS($K26))))&amp;""),$K26&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K26&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K26&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K26&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K26&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K26&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M26" s="3">
+        <f>IF(AND($A26=""),"",MID(IF(AND(NOT(($A26="")),NOT(EXACT($L26,"Completa"))),"; "&amp;IF(ISNUMBER($L26),IF($L26=0,"0",ROUND($L26,9-INT(LOG10(ABS($L26))))&amp;""),$L26&amp;""),"")&amp;IF(AND(NOT(($A26="")),EXACT($L26,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N26" s="3">
+        <f>IF(OR(AND(NOT(($A26="")),NOT(EXACT($L26,"Completa")))),2,IF(OR(AND(NOT(($A26="")),EXACT($L26,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n"/>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
       <c r="G27" s="3">
-        <f>IF($A27="","",($D27+($E27*$F27)))</f>
+        <f>IF(AND($A27=""),"",(IFERROR(VALUE($D27&amp;""),0)+IFERROR(VALUE((IFERROR(VALUE($E27&amp;""),0)*IFERROR(VALUE($F27&amp;""),0))&amp;""),0)))</f>
         <v/>
       </c>
       <c r="H27" s="3">
-        <f>IF($A27="","",COUNTIF(Asignacion!$B$4:$B$34,$A27))</f>
+        <f>IF(AND($A27=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A27)))))</f>
         <v/>
       </c>
       <c r="I27" s="3">
-        <f>IF($A27="","",SUMIF(Asignacion!$B$4:$B$34,$A27,Asignacion!$G$4:$G$34))</f>
+        <f>IF(AND($A27=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A27)))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="J27" s="3">
-        <f>IF($A27="","",SUMIFS(Asignacion!$G$4:$G$34,Asignacion!$B$4:$B$34,$A27,Asignacion!$E$4:$E$34,"&lt;&gt;"))</f>
+        <f>IF(AND($A27=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A27)))*((1-(('Asignacion'!$E$4:$E$34=""))))*(IFERROR(VALUE('Asignacion'!$G$4:$G$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="K27" s="3">
-        <f>IF($A27="","",COUNTIFS(Asignacion!$B$4:$B$34,$A27,Asignacion!$E$4:$E$34,""))</f>
+        <f>IF(AND($A27=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$B$4:$B$34,$A27)))*(('Asignacion'!$E$4:$E$34=""))))</f>
         <v/>
       </c>
       <c r="L27" s="3">
-        <f>IF($A27="","",IF(($H27=0),"Sin filas de carga",IF(($I27&lt;$G27),(IF(($G27-$I27)=1,"Falta","Faltan")&amp;" "&amp;($G27-$I27)&amp;" horas de carga"),IF(($K27&gt;0),(IF($K27=1,"Falta","Faltan")&amp;" "&amp;$K27&amp;" "&amp;IF($K27=1,"profesor","profesores")),"Completa"))))</f>
+        <f>IF(AND($A27=""),"",IF(EXACT($H27,0),"Sin filas de carga",IF((IFERROR(VALUE($I27&amp;""),0)&lt;IFERROR(VALUE($G27&amp;""),0)),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($G27&amp;""),0)-IFERROR(VALUE($I27&amp;""),0))&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($G27&amp;""),0)-IFERROR(VALUE($I27&amp;""),0))&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($G27&amp;""),0)-IFERROR(VALUE($I27&amp;""),0))&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($G27&amp;""),0)-IFERROR(VALUE($I27&amp;""),0))&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($G27&amp;""),0)-IFERROR(VALUE($I27&amp;""),0))&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($G27&amp;""),0)-IFERROR(VALUE($I27&amp;""),0))),IF((IFERROR(VALUE($G27&amp;""),0)-IFERROR(VALUE($I27&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($G27&amp;""),0)-IFERROR(VALUE($I27&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($G27&amp;""),0)-IFERROR(VALUE($I27&amp;""),0))))))&amp;""),(IFERROR(VALUE($G27&amp;""),0)-IFERROR(VALUE($I27&amp;""),0))&amp;"")&amp;" horas de carga"),IF((IFERROR(VALUE($K27&amp;""),0)&gt;0),(IF(ISNUMBER(IF(IFERROR(VALUE($K27&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($K27&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($K27&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K27&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($K27&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($K27),IF($K27=0,"0",ROUND($K27,9-INT(LOG10(ABS($K27))))&amp;""),$K27&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($K27&amp;""),0)=1,"profesor","profesores")),IF(IF(IFERROR(VALUE($K27&amp;""),0)=1,"profesor","profesores")=0,"0",ROUND(IF(IFERROR(VALUE($K27&amp;""),0)=1,"profesor","profesores"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($K27&amp;""),0)=1,"profesor","profesores")))))&amp;""),IF(IFERROR(VALUE($K27&amp;""),0)=1,"profesor","profesores")&amp;"")),"Completa"))))</f>
+        <v/>
+      </c>
+      <c r="M27" s="3">
+        <f>IF(AND($A27=""),"",MID(IF(AND(NOT(($A27="")),NOT(EXACT($L27,"Completa"))),"; "&amp;IF(ISNUMBER($L27),IF($L27=0,"0",ROUND($L27,9-INT(LOG10(ABS($L27))))&amp;""),$L27&amp;""),"")&amp;IF(AND(NOT(($A27="")),EXACT($L27,"Completa")),"; "&amp;"cobertura completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="N27" s="3">
+        <f>IF(OR(AND(NOT(($A27="")),NOT(EXACT($L27,"Completa")))),2,IF(OR(AND(NOT(($A27="")),EXACT($L27,"Completa"))),1,0))</f>
         <v/>
       </c>
     </row>
@@ -3400,21 +4071,22 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <conditionalFormatting sqref="B4:B27">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
-      <formula>AND(NOT(($A4="")),NOT(($L4="Completa")))</formula>
+      <formula>AND(NOT(($A4="")),NOT(EXACT($L4,"Completa")))</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="0">
-      <formula>AND(NOT(($A4="")),($L4="Completa"))</formula>
+      <formula>AND(NOT(($A4="")),EXACT($L4,"Completa"))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4:L27">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
-      <formula>AND(NOT(($A4="")),NOT(($L4="Completa")))</formula>
+      <formula>AND(NOT(($A4="")),NOT(EXACT($L4,"Completa")))</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="0">
-      <formula>AND(NOT(($A4="")),($L4="Completa"))</formula>
+      <formula>AND(NOT(($A4="")),EXACT($L4,"Completa"))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3442,17 +4114,17 @@
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="42" customWidth="1" min="15" max="15"/>
-    <col width="42" customWidth="1" min="16" max="16"/>
-    <col width="42" customWidth="1" min="17" max="17"/>
-    <col width="42" customWidth="1" min="18" max="18"/>
-    <col width="42" customWidth="1" min="19" max="19"/>
-    <col width="42" customWidth="1" min="20" max="20"/>
-    <col width="42" customWidth="1" min="21" max="21"/>
-    <col width="42" customWidth="1" min="22" max="22"/>
-    <col width="42" customWidth="1" min="23" max="23"/>
-    <col width="42" customWidth="1" min="24" max="24"/>
-    <col width="42" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3591,10 +4263,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>PIAD#1</t>
-        </is>
+      <c r="A4" s="3">
+        <f>"PIAD"&amp;CHAR(30)&amp;"1"</f>
+        <v/>
       </c>
       <c r="B4" s="3" t="n">
         <v>1</v>
@@ -3664,10 +4335,9 @@
       <c r="Y4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>PIAD#2</t>
-        </is>
+      <c r="A5" s="3">
+        <f>"PIAD"&amp;CHAR(30)&amp;"2"</f>
+        <v/>
       </c>
       <c r="B5" s="3" t="n">
         <v>2</v>
@@ -3725,59 +4395,58 @@
       </c>
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#1",'Detalle - Lo que imparte'!$A$4:$M$11,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P5" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#1",'Detalle - Lo que imparte'!$A$4:$M$11,3,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q5" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#1",'Detalle - Lo que imparte'!$A$4:$M$11,4,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R5" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#1",'Detalle - Lo que imparte'!$A$4:$M$11,5,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S5" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#1",'Detalle - Lo que imparte'!$A$4:$M$11,6,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T5" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#1",'Detalle - Lo que imparte'!$A$4:$M$11,7,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U5" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#1",'Detalle - Lo que imparte'!$A$4:$M$11,8,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V5" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#1",'Detalle - Lo que imparte'!$A$4:$M$11,9,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W5" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#1",'Detalle - Lo que imparte'!$A$4:$M$11,10,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="X5" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#1",'Detalle - Lo que imparte'!$A$4:$M$11,11,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Y5" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#1",'Detalle - Lo que imparte'!$A$4:$M$11,12,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Z5">
-        <f>IFERROR(VLOOKUP("PIAD#1",'Detalle - Lo que imparte'!$A$4:$M$11,13,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>PIAD#3</t>
-        </is>
+      <c r="A6" s="3">
+        <f>"PIAD"&amp;CHAR(30)&amp;"3"</f>
+        <v/>
       </c>
       <c r="B6" s="3" t="n">
         <v>3</v>
@@ -3835,59 +4504,58 @@
       </c>
       <c r="N6" s="3" t="n"/>
       <c r="O6" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#2",'Detalle - Lo que imparte'!$A$4:$M$11,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P6" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#2",'Detalle - Lo que imparte'!$A$4:$M$11,3,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q6" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#2",'Detalle - Lo que imparte'!$A$4:$M$11,4,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R6" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#2",'Detalle - Lo que imparte'!$A$4:$M$11,5,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S6" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#2",'Detalle - Lo que imparte'!$A$4:$M$11,6,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T6" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#2",'Detalle - Lo que imparte'!$A$4:$M$11,7,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U6" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#2",'Detalle - Lo que imparte'!$A$4:$M$11,8,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V6" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#2",'Detalle - Lo que imparte'!$A$4:$M$11,9,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W6" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#2",'Detalle - Lo que imparte'!$A$4:$M$11,10,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="X6" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#2",'Detalle - Lo que imparte'!$A$4:$M$11,11,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Y6" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#2",'Detalle - Lo que imparte'!$A$4:$M$11,12,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Z6">
-        <f>IFERROR(VLOOKUP("PIAD#2",'Detalle - Lo que imparte'!$A$4:$M$11,13,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>PIAD#4</t>
-        </is>
+      <c r="A7" s="3">
+        <f>"PIAD"&amp;CHAR(30)&amp;"4"</f>
+        <v/>
       </c>
       <c r="B7" s="3" t="n">
         <v>4</v>
@@ -3941,59 +4609,58 @@
       </c>
       <c r="N7" s="3" t="n"/>
       <c r="O7" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#3",'Detalle - Lo que imparte'!$A$4:$M$11,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P7" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#3",'Detalle - Lo que imparte'!$A$4:$M$11,3,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q7" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#3",'Detalle - Lo que imparte'!$A$4:$M$11,4,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R7" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#3",'Detalle - Lo que imparte'!$A$4:$M$11,5,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S7" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#3",'Detalle - Lo que imparte'!$A$4:$M$11,6,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T7" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#3",'Detalle - Lo que imparte'!$A$4:$M$11,7,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U7" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#3",'Detalle - Lo que imparte'!$A$4:$M$11,8,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V7" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#3",'Detalle - Lo que imparte'!$A$4:$M$11,9,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W7" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#3",'Detalle - Lo que imparte'!$A$4:$M$11,10,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="X7" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#3",'Detalle - Lo que imparte'!$A$4:$M$11,11,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Y7" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#3",'Detalle - Lo que imparte'!$A$4:$M$11,12,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Z7">
-        <f>IFERROR(VLOOKUP("PIAD#3",'Detalle - Lo que imparte'!$A$4:$M$11,13,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>MARA#1</t>
-        </is>
+      <c r="A8" s="3">
+        <f>"MARA"&amp;CHAR(30)&amp;"1"</f>
+        <v/>
       </c>
       <c r="B8" s="3" t="n">
         <v>6</v>
@@ -4047,59 +4714,58 @@
       </c>
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#4",'Detalle - Lo que imparte'!$A$4:$M$11,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P8" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#4",'Detalle - Lo que imparte'!$A$4:$M$11,3,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q8" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#4",'Detalle - Lo que imparte'!$A$4:$M$11,4,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R8" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#4",'Detalle - Lo que imparte'!$A$4:$M$11,5,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S8" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#4",'Detalle - Lo que imparte'!$A$4:$M$11,6,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T8" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#4",'Detalle - Lo que imparte'!$A$4:$M$11,7,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U8" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#4",'Detalle - Lo que imparte'!$A$4:$M$11,8,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V8" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#4",'Detalle - Lo que imparte'!$A$4:$M$11,9,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W8" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#4",'Detalle - Lo que imparte'!$A$4:$M$11,10,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="X8" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#4",'Detalle - Lo que imparte'!$A$4:$M$11,11,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Y8" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#4",'Detalle - Lo que imparte'!$A$4:$M$11,12,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Z8">
-        <f>IFERROR(VLOOKUP("PIAD#4",'Detalle - Lo que imparte'!$A$4:$M$11,13,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>MARA#2</t>
-        </is>
+      <c r="A9" s="3">
+        <f>"MARA"&amp;CHAR(30)&amp;"2"</f>
+        <v/>
       </c>
       <c r="B9" s="3" t="n">
         <v>7</v>
@@ -4157,59 +4823,58 @@
       </c>
       <c r="N9" s="3" t="n"/>
       <c r="O9" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#5",'Detalle - Lo que imparte'!$A$4:$M$11,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P9" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#5",'Detalle - Lo que imparte'!$A$4:$M$11,3,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q9" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#5",'Detalle - Lo que imparte'!$A$4:$M$11,4,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R9" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#5",'Detalle - Lo que imparte'!$A$4:$M$11,5,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S9" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#5",'Detalle - Lo que imparte'!$A$4:$M$11,6,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T9" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#5",'Detalle - Lo que imparte'!$A$4:$M$11,7,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U9" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#5",'Detalle - Lo que imparte'!$A$4:$M$11,8,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V9" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#5",'Detalle - Lo que imparte'!$A$4:$M$11,9,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W9" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#5",'Detalle - Lo que imparte'!$A$4:$M$11,10,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="X9" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#5",'Detalle - Lo que imparte'!$A$4:$M$11,11,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Y9" s="3">
-        <f>IFERROR(VLOOKUP("PIAD#5",'Detalle - Lo que imparte'!$A$4:$M$11,12,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Z9">
-        <f>IFERROR(VLOOKUP("PIAD#5",'Detalle - Lo que imparte'!$A$4:$M$11,13,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>MARA#3</t>
-        </is>
+      <c r="A10" s="3">
+        <f>"MARA"&amp;CHAR(30)&amp;"3"</f>
+        <v/>
       </c>
       <c r="B10" s="3" t="n">
         <v>9</v>
@@ -4279,10 +4944,9 @@
       <c r="Y10" s="3" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>LUGO#1</t>
-        </is>
+      <c r="A11" s="3">
+        <f>"LUGO"&amp;CHAR(30)&amp;"1"</f>
+        <v/>
       </c>
       <c r="B11" s="3" t="n">
         <v>5</v>
@@ -4340,51 +5004,51 @@
       </c>
       <c r="N11" s="3" t="n"/>
       <c r="O11" s="3">
-        <f>IFERROR(VLOOKUP("MARA#1",'Detalle - Lo que imparte'!$A$4:$M$11,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P11" s="3">
-        <f>IFERROR(VLOOKUP("MARA#1",'Detalle - Lo que imparte'!$A$4:$M$11,3,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q11" s="3">
-        <f>IFERROR(VLOOKUP("MARA#1",'Detalle - Lo que imparte'!$A$4:$M$11,4,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R11" s="3">
-        <f>IFERROR(VLOOKUP("MARA#1",'Detalle - Lo que imparte'!$A$4:$M$11,5,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S11" s="3">
-        <f>IFERROR(VLOOKUP("MARA#1",'Detalle - Lo que imparte'!$A$4:$M$11,6,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T11" s="3">
-        <f>IFERROR(VLOOKUP("MARA#1",'Detalle - Lo que imparte'!$A$4:$M$11,7,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U11" s="3">
-        <f>IFERROR(VLOOKUP("MARA#1",'Detalle - Lo que imparte'!$A$4:$M$11,8,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V11" s="3">
-        <f>IFERROR(VLOOKUP("MARA#1",'Detalle - Lo que imparte'!$A$4:$M$11,9,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W11" s="3">
-        <f>IFERROR(VLOOKUP("MARA#1",'Detalle - Lo que imparte'!$A$4:$M$11,10,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="X11" s="3">
-        <f>IFERROR(VLOOKUP("MARA#1",'Detalle - Lo que imparte'!$A$4:$M$11,11,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Y11" s="3">
-        <f>IFERROR(VLOOKUP("MARA#1",'Detalle - Lo que imparte'!$A$4:$M$11,12,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Z11">
-        <f>IFERROR(VLOOKUP("MARA#1",'Detalle - Lo que imparte'!$A$4:$M$11,13,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -4404,51 +5068,51 @@
       <c r="M12" s="3" t="n"/>
       <c r="N12" s="3" t="n"/>
       <c r="O12" s="3">
-        <f>IFERROR(VLOOKUP("MARA#2",'Detalle - Lo que imparte'!$A$4:$M$11,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P12" s="3">
-        <f>IFERROR(VLOOKUP("MARA#2",'Detalle - Lo que imparte'!$A$4:$M$11,3,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q12" s="3">
-        <f>IFERROR(VLOOKUP("MARA#2",'Detalle - Lo que imparte'!$A$4:$M$11,4,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R12" s="3">
-        <f>IFERROR(VLOOKUP("MARA#2",'Detalle - Lo que imparte'!$A$4:$M$11,5,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S12" s="3">
-        <f>IFERROR(VLOOKUP("MARA#2",'Detalle - Lo que imparte'!$A$4:$M$11,6,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T12" s="3">
-        <f>IFERROR(VLOOKUP("MARA#2",'Detalle - Lo que imparte'!$A$4:$M$11,7,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U12" s="3">
-        <f>IFERROR(VLOOKUP("MARA#2",'Detalle - Lo que imparte'!$A$4:$M$11,8,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V12" s="3">
-        <f>IFERROR(VLOOKUP("MARA#2",'Detalle - Lo que imparte'!$A$4:$M$11,9,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W12" s="3">
-        <f>IFERROR(VLOOKUP("MARA#2",'Detalle - Lo que imparte'!$A$4:$M$11,10,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="X12" s="3">
-        <f>IFERROR(VLOOKUP("MARA#2",'Detalle - Lo que imparte'!$A$4:$M$11,11,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Y12" s="3">
-        <f>IFERROR(VLOOKUP("MARA#2",'Detalle - Lo que imparte'!$A$4:$M$11,12,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Z12">
-        <f>IFERROR(VLOOKUP("MARA#2",'Detalle - Lo que imparte'!$A$4:$M$11,13,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -4468,51 +5132,51 @@
       <c r="M13" s="3" t="n"/>
       <c r="N13" s="3" t="n"/>
       <c r="O13" s="3">
-        <f>IFERROR(VLOOKUP("MARA#3",'Detalle - Lo que imparte'!$A$4:$M$11,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P13" s="3">
-        <f>IFERROR(VLOOKUP("MARA#3",'Detalle - Lo que imparte'!$A$4:$M$11,3,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q13" s="3">
-        <f>IFERROR(VLOOKUP("MARA#3",'Detalle - Lo que imparte'!$A$4:$M$11,4,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R13" s="3">
-        <f>IFERROR(VLOOKUP("MARA#3",'Detalle - Lo que imparte'!$A$4:$M$11,5,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S13" s="3">
-        <f>IFERROR(VLOOKUP("MARA#3",'Detalle - Lo que imparte'!$A$4:$M$11,6,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T13" s="3">
-        <f>IFERROR(VLOOKUP("MARA#3",'Detalle - Lo que imparte'!$A$4:$M$11,7,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U13" s="3">
-        <f>IFERROR(VLOOKUP("MARA#3",'Detalle - Lo que imparte'!$A$4:$M$11,8,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V13" s="3">
-        <f>IFERROR(VLOOKUP("MARA#3",'Detalle - Lo que imparte'!$A$4:$M$11,9,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W13" s="3">
-        <f>IFERROR(VLOOKUP("MARA#3",'Detalle - Lo que imparte'!$A$4:$M$11,10,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="X13" s="3">
-        <f>IFERROR(VLOOKUP("MARA#3",'Detalle - Lo que imparte'!$A$4:$M$11,11,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Y13" s="3">
-        <f>IFERROR(VLOOKUP("MARA#3",'Detalle - Lo que imparte'!$A$4:$M$11,12,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Z13">
-        <f>IFERROR(VLOOKUP("MARA#3",'Detalle - Lo que imparte'!$A$4:$M$11,13,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -4532,51 +5196,51 @@
       <c r="M14" s="3" t="n"/>
       <c r="N14" s="3" t="n"/>
       <c r="O14" s="3">
-        <f>IFERROR(VLOOKUP("MARA#4",'Detalle - Lo que imparte'!$A$4:$M$11,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P14" s="3">
-        <f>IFERROR(VLOOKUP("MARA#4",'Detalle - Lo que imparte'!$A$4:$M$11,3,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q14" s="3">
-        <f>IFERROR(VLOOKUP("MARA#4",'Detalle - Lo que imparte'!$A$4:$M$11,4,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R14" s="3">
-        <f>IFERROR(VLOOKUP("MARA#4",'Detalle - Lo que imparte'!$A$4:$M$11,5,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S14" s="3">
-        <f>IFERROR(VLOOKUP("MARA#4",'Detalle - Lo que imparte'!$A$4:$M$11,6,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T14" s="3">
-        <f>IFERROR(VLOOKUP("MARA#4",'Detalle - Lo que imparte'!$A$4:$M$11,7,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U14" s="3">
-        <f>IFERROR(VLOOKUP("MARA#4",'Detalle - Lo que imparte'!$A$4:$M$11,8,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V14" s="3">
-        <f>IFERROR(VLOOKUP("MARA#4",'Detalle - Lo que imparte'!$A$4:$M$11,9,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W14" s="3">
-        <f>IFERROR(VLOOKUP("MARA#4",'Detalle - Lo que imparte'!$A$4:$M$11,10,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="X14" s="3">
-        <f>IFERROR(VLOOKUP("MARA#4",'Detalle - Lo que imparte'!$A$4:$M$11,11,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Y14" s="3">
-        <f>IFERROR(VLOOKUP("MARA#4",'Detalle - Lo que imparte'!$A$4:$M$11,12,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Z14">
-        <f>IFERROR(VLOOKUP("MARA#4",'Detalle - Lo que imparte'!$A$4:$M$11,13,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -4596,51 +5260,51 @@
       <c r="M15" s="3" t="n"/>
       <c r="N15" s="3" t="n"/>
       <c r="O15" s="3">
-        <f>IFERROR(VLOOKUP("MARA#5",'Detalle - Lo que imparte'!$A$4:$M$11,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P15" s="3">
-        <f>IFERROR(VLOOKUP("MARA#5",'Detalle - Lo que imparte'!$A$4:$M$11,3,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q15" s="3">
-        <f>IFERROR(VLOOKUP("MARA#5",'Detalle - Lo que imparte'!$A$4:$M$11,4,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R15" s="3">
-        <f>IFERROR(VLOOKUP("MARA#5",'Detalle - Lo que imparte'!$A$4:$M$11,5,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S15" s="3">
-        <f>IFERROR(VLOOKUP("MARA#5",'Detalle - Lo que imparte'!$A$4:$M$11,6,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T15" s="3">
-        <f>IFERROR(VLOOKUP("MARA#5",'Detalle - Lo que imparte'!$A$4:$M$11,7,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U15" s="3">
-        <f>IFERROR(VLOOKUP("MARA#5",'Detalle - Lo que imparte'!$A$4:$M$11,8,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V15" s="3">
-        <f>IFERROR(VLOOKUP("MARA#5",'Detalle - Lo que imparte'!$A$4:$M$11,9,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W15" s="3">
-        <f>IFERROR(VLOOKUP("MARA#5",'Detalle - Lo que imparte'!$A$4:$M$11,10,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="X15" s="3">
-        <f>IFERROR(VLOOKUP("MARA#5",'Detalle - Lo que imparte'!$A$4:$M$11,11,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Y15" s="3">
-        <f>IFERROR(VLOOKUP("MARA#5",'Detalle - Lo que imparte'!$A$4:$M$11,12,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Z15">
-        <f>IFERROR(VLOOKUP("MARA#5",'Detalle - Lo que imparte'!$A$4:$M$11,13,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -4691,51 +5355,51 @@
       <c r="M17" s="3" t="n"/>
       <c r="N17" s="3" t="n"/>
       <c r="O17" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#1",'Detalle - Lo que imparte'!$A$4:$M$11,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P17" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#1",'Detalle - Lo que imparte'!$A$4:$M$11,3,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q17" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#1",'Detalle - Lo que imparte'!$A$4:$M$11,4,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R17" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#1",'Detalle - Lo que imparte'!$A$4:$M$11,5,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S17" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#1",'Detalle - Lo que imparte'!$A$4:$M$11,6,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T17" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#1",'Detalle - Lo que imparte'!$A$4:$M$11,7,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U17" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#1",'Detalle - Lo que imparte'!$A$4:$M$11,8,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V17" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#1",'Detalle - Lo que imparte'!$A$4:$M$11,9,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W17" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#1",'Detalle - Lo que imparte'!$A$4:$M$11,10,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="X17" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#1",'Detalle - Lo que imparte'!$A$4:$M$11,11,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Y17" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#1",'Detalle - Lo que imparte'!$A$4:$M$11,12,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Z17">
-        <f>IFERROR(VLOOKUP("LUGO#1",'Detalle - Lo que imparte'!$A$4:$M$11,13,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -4755,51 +5419,51 @@
       <c r="M18" s="3" t="n"/>
       <c r="N18" s="3" t="n"/>
       <c r="O18" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#2",'Detalle - Lo que imparte'!$A$4:$M$11,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P18" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#2",'Detalle - Lo que imparte'!$A$4:$M$11,3,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q18" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#2",'Detalle - Lo que imparte'!$A$4:$M$11,4,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R18" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#2",'Detalle - Lo que imparte'!$A$4:$M$11,5,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S18" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#2",'Detalle - Lo que imparte'!$A$4:$M$11,6,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T18" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#2",'Detalle - Lo que imparte'!$A$4:$M$11,7,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U18" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#2",'Detalle - Lo que imparte'!$A$4:$M$11,8,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V18" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#2",'Detalle - Lo que imparte'!$A$4:$M$11,9,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W18" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#2",'Detalle - Lo que imparte'!$A$4:$M$11,10,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="X18" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#2",'Detalle - Lo que imparte'!$A$4:$M$11,11,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Y18" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#2",'Detalle - Lo que imparte'!$A$4:$M$11,12,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Z18">
-        <f>IFERROR(VLOOKUP("LUGO#2",'Detalle - Lo que imparte'!$A$4:$M$11,13,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -4819,51 +5483,51 @@
       <c r="M19" s="3" t="n"/>
       <c r="N19" s="3" t="n"/>
       <c r="O19" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#3",'Detalle - Lo que imparte'!$A$4:$M$11,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P19" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#3",'Detalle - Lo que imparte'!$A$4:$M$11,3,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q19" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#3",'Detalle - Lo que imparte'!$A$4:$M$11,4,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R19" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#3",'Detalle - Lo que imparte'!$A$4:$M$11,5,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S19" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#3",'Detalle - Lo que imparte'!$A$4:$M$11,6,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T19" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#3",'Detalle - Lo que imparte'!$A$4:$M$11,7,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U19" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#3",'Detalle - Lo que imparte'!$A$4:$M$11,8,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V19" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#3",'Detalle - Lo que imparte'!$A$4:$M$11,9,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W19" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#3",'Detalle - Lo que imparte'!$A$4:$M$11,10,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="X19" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#3",'Detalle - Lo que imparte'!$A$4:$M$11,11,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Y19" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#3",'Detalle - Lo que imparte'!$A$4:$M$11,12,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Z19">
-        <f>IFERROR(VLOOKUP("LUGO#3",'Detalle - Lo que imparte'!$A$4:$M$11,13,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -4883,51 +5547,51 @@
       <c r="M20" s="3" t="n"/>
       <c r="N20" s="3" t="n"/>
       <c r="O20" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#4",'Detalle - Lo que imparte'!$A$4:$M$11,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P20" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#4",'Detalle - Lo que imparte'!$A$4:$M$11,3,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q20" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#4",'Detalle - Lo que imparte'!$A$4:$M$11,4,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R20" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#4",'Detalle - Lo que imparte'!$A$4:$M$11,5,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S20" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#4",'Detalle - Lo que imparte'!$A$4:$M$11,6,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T20" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#4",'Detalle - Lo que imparte'!$A$4:$M$11,7,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U20" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#4",'Detalle - Lo que imparte'!$A$4:$M$11,8,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V20" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#4",'Detalle - Lo que imparte'!$A$4:$M$11,9,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W20" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#4",'Detalle - Lo que imparte'!$A$4:$M$11,10,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="X20" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#4",'Detalle - Lo que imparte'!$A$4:$M$11,11,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Y20" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#4",'Detalle - Lo que imparte'!$A$4:$M$11,12,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Z20">
-        <f>IFERROR(VLOOKUP("LUGO#4",'Detalle - Lo que imparte'!$A$4:$M$11,13,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -4947,51 +5611,51 @@
       <c r="M21" s="3" t="n"/>
       <c r="N21" s="3" t="n"/>
       <c r="O21" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#5",'Detalle - Lo que imparte'!$A$4:$M$11,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P21" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#5",'Detalle - Lo que imparte'!$A$4:$M$11,3,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q21" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#5",'Detalle - Lo que imparte'!$A$4:$M$11,4,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R21" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#5",'Detalle - Lo que imparte'!$A$4:$M$11,5,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S21" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#5",'Detalle - Lo que imparte'!$A$4:$M$11,6,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T21" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#5",'Detalle - Lo que imparte'!$A$4:$M$11,7,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U21" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#5",'Detalle - Lo que imparte'!$A$4:$M$11,8,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V21" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#5",'Detalle - Lo que imparte'!$A$4:$M$11,9,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W21" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#5",'Detalle - Lo que imparte'!$A$4:$M$11,10,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="X21" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#5",'Detalle - Lo que imparte'!$A$4:$M$11,11,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Y21" s="3">
-        <f>IFERROR(VLOOKUP("LUGO#5",'Detalle - Lo que imparte'!$A$4:$M$11,12,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Z21">
-        <f>IFERROR(VLOOKUP("LUGO#5",'Detalle - Lo que imparte'!$A$4:$M$11,13,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -5042,51 +5706,51 @@
       <c r="M23" s="3" t="n"/>
       <c r="N23" s="3" t="n"/>
       <c r="O23" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#1",'Detalle - Lo que imparte'!$A$4:$M$11,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P23" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#1",'Detalle - Lo que imparte'!$A$4:$M$11,3,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q23" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#1",'Detalle - Lo que imparte'!$A$4:$M$11,4,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R23" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#1",'Detalle - Lo que imparte'!$A$4:$M$11,5,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S23" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#1",'Detalle - Lo que imparte'!$A$4:$M$11,6,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T23" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#1",'Detalle - Lo que imparte'!$A$4:$M$11,7,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U23" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#1",'Detalle - Lo que imparte'!$A$4:$M$11,8,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V23" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#1",'Detalle - Lo que imparte'!$A$4:$M$11,9,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W23" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#1",'Detalle - Lo que imparte'!$A$4:$M$11,10,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="X23" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#1",'Detalle - Lo que imparte'!$A$4:$M$11,11,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Y23" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#1",'Detalle - Lo que imparte'!$A$4:$M$11,12,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Z23">
-        <f>IFERROR(VLOOKUP("ROTO#1",'Detalle - Lo que imparte'!$A$4:$M$11,13,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -5106,51 +5770,51 @@
       <c r="M24" s="3" t="n"/>
       <c r="N24" s="3" t="n"/>
       <c r="O24" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#2",'Detalle - Lo que imparte'!$A$4:$M$11,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P24" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#2",'Detalle - Lo que imparte'!$A$4:$M$11,3,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q24" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#2",'Detalle - Lo que imparte'!$A$4:$M$11,4,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R24" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#2",'Detalle - Lo que imparte'!$A$4:$M$11,5,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S24" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#2",'Detalle - Lo que imparte'!$A$4:$M$11,6,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T24" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#2",'Detalle - Lo que imparte'!$A$4:$M$11,7,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U24" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#2",'Detalle - Lo que imparte'!$A$4:$M$11,8,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V24" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#2",'Detalle - Lo que imparte'!$A$4:$M$11,9,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W24" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#2",'Detalle - Lo que imparte'!$A$4:$M$11,10,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="X24" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#2",'Detalle - Lo que imparte'!$A$4:$M$11,11,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Y24" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#2",'Detalle - Lo que imparte'!$A$4:$M$11,12,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Z24">
-        <f>IFERROR(VLOOKUP("ROTO#2",'Detalle - Lo que imparte'!$A$4:$M$11,13,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -5170,51 +5834,51 @@
       <c r="M25" s="3" t="n"/>
       <c r="N25" s="3" t="n"/>
       <c r="O25" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#3",'Detalle - Lo que imparte'!$A$4:$M$11,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P25" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#3",'Detalle - Lo que imparte'!$A$4:$M$11,3,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q25" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#3",'Detalle - Lo que imparte'!$A$4:$M$11,4,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R25" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#3",'Detalle - Lo que imparte'!$A$4:$M$11,5,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S25" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#3",'Detalle - Lo que imparte'!$A$4:$M$11,6,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T25" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#3",'Detalle - Lo que imparte'!$A$4:$M$11,7,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U25" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#3",'Detalle - Lo que imparte'!$A$4:$M$11,8,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V25" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#3",'Detalle - Lo que imparte'!$A$4:$M$11,9,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W25" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#3",'Detalle - Lo que imparte'!$A$4:$M$11,10,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="X25" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#3",'Detalle - Lo que imparte'!$A$4:$M$11,11,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Y25" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#3",'Detalle - Lo que imparte'!$A$4:$M$11,12,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Z25">
-        <f>IFERROR(VLOOKUP("ROTO#3",'Detalle - Lo que imparte'!$A$4:$M$11,13,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -5234,51 +5898,51 @@
       <c r="M26" s="3" t="n"/>
       <c r="N26" s="3" t="n"/>
       <c r="O26" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#4",'Detalle - Lo que imparte'!$A$4:$M$11,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P26" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#4",'Detalle - Lo que imparte'!$A$4:$M$11,3,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q26" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#4",'Detalle - Lo que imparte'!$A$4:$M$11,4,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R26" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#4",'Detalle - Lo que imparte'!$A$4:$M$11,5,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S26" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#4",'Detalle - Lo que imparte'!$A$4:$M$11,6,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T26" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#4",'Detalle - Lo que imparte'!$A$4:$M$11,7,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U26" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#4",'Detalle - Lo que imparte'!$A$4:$M$11,8,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V26" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#4",'Detalle - Lo que imparte'!$A$4:$M$11,9,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W26" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#4",'Detalle - Lo que imparte'!$A$4:$M$11,10,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="X26" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#4",'Detalle - Lo que imparte'!$A$4:$M$11,11,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Y26" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#4",'Detalle - Lo que imparte'!$A$4:$M$11,12,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Z26">
-        <f>IFERROR(VLOOKUP("ROTO#4",'Detalle - Lo que imparte'!$A$4:$M$11,13,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -5298,52 +5962,139 @@
       <c r="M27" s="3" t="n"/>
       <c r="N27" s="3" t="n"/>
       <c r="O27" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#5",'Detalle - Lo que imparte'!$A$4:$M$11,2,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P27" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#5",'Detalle - Lo que imparte'!$A$4:$M$11,3,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q27" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#5",'Detalle - Lo que imparte'!$A$4:$M$11,4,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R27" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#5",'Detalle - Lo que imparte'!$A$4:$M$11,5,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S27" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#5",'Detalle - Lo que imparte'!$A$4:$M$11,6,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T27" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#5",'Detalle - Lo que imparte'!$A$4:$M$11,7,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U27" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#5",'Detalle - Lo que imparte'!$A$4:$M$11,8,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V27" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#5",'Detalle - Lo que imparte'!$A$4:$M$11,9,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W27" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#5",'Detalle - Lo que imparte'!$A$4:$M$11,10,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="X27" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#5",'Detalle - Lo que imparte'!$A$4:$M$11,11,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Y27" s="3">
-        <f>IFERROR(VLOOKUP("ROTO#5",'Detalle - Lo que imparte'!$A$4:$M$11,12,FALSE),"")</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Z27">
-        <f>IFERROR(VLOOKUP("ROTO#5",'Detalle - Lo que imparte'!$A$4:$M$11,13,FALSE),"")</f>
-        <v/>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00BFBFBF"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Listas de los desplegables</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>EST-CC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Conf</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PIAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>EST-MAT</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MARA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>PROB</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LUGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>MNUM</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ROTO</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/ejemplos/resultados/departamento.xlsx
+++ b/ejemplos/resultados/departamento.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="Asignacion">OFFSET('Asignacion'!$A$4,0,0,COUNTA('Asignacion'!$A$4:$A$34),12)</definedName>
+    <definedName name="Asignacion">OFFSET('Asignacion'!$A$4,0,0,COUNTA('Asignacion'!$A$4:$A$34),11)</definedName>
     <definedName name="Profesores">OFFSET('Carga por profesor'!$A$4,0,0,COUNTA('Carga por profesor'!$A$4:$A$27),7)</definedName>
     <definedName name="Asignaturas">OFFSET('Cobertura por asignatura'!$A$4,0,0,COUNTA('Cobertura por asignatura'!$A$4:$A$27),12)</definedName>
   </definedNames>
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -516,12 +516,11 @@
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
-    <col hidden="1" width="24" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col hidden="1" width="24" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,30 +573,25 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Par</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Codigo</t>
+          <t>Primera del par</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Primera del par</t>
+          <t>Cuenta</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Cuenta</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>(nivel de las marcas)</t>
         </is>
@@ -636,26 +630,22 @@
         <v/>
       </c>
       <c r="I4" s="3">
-        <f>IF(AND($A4=""),"",IF(OR(($E4=""),($B4="")),"",(IF(ISNUMBER($E4),IF($E4=0,"0",ROUND($E4,9-INT(LOG10(ABS($E4))))&amp;""),$E4&amp;"")&amp;"|"&amp;IF(ISNUMBER($B4),IF($B4=0,"0",ROUND($B4,9-INT(LOG10(ABS($B4))))&amp;""),$B4&amp;""))))</f>
+        <f>IF(AND($A4=""),"",(IF(ISNUMBER($B4),IF($B4=0,"0",ROUND($B4,9-INT(LOG10(ABS($B4))))&amp;""),$B4&amp;"")&amp;" "&amp;IF(ISNUMBER($C4),IF($C4=0,"0",ROUND($C4,9-INT(LOG10(ABS($C4))))&amp;""),$C4&amp;"")&amp;" "&amp;IF(ISNUMBER($D4),IF($D4=0,"0",ROUND($D4,9-INT(LOG10(ABS($D4))))&amp;""),$D4&amp;"")))</f>
         <v/>
       </c>
       <c r="J4" s="3">
-        <f>IF(AND($A4=""),"",(IF(ISNUMBER($B4),IF($B4=0,"0",ROUND($B4,9-INT(LOG10(ABS($B4))))&amp;""),$B4&amp;"")&amp;" "&amp;IF(ISNUMBER($C4),IF($C4=0,"0",ROUND($C4,9-INT(LOG10(ABS($C4))))&amp;""),$C4&amp;"")&amp;" "&amp;IF(ISNUMBER($D4),IF($D4=0,"0",ROUND($D4,9-INT(LOG10(ABS($D4))))&amp;""),$D4&amp;"")))</f>
+        <f>IF(AND($A4=""),"",IF(OR(($E4=""),($B4="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E4))*(EXACT('Asignacion'!$B$4:$B$34,$B4)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E4))*(EXACT('Asignacion'!$B$4:$B$34,$B4)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E4))*(EXACT('Asignacion'!$B$4:$B$34,$B4)),0),0))))))</f>
         <v/>
       </c>
       <c r="K4" s="3">
-        <f>IF(AND($A4=""),"",IF(EXACT($I4,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I4)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I4)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I4)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A4=""),"",IF(AND(NOT(EXACT($J4,"")),EXACT($J4,$I4)),1,0))</f>
         <v/>
       </c>
       <c r="L4" s="3">
-        <f>IF(AND($A4=""),"",IF(AND(NOT(EXACT($I4,"")),EXACT($K4,$J4)),1,0))</f>
+        <f>IF(AND($A4=""),"",MID(IF(AND(NOT(($B4="")),($E4="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M4" s="3">
-        <f>IF(AND($A4=""),"",MID(IF(AND(NOT(($B4="")),($E4="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N4" s="3">
         <f>IF(OR(AND(NOT(($B4="")),($E4=""))),2,0)</f>
         <v/>
       </c>
@@ -697,26 +687,22 @@
         <v/>
       </c>
       <c r="I5" s="3">
-        <f>IF(AND($A5=""),"",IF(OR(($E5=""),($B5="")),"",(IF(ISNUMBER($E5),IF($E5=0,"0",ROUND($E5,9-INT(LOG10(ABS($E5))))&amp;""),$E5&amp;"")&amp;"|"&amp;IF(ISNUMBER($B5),IF($B5=0,"0",ROUND($B5,9-INT(LOG10(ABS($B5))))&amp;""),$B5&amp;""))))</f>
+        <f>IF(AND($A5=""),"",(IF(ISNUMBER($B5),IF($B5=0,"0",ROUND($B5,9-INT(LOG10(ABS($B5))))&amp;""),$B5&amp;"")&amp;" "&amp;IF(ISNUMBER($C5),IF($C5=0,"0",ROUND($C5,9-INT(LOG10(ABS($C5))))&amp;""),$C5&amp;"")&amp;" "&amp;IF(ISNUMBER($D5),IF($D5=0,"0",ROUND($D5,9-INT(LOG10(ABS($D5))))&amp;""),$D5&amp;"")))</f>
         <v/>
       </c>
       <c r="J5" s="3">
-        <f>IF(AND($A5=""),"",(IF(ISNUMBER($B5),IF($B5=0,"0",ROUND($B5,9-INT(LOG10(ABS($B5))))&amp;""),$B5&amp;"")&amp;" "&amp;IF(ISNUMBER($C5),IF($C5=0,"0",ROUND($C5,9-INT(LOG10(ABS($C5))))&amp;""),$C5&amp;"")&amp;" "&amp;IF(ISNUMBER($D5),IF($D5=0,"0",ROUND($D5,9-INT(LOG10(ABS($D5))))&amp;""),$D5&amp;"")))</f>
+        <f>IF(AND($A5=""),"",IF(OR(($E5=""),($B5="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E5))*(EXACT('Asignacion'!$B$4:$B$34,$B5)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E5))*(EXACT('Asignacion'!$B$4:$B$34,$B5)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E5))*(EXACT('Asignacion'!$B$4:$B$34,$B5)),0),0))))))</f>
         <v/>
       </c>
       <c r="K5" s="3">
-        <f>IF(AND($A5=""),"",IF(EXACT($I5,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I5)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I5)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I5)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A5=""),"",IF(AND(NOT(EXACT($J5,"")),EXACT($J5,$I5)),1,0))</f>
         <v/>
       </c>
       <c r="L5" s="3">
-        <f>IF(AND($A5=""),"",IF(AND(NOT(EXACT($I5,"")),EXACT($K5,$J5)),1,0))</f>
+        <f>IF(AND($A5=""),"",MID(IF(AND(NOT(($B5="")),($E5="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M5" s="3">
-        <f>IF(AND($A5=""),"",MID(IF(AND(NOT(($B5="")),($E5="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N5" s="3">
         <f>IF(OR(AND(NOT(($B5="")),($E5=""))),2,0)</f>
         <v/>
       </c>
@@ -758,26 +744,22 @@
         <v/>
       </c>
       <c r="I6" s="3">
-        <f>IF(AND($A6=""),"",IF(OR(($E6=""),($B6="")),"",(IF(ISNUMBER($E6),IF($E6=0,"0",ROUND($E6,9-INT(LOG10(ABS($E6))))&amp;""),$E6&amp;"")&amp;"|"&amp;IF(ISNUMBER($B6),IF($B6=0,"0",ROUND($B6,9-INT(LOG10(ABS($B6))))&amp;""),$B6&amp;""))))</f>
+        <f>IF(AND($A6=""),"",(IF(ISNUMBER($B6),IF($B6=0,"0",ROUND($B6,9-INT(LOG10(ABS($B6))))&amp;""),$B6&amp;"")&amp;" "&amp;IF(ISNUMBER($C6),IF($C6=0,"0",ROUND($C6,9-INT(LOG10(ABS($C6))))&amp;""),$C6&amp;"")&amp;" "&amp;IF(ISNUMBER($D6),IF($D6=0,"0",ROUND($D6,9-INT(LOG10(ABS($D6))))&amp;""),$D6&amp;"")))</f>
         <v/>
       </c>
       <c r="J6" s="3">
-        <f>IF(AND($A6=""),"",(IF(ISNUMBER($B6),IF($B6=0,"0",ROUND($B6,9-INT(LOG10(ABS($B6))))&amp;""),$B6&amp;"")&amp;" "&amp;IF(ISNUMBER($C6),IF($C6=0,"0",ROUND($C6,9-INT(LOG10(ABS($C6))))&amp;""),$C6&amp;"")&amp;" "&amp;IF(ISNUMBER($D6),IF($D6=0,"0",ROUND($D6,9-INT(LOG10(ABS($D6))))&amp;""),$D6&amp;"")))</f>
+        <f>IF(AND($A6=""),"",IF(OR(($E6=""),($B6="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E6))*(EXACT('Asignacion'!$B$4:$B$34,$B6)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E6))*(EXACT('Asignacion'!$B$4:$B$34,$B6)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E6))*(EXACT('Asignacion'!$B$4:$B$34,$B6)),0),0))))))</f>
         <v/>
       </c>
       <c r="K6" s="3">
-        <f>IF(AND($A6=""),"",IF(EXACT($I6,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I6)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I6)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I6)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A6=""),"",IF(AND(NOT(EXACT($J6,"")),EXACT($J6,$I6)),1,0))</f>
         <v/>
       </c>
       <c r="L6" s="3">
-        <f>IF(AND($A6=""),"",IF(AND(NOT(EXACT($I6,"")),EXACT($K6,$J6)),1,0))</f>
+        <f>IF(AND($A6=""),"",MID(IF(AND(NOT(($B6="")),($E6="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M6" s="3">
-        <f>IF(AND($A6=""),"",MID(IF(AND(NOT(($B6="")),($E6="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N6" s="3">
         <f>IF(OR(AND(NOT(($B6="")),($E6=""))),2,0)</f>
         <v/>
       </c>
@@ -815,26 +797,22 @@
         <v/>
       </c>
       <c r="I7" s="3">
-        <f>IF(AND($A7=""),"",IF(OR(($E7=""),($B7="")),"",(IF(ISNUMBER($E7),IF($E7=0,"0",ROUND($E7,9-INT(LOG10(ABS($E7))))&amp;""),$E7&amp;"")&amp;"|"&amp;IF(ISNUMBER($B7),IF($B7=0,"0",ROUND($B7,9-INT(LOG10(ABS($B7))))&amp;""),$B7&amp;""))))</f>
+        <f>IF(AND($A7=""),"",(IF(ISNUMBER($B7),IF($B7=0,"0",ROUND($B7,9-INT(LOG10(ABS($B7))))&amp;""),$B7&amp;"")&amp;" "&amp;IF(ISNUMBER($C7),IF($C7=0,"0",ROUND($C7,9-INT(LOG10(ABS($C7))))&amp;""),$C7&amp;"")&amp;" "&amp;IF(ISNUMBER($D7),IF($D7=0,"0",ROUND($D7,9-INT(LOG10(ABS($D7))))&amp;""),$D7&amp;"")))</f>
         <v/>
       </c>
       <c r="J7" s="3">
-        <f>IF(AND($A7=""),"",(IF(ISNUMBER($B7),IF($B7=0,"0",ROUND($B7,9-INT(LOG10(ABS($B7))))&amp;""),$B7&amp;"")&amp;" "&amp;IF(ISNUMBER($C7),IF($C7=0,"0",ROUND($C7,9-INT(LOG10(ABS($C7))))&amp;""),$C7&amp;"")&amp;" "&amp;IF(ISNUMBER($D7),IF($D7=0,"0",ROUND($D7,9-INT(LOG10(ABS($D7))))&amp;""),$D7&amp;"")))</f>
+        <f>IF(AND($A7=""),"",IF(OR(($E7=""),($B7="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E7))*(EXACT('Asignacion'!$B$4:$B$34,$B7)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E7))*(EXACT('Asignacion'!$B$4:$B$34,$B7)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E7))*(EXACT('Asignacion'!$B$4:$B$34,$B7)),0),0))))))</f>
         <v/>
       </c>
       <c r="K7" s="3">
-        <f>IF(AND($A7=""),"",IF(EXACT($I7,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I7)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I7)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I7)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A7=""),"",IF(AND(NOT(EXACT($J7,"")),EXACT($J7,$I7)),1,0))</f>
         <v/>
       </c>
       <c r="L7" s="3">
-        <f>IF(AND($A7=""),"",IF(AND(NOT(EXACT($I7,"")),EXACT($K7,$J7)),1,0))</f>
+        <f>IF(AND($A7=""),"",MID(IF(AND(NOT(($B7="")),($E7="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M7" s="3">
-        <f>IF(AND($A7=""),"",MID(IF(AND(NOT(($B7="")),($E7="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N7" s="3">
         <f>IF(OR(AND(NOT(($B7="")),($E7=""))),2,0)</f>
         <v/>
       </c>
@@ -876,26 +854,22 @@
         <v/>
       </c>
       <c r="I8" s="3">
-        <f>IF(AND($A8=""),"",IF(OR(($E8=""),($B8="")),"",(IF(ISNUMBER($E8),IF($E8=0,"0",ROUND($E8,9-INT(LOG10(ABS($E8))))&amp;""),$E8&amp;"")&amp;"|"&amp;IF(ISNUMBER($B8),IF($B8=0,"0",ROUND($B8,9-INT(LOG10(ABS($B8))))&amp;""),$B8&amp;""))))</f>
+        <f>IF(AND($A8=""),"",(IF(ISNUMBER($B8),IF($B8=0,"0",ROUND($B8,9-INT(LOG10(ABS($B8))))&amp;""),$B8&amp;"")&amp;" "&amp;IF(ISNUMBER($C8),IF($C8=0,"0",ROUND($C8,9-INT(LOG10(ABS($C8))))&amp;""),$C8&amp;"")&amp;" "&amp;IF(ISNUMBER($D8),IF($D8=0,"0",ROUND($D8,9-INT(LOG10(ABS($D8))))&amp;""),$D8&amp;"")))</f>
         <v/>
       </c>
       <c r="J8" s="3">
-        <f>IF(AND($A8=""),"",(IF(ISNUMBER($B8),IF($B8=0,"0",ROUND($B8,9-INT(LOG10(ABS($B8))))&amp;""),$B8&amp;"")&amp;" "&amp;IF(ISNUMBER($C8),IF($C8=0,"0",ROUND($C8,9-INT(LOG10(ABS($C8))))&amp;""),$C8&amp;"")&amp;" "&amp;IF(ISNUMBER($D8),IF($D8=0,"0",ROUND($D8,9-INT(LOG10(ABS($D8))))&amp;""),$D8&amp;"")))</f>
+        <f>IF(AND($A8=""),"",IF(OR(($E8=""),($B8="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E8))*(EXACT('Asignacion'!$B$4:$B$34,$B8)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E8))*(EXACT('Asignacion'!$B$4:$B$34,$B8)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E8))*(EXACT('Asignacion'!$B$4:$B$34,$B8)),0),0))))))</f>
         <v/>
       </c>
       <c r="K8" s="3">
-        <f>IF(AND($A8=""),"",IF(EXACT($I8,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I8)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I8)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I8)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A8=""),"",IF(AND(NOT(EXACT($J8,"")),EXACT($J8,$I8)),1,0))</f>
         <v/>
       </c>
       <c r="L8" s="3">
-        <f>IF(AND($A8=""),"",IF(AND(NOT(EXACT($I8,"")),EXACT($K8,$J8)),1,0))</f>
+        <f>IF(AND($A8=""),"",MID(IF(AND(NOT(($B8="")),($E8="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M8" s="3">
-        <f>IF(AND($A8=""),"",MID(IF(AND(NOT(($B8="")),($E8="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N8" s="3">
         <f>IF(OR(AND(NOT(($B8="")),($E8=""))),2,0)</f>
         <v/>
       </c>
@@ -933,26 +907,22 @@
         <v/>
       </c>
       <c r="I9" s="3">
-        <f>IF(AND($A9=""),"",IF(OR(($E9=""),($B9="")),"",(IF(ISNUMBER($E9),IF($E9=0,"0",ROUND($E9,9-INT(LOG10(ABS($E9))))&amp;""),$E9&amp;"")&amp;"|"&amp;IF(ISNUMBER($B9),IF($B9=0,"0",ROUND($B9,9-INT(LOG10(ABS($B9))))&amp;""),$B9&amp;""))))</f>
+        <f>IF(AND($A9=""),"",(IF(ISNUMBER($B9),IF($B9=0,"0",ROUND($B9,9-INT(LOG10(ABS($B9))))&amp;""),$B9&amp;"")&amp;" "&amp;IF(ISNUMBER($C9),IF($C9=0,"0",ROUND($C9,9-INT(LOG10(ABS($C9))))&amp;""),$C9&amp;"")&amp;" "&amp;IF(ISNUMBER($D9),IF($D9=0,"0",ROUND($D9,9-INT(LOG10(ABS($D9))))&amp;""),$D9&amp;"")))</f>
         <v/>
       </c>
       <c r="J9" s="3">
-        <f>IF(AND($A9=""),"",(IF(ISNUMBER($B9),IF($B9=0,"0",ROUND($B9,9-INT(LOG10(ABS($B9))))&amp;""),$B9&amp;"")&amp;" "&amp;IF(ISNUMBER($C9),IF($C9=0,"0",ROUND($C9,9-INT(LOG10(ABS($C9))))&amp;""),$C9&amp;"")&amp;" "&amp;IF(ISNUMBER($D9),IF($D9=0,"0",ROUND($D9,9-INT(LOG10(ABS($D9))))&amp;""),$D9&amp;"")))</f>
+        <f>IF(AND($A9=""),"",IF(OR(($E9=""),($B9="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E9))*(EXACT('Asignacion'!$B$4:$B$34,$B9)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E9))*(EXACT('Asignacion'!$B$4:$B$34,$B9)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E9))*(EXACT('Asignacion'!$B$4:$B$34,$B9)),0),0))))))</f>
         <v/>
       </c>
       <c r="K9" s="3">
-        <f>IF(AND($A9=""),"",IF(EXACT($I9,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I9)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I9)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I9)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A9=""),"",IF(AND(NOT(EXACT($J9,"")),EXACT($J9,$I9)),1,0))</f>
         <v/>
       </c>
       <c r="L9" s="3">
-        <f>IF(AND($A9=""),"",IF(AND(NOT(EXACT($I9,"")),EXACT($K9,$J9)),1,0))</f>
+        <f>IF(AND($A9=""),"",MID(IF(AND(NOT(($B9="")),($E9="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M9" s="3">
-        <f>IF(AND($A9=""),"",MID(IF(AND(NOT(($B9="")),($E9="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N9" s="3">
         <f>IF(OR(AND(NOT(($B9="")),($E9=""))),2,0)</f>
         <v/>
       </c>
@@ -994,26 +964,22 @@
         <v/>
       </c>
       <c r="I10" s="3">
-        <f>IF(AND($A10=""),"",IF(OR(($E10=""),($B10="")),"",(IF(ISNUMBER($E10),IF($E10=0,"0",ROUND($E10,9-INT(LOG10(ABS($E10))))&amp;""),$E10&amp;"")&amp;"|"&amp;IF(ISNUMBER($B10),IF($B10=0,"0",ROUND($B10,9-INT(LOG10(ABS($B10))))&amp;""),$B10&amp;""))))</f>
+        <f>IF(AND($A10=""),"",(IF(ISNUMBER($B10),IF($B10=0,"0",ROUND($B10,9-INT(LOG10(ABS($B10))))&amp;""),$B10&amp;"")&amp;" "&amp;IF(ISNUMBER($C10),IF($C10=0,"0",ROUND($C10,9-INT(LOG10(ABS($C10))))&amp;""),$C10&amp;"")&amp;" "&amp;IF(ISNUMBER($D10),IF($D10=0,"0",ROUND($D10,9-INT(LOG10(ABS($D10))))&amp;""),$D10&amp;"")))</f>
         <v/>
       </c>
       <c r="J10" s="3">
-        <f>IF(AND($A10=""),"",(IF(ISNUMBER($B10),IF($B10=0,"0",ROUND($B10,9-INT(LOG10(ABS($B10))))&amp;""),$B10&amp;"")&amp;" "&amp;IF(ISNUMBER($C10),IF($C10=0,"0",ROUND($C10,9-INT(LOG10(ABS($C10))))&amp;""),$C10&amp;"")&amp;" "&amp;IF(ISNUMBER($D10),IF($D10=0,"0",ROUND($D10,9-INT(LOG10(ABS($D10))))&amp;""),$D10&amp;"")))</f>
+        <f>IF(AND($A10=""),"",IF(OR(($E10=""),($B10="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E10))*(EXACT('Asignacion'!$B$4:$B$34,$B10)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E10))*(EXACT('Asignacion'!$B$4:$B$34,$B10)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E10))*(EXACT('Asignacion'!$B$4:$B$34,$B10)),0),0))))))</f>
         <v/>
       </c>
       <c r="K10" s="3">
-        <f>IF(AND($A10=""),"",IF(EXACT($I10,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I10)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I10)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I10)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A10=""),"",IF(AND(NOT(EXACT($J10,"")),EXACT($J10,$I10)),1,0))</f>
         <v/>
       </c>
       <c r="L10" s="3">
-        <f>IF(AND($A10=""),"",IF(AND(NOT(EXACT($I10,"")),EXACT($K10,$J10)),1,0))</f>
+        <f>IF(AND($A10=""),"",MID(IF(AND(NOT(($B10="")),($E10="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M10" s="3">
-        <f>IF(AND($A10=""),"",MID(IF(AND(NOT(($B10="")),($E10="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N10" s="3">
         <f>IF(OR(AND(NOT(($B10="")),($E10=""))),2,0)</f>
         <v/>
       </c>
@@ -1051,26 +1017,22 @@
         <v/>
       </c>
       <c r="I11" s="3">
-        <f>IF(AND($A11=""),"",IF(OR(($E11=""),($B11="")),"",(IF(ISNUMBER($E11),IF($E11=0,"0",ROUND($E11,9-INT(LOG10(ABS($E11))))&amp;""),$E11&amp;"")&amp;"|"&amp;IF(ISNUMBER($B11),IF($B11=0,"0",ROUND($B11,9-INT(LOG10(ABS($B11))))&amp;""),$B11&amp;""))))</f>
+        <f>IF(AND($A11=""),"",(IF(ISNUMBER($B11),IF($B11=0,"0",ROUND($B11,9-INT(LOG10(ABS($B11))))&amp;""),$B11&amp;"")&amp;" "&amp;IF(ISNUMBER($C11),IF($C11=0,"0",ROUND($C11,9-INT(LOG10(ABS($C11))))&amp;""),$C11&amp;"")&amp;" "&amp;IF(ISNUMBER($D11),IF($D11=0,"0",ROUND($D11,9-INT(LOG10(ABS($D11))))&amp;""),$D11&amp;"")))</f>
         <v/>
       </c>
       <c r="J11" s="3">
-        <f>IF(AND($A11=""),"",(IF(ISNUMBER($B11),IF($B11=0,"0",ROUND($B11,9-INT(LOG10(ABS($B11))))&amp;""),$B11&amp;"")&amp;" "&amp;IF(ISNUMBER($C11),IF($C11=0,"0",ROUND($C11,9-INT(LOG10(ABS($C11))))&amp;""),$C11&amp;"")&amp;" "&amp;IF(ISNUMBER($D11),IF($D11=0,"0",ROUND($D11,9-INT(LOG10(ABS($D11))))&amp;""),$D11&amp;"")))</f>
+        <f>IF(AND($A11=""),"",IF(OR(($E11=""),($B11="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E11))*(EXACT('Asignacion'!$B$4:$B$34,$B11)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E11))*(EXACT('Asignacion'!$B$4:$B$34,$B11)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E11))*(EXACT('Asignacion'!$B$4:$B$34,$B11)),0),0))))))</f>
         <v/>
       </c>
       <c r="K11" s="3">
-        <f>IF(AND($A11=""),"",IF(EXACT($I11,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I11)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I11)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I11)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A11=""),"",IF(AND(NOT(EXACT($J11,"")),EXACT($J11,$I11)),1,0))</f>
         <v/>
       </c>
       <c r="L11" s="3">
-        <f>IF(AND($A11=""),"",IF(AND(NOT(EXACT($I11,"")),EXACT($K11,$J11)),1,0))</f>
+        <f>IF(AND($A11=""),"",MID(IF(AND(NOT(($B11="")),($E11="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M11" s="3">
-        <f>IF(AND($A11=""),"",MID(IF(AND(NOT(($B11="")),($E11="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N11" s="3">
         <f>IF(OR(AND(NOT(($B11="")),($E11=""))),2,0)</f>
         <v/>
       </c>
@@ -1108,26 +1070,22 @@
         <v/>
       </c>
       <c r="I12" s="3">
-        <f>IF(AND($A12=""),"",IF(OR(($E12=""),($B12="")),"",(IF(ISNUMBER($E12),IF($E12=0,"0",ROUND($E12,9-INT(LOG10(ABS($E12))))&amp;""),$E12&amp;"")&amp;"|"&amp;IF(ISNUMBER($B12),IF($B12=0,"0",ROUND($B12,9-INT(LOG10(ABS($B12))))&amp;""),$B12&amp;""))))</f>
+        <f>IF(AND($A12=""),"",(IF(ISNUMBER($B12),IF($B12=0,"0",ROUND($B12,9-INT(LOG10(ABS($B12))))&amp;""),$B12&amp;"")&amp;" "&amp;IF(ISNUMBER($C12),IF($C12=0,"0",ROUND($C12,9-INT(LOG10(ABS($C12))))&amp;""),$C12&amp;"")&amp;" "&amp;IF(ISNUMBER($D12),IF($D12=0,"0",ROUND($D12,9-INT(LOG10(ABS($D12))))&amp;""),$D12&amp;"")))</f>
         <v/>
       </c>
       <c r="J12" s="3">
-        <f>IF(AND($A12=""),"",(IF(ISNUMBER($B12),IF($B12=0,"0",ROUND($B12,9-INT(LOG10(ABS($B12))))&amp;""),$B12&amp;"")&amp;" "&amp;IF(ISNUMBER($C12),IF($C12=0,"0",ROUND($C12,9-INT(LOG10(ABS($C12))))&amp;""),$C12&amp;"")&amp;" "&amp;IF(ISNUMBER($D12),IF($D12=0,"0",ROUND($D12,9-INT(LOG10(ABS($D12))))&amp;""),$D12&amp;"")))</f>
+        <f>IF(AND($A12=""),"",IF(OR(($E12=""),($B12="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E12))*(EXACT('Asignacion'!$B$4:$B$34,$B12)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E12))*(EXACT('Asignacion'!$B$4:$B$34,$B12)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E12))*(EXACT('Asignacion'!$B$4:$B$34,$B12)),0),0))))))</f>
         <v/>
       </c>
       <c r="K12" s="3">
-        <f>IF(AND($A12=""),"",IF(EXACT($I12,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I12)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I12)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I12)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A12=""),"",IF(AND(NOT(EXACT($J12,"")),EXACT($J12,$I12)),1,0))</f>
         <v/>
       </c>
       <c r="L12" s="3">
-        <f>IF(AND($A12=""),"",IF(AND(NOT(EXACT($I12,"")),EXACT($K12,$J12)),1,0))</f>
+        <f>IF(AND($A12=""),"",MID(IF(AND(NOT(($B12="")),($E12="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M12" s="3">
-        <f>IF(AND($A12=""),"",MID(IF(AND(NOT(($B12="")),($E12="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N12" s="3">
         <f>IF(OR(AND(NOT(($B12="")),($E12=""))),2,0)</f>
         <v/>
       </c>
@@ -1153,26 +1111,22 @@
         <v/>
       </c>
       <c r="I13" s="3">
-        <f>IF(AND($A13=""),"",IF(OR(($E13=""),($B13="")),"",(IF(ISNUMBER($E13),IF($E13=0,"0",ROUND($E13,9-INT(LOG10(ABS($E13))))&amp;""),$E13&amp;"")&amp;"|"&amp;IF(ISNUMBER($B13),IF($B13=0,"0",ROUND($B13,9-INT(LOG10(ABS($B13))))&amp;""),$B13&amp;""))))</f>
+        <f>IF(AND($A13=""),"",(IF(ISNUMBER($B13),IF($B13=0,"0",ROUND($B13,9-INT(LOG10(ABS($B13))))&amp;""),$B13&amp;"")&amp;" "&amp;IF(ISNUMBER($C13),IF($C13=0,"0",ROUND($C13,9-INT(LOG10(ABS($C13))))&amp;""),$C13&amp;"")&amp;" "&amp;IF(ISNUMBER($D13),IF($D13=0,"0",ROUND($D13,9-INT(LOG10(ABS($D13))))&amp;""),$D13&amp;"")))</f>
         <v/>
       </c>
       <c r="J13" s="3">
-        <f>IF(AND($A13=""),"",(IF(ISNUMBER($B13),IF($B13=0,"0",ROUND($B13,9-INT(LOG10(ABS($B13))))&amp;""),$B13&amp;"")&amp;" "&amp;IF(ISNUMBER($C13),IF($C13=0,"0",ROUND($C13,9-INT(LOG10(ABS($C13))))&amp;""),$C13&amp;"")&amp;" "&amp;IF(ISNUMBER($D13),IF($D13=0,"0",ROUND($D13,9-INT(LOG10(ABS($D13))))&amp;""),$D13&amp;"")))</f>
+        <f>IF(AND($A13=""),"",IF(OR(($E13=""),($B13="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E13))*(EXACT('Asignacion'!$B$4:$B$34,$B13)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E13))*(EXACT('Asignacion'!$B$4:$B$34,$B13)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E13))*(EXACT('Asignacion'!$B$4:$B$34,$B13)),0),0))))))</f>
         <v/>
       </c>
       <c r="K13" s="3">
-        <f>IF(AND($A13=""),"",IF(EXACT($I13,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I13)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I13)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I13)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A13=""),"",IF(AND(NOT(EXACT($J13,"")),EXACT($J13,$I13)),1,0))</f>
         <v/>
       </c>
       <c r="L13" s="3">
-        <f>IF(AND($A13=""),"",IF(AND(NOT(EXACT($I13,"")),EXACT($K13,$J13)),1,0))</f>
+        <f>IF(AND($A13=""),"",MID(IF(AND(NOT(($B13="")),($E13="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M13" s="3">
-        <f>IF(AND($A13=""),"",MID(IF(AND(NOT(($B13="")),($E13="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N13" s="3">
         <f>IF(OR(AND(NOT(($B13="")),($E13=""))),2,0)</f>
         <v/>
       </c>
@@ -1198,26 +1152,22 @@
         <v/>
       </c>
       <c r="I14" s="3">
-        <f>IF(AND($A14=""),"",IF(OR(($E14=""),($B14="")),"",(IF(ISNUMBER($E14),IF($E14=0,"0",ROUND($E14,9-INT(LOG10(ABS($E14))))&amp;""),$E14&amp;"")&amp;"|"&amp;IF(ISNUMBER($B14),IF($B14=0,"0",ROUND($B14,9-INT(LOG10(ABS($B14))))&amp;""),$B14&amp;""))))</f>
+        <f>IF(AND($A14=""),"",(IF(ISNUMBER($B14),IF($B14=0,"0",ROUND($B14,9-INT(LOG10(ABS($B14))))&amp;""),$B14&amp;"")&amp;" "&amp;IF(ISNUMBER($C14),IF($C14=0,"0",ROUND($C14,9-INT(LOG10(ABS($C14))))&amp;""),$C14&amp;"")&amp;" "&amp;IF(ISNUMBER($D14),IF($D14=0,"0",ROUND($D14,9-INT(LOG10(ABS($D14))))&amp;""),$D14&amp;"")))</f>
         <v/>
       </c>
       <c r="J14" s="3">
-        <f>IF(AND($A14=""),"",(IF(ISNUMBER($B14),IF($B14=0,"0",ROUND($B14,9-INT(LOG10(ABS($B14))))&amp;""),$B14&amp;"")&amp;" "&amp;IF(ISNUMBER($C14),IF($C14=0,"0",ROUND($C14,9-INT(LOG10(ABS($C14))))&amp;""),$C14&amp;"")&amp;" "&amp;IF(ISNUMBER($D14),IF($D14=0,"0",ROUND($D14,9-INT(LOG10(ABS($D14))))&amp;""),$D14&amp;"")))</f>
+        <f>IF(AND($A14=""),"",IF(OR(($E14=""),($B14="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E14))*(EXACT('Asignacion'!$B$4:$B$34,$B14)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E14))*(EXACT('Asignacion'!$B$4:$B$34,$B14)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E14))*(EXACT('Asignacion'!$B$4:$B$34,$B14)),0),0))))))</f>
         <v/>
       </c>
       <c r="K14" s="3">
-        <f>IF(AND($A14=""),"",IF(EXACT($I14,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I14)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I14)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I14)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A14=""),"",IF(AND(NOT(EXACT($J14,"")),EXACT($J14,$I14)),1,0))</f>
         <v/>
       </c>
       <c r="L14" s="3">
-        <f>IF(AND($A14=""),"",IF(AND(NOT(EXACT($I14,"")),EXACT($K14,$J14)),1,0))</f>
+        <f>IF(AND($A14=""),"",MID(IF(AND(NOT(($B14="")),($E14="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M14" s="3">
-        <f>IF(AND($A14=""),"",MID(IF(AND(NOT(($B14="")),($E14="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N14" s="3">
         <f>IF(OR(AND(NOT(($B14="")),($E14=""))),2,0)</f>
         <v/>
       </c>
@@ -1241,26 +1191,22 @@
         <v/>
       </c>
       <c r="I15" s="3">
-        <f>IF(AND($A15=""),"",IF(OR(($E15=""),($B15="")),"",(IF(ISNUMBER($E15),IF($E15=0,"0",ROUND($E15,9-INT(LOG10(ABS($E15))))&amp;""),$E15&amp;"")&amp;"|"&amp;IF(ISNUMBER($B15),IF($B15=0,"0",ROUND($B15,9-INT(LOG10(ABS($B15))))&amp;""),$B15&amp;""))))</f>
+        <f>IF(AND($A15=""),"",(IF(ISNUMBER($B15),IF($B15=0,"0",ROUND($B15,9-INT(LOG10(ABS($B15))))&amp;""),$B15&amp;"")&amp;" "&amp;IF(ISNUMBER($C15),IF($C15=0,"0",ROUND($C15,9-INT(LOG10(ABS($C15))))&amp;""),$C15&amp;"")&amp;" "&amp;IF(ISNUMBER($D15),IF($D15=0,"0",ROUND($D15,9-INT(LOG10(ABS($D15))))&amp;""),$D15&amp;"")))</f>
         <v/>
       </c>
       <c r="J15" s="3">
-        <f>IF(AND($A15=""),"",(IF(ISNUMBER($B15),IF($B15=0,"0",ROUND($B15,9-INT(LOG10(ABS($B15))))&amp;""),$B15&amp;"")&amp;" "&amp;IF(ISNUMBER($C15),IF($C15=0,"0",ROUND($C15,9-INT(LOG10(ABS($C15))))&amp;""),$C15&amp;"")&amp;" "&amp;IF(ISNUMBER($D15),IF($D15=0,"0",ROUND($D15,9-INT(LOG10(ABS($D15))))&amp;""),$D15&amp;"")))</f>
+        <f>IF(AND($A15=""),"",IF(OR(($E15=""),($B15="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E15))*(EXACT('Asignacion'!$B$4:$B$34,$B15)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E15))*(EXACT('Asignacion'!$B$4:$B$34,$B15)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E15))*(EXACT('Asignacion'!$B$4:$B$34,$B15)),0),0))))))</f>
         <v/>
       </c>
       <c r="K15" s="3">
-        <f>IF(AND($A15=""),"",IF(EXACT($I15,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I15)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I15)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I15)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A15=""),"",IF(AND(NOT(EXACT($J15,"")),EXACT($J15,$I15)),1,0))</f>
         <v/>
       </c>
       <c r="L15" s="3">
-        <f>IF(AND($A15=""),"",IF(AND(NOT(EXACT($I15,"")),EXACT($K15,$J15)),1,0))</f>
+        <f>IF(AND($A15=""),"",MID(IF(AND(NOT(($B15="")),($E15="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M15" s="3">
-        <f>IF(AND($A15=""),"",MID(IF(AND(NOT(($B15="")),($E15="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N15" s="3">
         <f>IF(OR(AND(NOT(($B15="")),($E15=""))),2,0)</f>
         <v/>
       </c>
@@ -1284,26 +1230,22 @@
         <v/>
       </c>
       <c r="I16" s="3">
-        <f>IF(AND($A16=""),"",IF(OR(($E16=""),($B16="")),"",(IF(ISNUMBER($E16),IF($E16=0,"0",ROUND($E16,9-INT(LOG10(ABS($E16))))&amp;""),$E16&amp;"")&amp;"|"&amp;IF(ISNUMBER($B16),IF($B16=0,"0",ROUND($B16,9-INT(LOG10(ABS($B16))))&amp;""),$B16&amp;""))))</f>
+        <f>IF(AND($A16=""),"",(IF(ISNUMBER($B16),IF($B16=0,"0",ROUND($B16,9-INT(LOG10(ABS($B16))))&amp;""),$B16&amp;"")&amp;" "&amp;IF(ISNUMBER($C16),IF($C16=0,"0",ROUND($C16,9-INT(LOG10(ABS($C16))))&amp;""),$C16&amp;"")&amp;" "&amp;IF(ISNUMBER($D16),IF($D16=0,"0",ROUND($D16,9-INT(LOG10(ABS($D16))))&amp;""),$D16&amp;"")))</f>
         <v/>
       </c>
       <c r="J16" s="3">
-        <f>IF(AND($A16=""),"",(IF(ISNUMBER($B16),IF($B16=0,"0",ROUND($B16,9-INT(LOG10(ABS($B16))))&amp;""),$B16&amp;"")&amp;" "&amp;IF(ISNUMBER($C16),IF($C16=0,"0",ROUND($C16,9-INT(LOG10(ABS($C16))))&amp;""),$C16&amp;"")&amp;" "&amp;IF(ISNUMBER($D16),IF($D16=0,"0",ROUND($D16,9-INT(LOG10(ABS($D16))))&amp;""),$D16&amp;"")))</f>
+        <f>IF(AND($A16=""),"",IF(OR(($E16=""),($B16="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E16))*(EXACT('Asignacion'!$B$4:$B$34,$B16)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E16))*(EXACT('Asignacion'!$B$4:$B$34,$B16)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E16))*(EXACT('Asignacion'!$B$4:$B$34,$B16)),0),0))))))</f>
         <v/>
       </c>
       <c r="K16" s="3">
-        <f>IF(AND($A16=""),"",IF(EXACT($I16,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I16)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I16)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I16)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A16=""),"",IF(AND(NOT(EXACT($J16,"")),EXACT($J16,$I16)),1,0))</f>
         <v/>
       </c>
       <c r="L16" s="3">
-        <f>IF(AND($A16=""),"",IF(AND(NOT(EXACT($I16,"")),EXACT($K16,$J16)),1,0))</f>
+        <f>IF(AND($A16=""),"",MID(IF(AND(NOT(($B16="")),($E16="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M16" s="3">
-        <f>IF(AND($A16=""),"",MID(IF(AND(NOT(($B16="")),($E16="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N16" s="3">
         <f>IF(OR(AND(NOT(($B16="")),($E16=""))),2,0)</f>
         <v/>
       </c>
@@ -1327,26 +1269,22 @@
         <v/>
       </c>
       <c r="I17" s="3">
-        <f>IF(AND($A17=""),"",IF(OR(($E17=""),($B17="")),"",(IF(ISNUMBER($E17),IF($E17=0,"0",ROUND($E17,9-INT(LOG10(ABS($E17))))&amp;""),$E17&amp;"")&amp;"|"&amp;IF(ISNUMBER($B17),IF($B17=0,"0",ROUND($B17,9-INT(LOG10(ABS($B17))))&amp;""),$B17&amp;""))))</f>
+        <f>IF(AND($A17=""),"",(IF(ISNUMBER($B17),IF($B17=0,"0",ROUND($B17,9-INT(LOG10(ABS($B17))))&amp;""),$B17&amp;"")&amp;" "&amp;IF(ISNUMBER($C17),IF($C17=0,"0",ROUND($C17,9-INT(LOG10(ABS($C17))))&amp;""),$C17&amp;"")&amp;" "&amp;IF(ISNUMBER($D17),IF($D17=0,"0",ROUND($D17,9-INT(LOG10(ABS($D17))))&amp;""),$D17&amp;"")))</f>
         <v/>
       </c>
       <c r="J17" s="3">
-        <f>IF(AND($A17=""),"",(IF(ISNUMBER($B17),IF($B17=0,"0",ROUND($B17,9-INT(LOG10(ABS($B17))))&amp;""),$B17&amp;"")&amp;" "&amp;IF(ISNUMBER($C17),IF($C17=0,"0",ROUND($C17,9-INT(LOG10(ABS($C17))))&amp;""),$C17&amp;"")&amp;" "&amp;IF(ISNUMBER($D17),IF($D17=0,"0",ROUND($D17,9-INT(LOG10(ABS($D17))))&amp;""),$D17&amp;"")))</f>
+        <f>IF(AND($A17=""),"",IF(OR(($E17=""),($B17="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E17))*(EXACT('Asignacion'!$B$4:$B$34,$B17)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E17))*(EXACT('Asignacion'!$B$4:$B$34,$B17)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E17))*(EXACT('Asignacion'!$B$4:$B$34,$B17)),0),0))))))</f>
         <v/>
       </c>
       <c r="K17" s="3">
-        <f>IF(AND($A17=""),"",IF(EXACT($I17,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I17)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I17)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I17)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A17=""),"",IF(AND(NOT(EXACT($J17,"")),EXACT($J17,$I17)),1,0))</f>
         <v/>
       </c>
       <c r="L17" s="3">
-        <f>IF(AND($A17=""),"",IF(AND(NOT(EXACT($I17,"")),EXACT($K17,$J17)),1,0))</f>
+        <f>IF(AND($A17=""),"",MID(IF(AND(NOT(($B17="")),($E17="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M17" s="3">
-        <f>IF(AND($A17=""),"",MID(IF(AND(NOT(($B17="")),($E17="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N17" s="3">
         <f>IF(OR(AND(NOT(($B17="")),($E17=""))),2,0)</f>
         <v/>
       </c>
@@ -1370,26 +1308,22 @@
         <v/>
       </c>
       <c r="I18" s="3">
-        <f>IF(AND($A18=""),"",IF(OR(($E18=""),($B18="")),"",(IF(ISNUMBER($E18),IF($E18=0,"0",ROUND($E18,9-INT(LOG10(ABS($E18))))&amp;""),$E18&amp;"")&amp;"|"&amp;IF(ISNUMBER($B18),IF($B18=0,"0",ROUND($B18,9-INT(LOG10(ABS($B18))))&amp;""),$B18&amp;""))))</f>
+        <f>IF(AND($A18=""),"",(IF(ISNUMBER($B18),IF($B18=0,"0",ROUND($B18,9-INT(LOG10(ABS($B18))))&amp;""),$B18&amp;"")&amp;" "&amp;IF(ISNUMBER($C18),IF($C18=0,"0",ROUND($C18,9-INT(LOG10(ABS($C18))))&amp;""),$C18&amp;"")&amp;" "&amp;IF(ISNUMBER($D18),IF($D18=0,"0",ROUND($D18,9-INT(LOG10(ABS($D18))))&amp;""),$D18&amp;"")))</f>
         <v/>
       </c>
       <c r="J18" s="3">
-        <f>IF(AND($A18=""),"",(IF(ISNUMBER($B18),IF($B18=0,"0",ROUND($B18,9-INT(LOG10(ABS($B18))))&amp;""),$B18&amp;"")&amp;" "&amp;IF(ISNUMBER($C18),IF($C18=0,"0",ROUND($C18,9-INT(LOG10(ABS($C18))))&amp;""),$C18&amp;"")&amp;" "&amp;IF(ISNUMBER($D18),IF($D18=0,"0",ROUND($D18,9-INT(LOG10(ABS($D18))))&amp;""),$D18&amp;"")))</f>
+        <f>IF(AND($A18=""),"",IF(OR(($E18=""),($B18="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E18))*(EXACT('Asignacion'!$B$4:$B$34,$B18)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E18))*(EXACT('Asignacion'!$B$4:$B$34,$B18)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E18))*(EXACT('Asignacion'!$B$4:$B$34,$B18)),0),0))))))</f>
         <v/>
       </c>
       <c r="K18" s="3">
-        <f>IF(AND($A18=""),"",IF(EXACT($I18,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I18)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I18)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I18)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A18=""),"",IF(AND(NOT(EXACT($J18,"")),EXACT($J18,$I18)),1,0))</f>
         <v/>
       </c>
       <c r="L18" s="3">
-        <f>IF(AND($A18=""),"",IF(AND(NOT(EXACT($I18,"")),EXACT($K18,$J18)),1,0))</f>
+        <f>IF(AND($A18=""),"",MID(IF(AND(NOT(($B18="")),($E18="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M18" s="3">
-        <f>IF(AND($A18=""),"",MID(IF(AND(NOT(($B18="")),($E18="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N18" s="3">
         <f>IF(OR(AND(NOT(($B18="")),($E18=""))),2,0)</f>
         <v/>
       </c>
@@ -1413,26 +1347,22 @@
         <v/>
       </c>
       <c r="I19" s="3">
-        <f>IF(AND($A19=""),"",IF(OR(($E19=""),($B19="")),"",(IF(ISNUMBER($E19),IF($E19=0,"0",ROUND($E19,9-INT(LOG10(ABS($E19))))&amp;""),$E19&amp;"")&amp;"|"&amp;IF(ISNUMBER($B19),IF($B19=0,"0",ROUND($B19,9-INT(LOG10(ABS($B19))))&amp;""),$B19&amp;""))))</f>
+        <f>IF(AND($A19=""),"",(IF(ISNUMBER($B19),IF($B19=0,"0",ROUND($B19,9-INT(LOG10(ABS($B19))))&amp;""),$B19&amp;"")&amp;" "&amp;IF(ISNUMBER($C19),IF($C19=0,"0",ROUND($C19,9-INT(LOG10(ABS($C19))))&amp;""),$C19&amp;"")&amp;" "&amp;IF(ISNUMBER($D19),IF($D19=0,"0",ROUND($D19,9-INT(LOG10(ABS($D19))))&amp;""),$D19&amp;"")))</f>
         <v/>
       </c>
       <c r="J19" s="3">
-        <f>IF(AND($A19=""),"",(IF(ISNUMBER($B19),IF($B19=0,"0",ROUND($B19,9-INT(LOG10(ABS($B19))))&amp;""),$B19&amp;"")&amp;" "&amp;IF(ISNUMBER($C19),IF($C19=0,"0",ROUND($C19,9-INT(LOG10(ABS($C19))))&amp;""),$C19&amp;"")&amp;" "&amp;IF(ISNUMBER($D19),IF($D19=0,"0",ROUND($D19,9-INT(LOG10(ABS($D19))))&amp;""),$D19&amp;"")))</f>
+        <f>IF(AND($A19=""),"",IF(OR(($E19=""),($B19="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E19))*(EXACT('Asignacion'!$B$4:$B$34,$B19)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E19))*(EXACT('Asignacion'!$B$4:$B$34,$B19)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E19))*(EXACT('Asignacion'!$B$4:$B$34,$B19)),0),0))))))</f>
         <v/>
       </c>
       <c r="K19" s="3">
-        <f>IF(AND($A19=""),"",IF(EXACT($I19,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I19)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I19)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I19)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A19=""),"",IF(AND(NOT(EXACT($J19,"")),EXACT($J19,$I19)),1,0))</f>
         <v/>
       </c>
       <c r="L19" s="3">
-        <f>IF(AND($A19=""),"",IF(AND(NOT(EXACT($I19,"")),EXACT($K19,$J19)),1,0))</f>
+        <f>IF(AND($A19=""),"",MID(IF(AND(NOT(($B19="")),($E19="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M19" s="3">
-        <f>IF(AND($A19=""),"",MID(IF(AND(NOT(($B19="")),($E19="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N19" s="3">
         <f>IF(OR(AND(NOT(($B19="")),($E19=""))),2,0)</f>
         <v/>
       </c>
@@ -1456,26 +1386,22 @@
         <v/>
       </c>
       <c r="I20" s="3">
-        <f>IF(AND($A20=""),"",IF(OR(($E20=""),($B20="")),"",(IF(ISNUMBER($E20),IF($E20=0,"0",ROUND($E20,9-INT(LOG10(ABS($E20))))&amp;""),$E20&amp;"")&amp;"|"&amp;IF(ISNUMBER($B20),IF($B20=0,"0",ROUND($B20,9-INT(LOG10(ABS($B20))))&amp;""),$B20&amp;""))))</f>
+        <f>IF(AND($A20=""),"",(IF(ISNUMBER($B20),IF($B20=0,"0",ROUND($B20,9-INT(LOG10(ABS($B20))))&amp;""),$B20&amp;"")&amp;" "&amp;IF(ISNUMBER($C20),IF($C20=0,"0",ROUND($C20,9-INT(LOG10(ABS($C20))))&amp;""),$C20&amp;"")&amp;" "&amp;IF(ISNUMBER($D20),IF($D20=0,"0",ROUND($D20,9-INT(LOG10(ABS($D20))))&amp;""),$D20&amp;"")))</f>
         <v/>
       </c>
       <c r="J20" s="3">
-        <f>IF(AND($A20=""),"",(IF(ISNUMBER($B20),IF($B20=0,"0",ROUND($B20,9-INT(LOG10(ABS($B20))))&amp;""),$B20&amp;"")&amp;" "&amp;IF(ISNUMBER($C20),IF($C20=0,"0",ROUND($C20,9-INT(LOG10(ABS($C20))))&amp;""),$C20&amp;"")&amp;" "&amp;IF(ISNUMBER($D20),IF($D20=0,"0",ROUND($D20,9-INT(LOG10(ABS($D20))))&amp;""),$D20&amp;"")))</f>
+        <f>IF(AND($A20=""),"",IF(OR(($E20=""),($B20="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E20))*(EXACT('Asignacion'!$B$4:$B$34,$B20)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E20))*(EXACT('Asignacion'!$B$4:$B$34,$B20)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E20))*(EXACT('Asignacion'!$B$4:$B$34,$B20)),0),0))))))</f>
         <v/>
       </c>
       <c r="K20" s="3">
-        <f>IF(AND($A20=""),"",IF(EXACT($I20,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I20)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I20)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I20)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A20=""),"",IF(AND(NOT(EXACT($J20,"")),EXACT($J20,$I20)),1,0))</f>
         <v/>
       </c>
       <c r="L20" s="3">
-        <f>IF(AND($A20=""),"",IF(AND(NOT(EXACT($I20,"")),EXACT($K20,$J20)),1,0))</f>
+        <f>IF(AND($A20=""),"",MID(IF(AND(NOT(($B20="")),($E20="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M20" s="3">
-        <f>IF(AND($A20=""),"",MID(IF(AND(NOT(($B20="")),($E20="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N20" s="3">
         <f>IF(OR(AND(NOT(($B20="")),($E20=""))),2,0)</f>
         <v/>
       </c>
@@ -1499,26 +1425,22 @@
         <v/>
       </c>
       <c r="I21" s="3">
-        <f>IF(AND($A21=""),"",IF(OR(($E21=""),($B21="")),"",(IF(ISNUMBER($E21),IF($E21=0,"0",ROUND($E21,9-INT(LOG10(ABS($E21))))&amp;""),$E21&amp;"")&amp;"|"&amp;IF(ISNUMBER($B21),IF($B21=0,"0",ROUND($B21,9-INT(LOG10(ABS($B21))))&amp;""),$B21&amp;""))))</f>
+        <f>IF(AND($A21=""),"",(IF(ISNUMBER($B21),IF($B21=0,"0",ROUND($B21,9-INT(LOG10(ABS($B21))))&amp;""),$B21&amp;"")&amp;" "&amp;IF(ISNUMBER($C21),IF($C21=0,"0",ROUND($C21,9-INT(LOG10(ABS($C21))))&amp;""),$C21&amp;"")&amp;" "&amp;IF(ISNUMBER($D21),IF($D21=0,"0",ROUND($D21,9-INT(LOG10(ABS($D21))))&amp;""),$D21&amp;"")))</f>
         <v/>
       </c>
       <c r="J21" s="3">
-        <f>IF(AND($A21=""),"",(IF(ISNUMBER($B21),IF($B21=0,"0",ROUND($B21,9-INT(LOG10(ABS($B21))))&amp;""),$B21&amp;"")&amp;" "&amp;IF(ISNUMBER($C21),IF($C21=0,"0",ROUND($C21,9-INT(LOG10(ABS($C21))))&amp;""),$C21&amp;"")&amp;" "&amp;IF(ISNUMBER($D21),IF($D21=0,"0",ROUND($D21,9-INT(LOG10(ABS($D21))))&amp;""),$D21&amp;"")))</f>
+        <f>IF(AND($A21=""),"",IF(OR(($E21=""),($B21="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E21))*(EXACT('Asignacion'!$B$4:$B$34,$B21)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E21))*(EXACT('Asignacion'!$B$4:$B$34,$B21)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E21))*(EXACT('Asignacion'!$B$4:$B$34,$B21)),0),0))))))</f>
         <v/>
       </c>
       <c r="K21" s="3">
-        <f>IF(AND($A21=""),"",IF(EXACT($I21,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I21)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I21)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I21)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A21=""),"",IF(AND(NOT(EXACT($J21,"")),EXACT($J21,$I21)),1,0))</f>
         <v/>
       </c>
       <c r="L21" s="3">
-        <f>IF(AND($A21=""),"",IF(AND(NOT(EXACT($I21,"")),EXACT($K21,$J21)),1,0))</f>
+        <f>IF(AND($A21=""),"",MID(IF(AND(NOT(($B21="")),($E21="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M21" s="3">
-        <f>IF(AND($A21=""),"",MID(IF(AND(NOT(($B21="")),($E21="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N21" s="3">
         <f>IF(OR(AND(NOT(($B21="")),($E21=""))),2,0)</f>
         <v/>
       </c>
@@ -1542,26 +1464,22 @@
         <v/>
       </c>
       <c r="I22" s="3">
-        <f>IF(AND($A22=""),"",IF(OR(($E22=""),($B22="")),"",(IF(ISNUMBER($E22),IF($E22=0,"0",ROUND($E22,9-INT(LOG10(ABS($E22))))&amp;""),$E22&amp;"")&amp;"|"&amp;IF(ISNUMBER($B22),IF($B22=0,"0",ROUND($B22,9-INT(LOG10(ABS($B22))))&amp;""),$B22&amp;""))))</f>
+        <f>IF(AND($A22=""),"",(IF(ISNUMBER($B22),IF($B22=0,"0",ROUND($B22,9-INT(LOG10(ABS($B22))))&amp;""),$B22&amp;"")&amp;" "&amp;IF(ISNUMBER($C22),IF($C22=0,"0",ROUND($C22,9-INT(LOG10(ABS($C22))))&amp;""),$C22&amp;"")&amp;" "&amp;IF(ISNUMBER($D22),IF($D22=0,"0",ROUND($D22,9-INT(LOG10(ABS($D22))))&amp;""),$D22&amp;"")))</f>
         <v/>
       </c>
       <c r="J22" s="3">
-        <f>IF(AND($A22=""),"",(IF(ISNUMBER($B22),IF($B22=0,"0",ROUND($B22,9-INT(LOG10(ABS($B22))))&amp;""),$B22&amp;"")&amp;" "&amp;IF(ISNUMBER($C22),IF($C22=0,"0",ROUND($C22,9-INT(LOG10(ABS($C22))))&amp;""),$C22&amp;"")&amp;" "&amp;IF(ISNUMBER($D22),IF($D22=0,"0",ROUND($D22,9-INT(LOG10(ABS($D22))))&amp;""),$D22&amp;"")))</f>
+        <f>IF(AND($A22=""),"",IF(OR(($E22=""),($B22="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E22))*(EXACT('Asignacion'!$B$4:$B$34,$B22)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E22))*(EXACT('Asignacion'!$B$4:$B$34,$B22)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E22))*(EXACT('Asignacion'!$B$4:$B$34,$B22)),0),0))))))</f>
         <v/>
       </c>
       <c r="K22" s="3">
-        <f>IF(AND($A22=""),"",IF(EXACT($I22,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I22)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I22)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I22)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A22=""),"",IF(AND(NOT(EXACT($J22,"")),EXACT($J22,$I22)),1,0))</f>
         <v/>
       </c>
       <c r="L22" s="3">
-        <f>IF(AND($A22=""),"",IF(AND(NOT(EXACT($I22,"")),EXACT($K22,$J22)),1,0))</f>
+        <f>IF(AND($A22=""),"",MID(IF(AND(NOT(($B22="")),($E22="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M22" s="3">
-        <f>IF(AND($A22=""),"",MID(IF(AND(NOT(($B22="")),($E22="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N22" s="3">
         <f>IF(OR(AND(NOT(($B22="")),($E22=""))),2,0)</f>
         <v/>
       </c>
@@ -1585,26 +1503,22 @@
         <v/>
       </c>
       <c r="I23" s="3">
-        <f>IF(AND($A23=""),"",IF(OR(($E23=""),($B23="")),"",(IF(ISNUMBER($E23),IF($E23=0,"0",ROUND($E23,9-INT(LOG10(ABS($E23))))&amp;""),$E23&amp;"")&amp;"|"&amp;IF(ISNUMBER($B23),IF($B23=0,"0",ROUND($B23,9-INT(LOG10(ABS($B23))))&amp;""),$B23&amp;""))))</f>
+        <f>IF(AND($A23=""),"",(IF(ISNUMBER($B23),IF($B23=0,"0",ROUND($B23,9-INT(LOG10(ABS($B23))))&amp;""),$B23&amp;"")&amp;" "&amp;IF(ISNUMBER($C23),IF($C23=0,"0",ROUND($C23,9-INT(LOG10(ABS($C23))))&amp;""),$C23&amp;"")&amp;" "&amp;IF(ISNUMBER($D23),IF($D23=0,"0",ROUND($D23,9-INT(LOG10(ABS($D23))))&amp;""),$D23&amp;"")))</f>
         <v/>
       </c>
       <c r="J23" s="3">
-        <f>IF(AND($A23=""),"",(IF(ISNUMBER($B23),IF($B23=0,"0",ROUND($B23,9-INT(LOG10(ABS($B23))))&amp;""),$B23&amp;"")&amp;" "&amp;IF(ISNUMBER($C23),IF($C23=0,"0",ROUND($C23,9-INT(LOG10(ABS($C23))))&amp;""),$C23&amp;"")&amp;" "&amp;IF(ISNUMBER($D23),IF($D23=0,"0",ROUND($D23,9-INT(LOG10(ABS($D23))))&amp;""),$D23&amp;"")))</f>
+        <f>IF(AND($A23=""),"",IF(OR(($E23=""),($B23="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E23))*(EXACT('Asignacion'!$B$4:$B$34,$B23)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E23))*(EXACT('Asignacion'!$B$4:$B$34,$B23)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E23))*(EXACT('Asignacion'!$B$4:$B$34,$B23)),0),0))))))</f>
         <v/>
       </c>
       <c r="K23" s="3">
-        <f>IF(AND($A23=""),"",IF(EXACT($I23,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I23)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I23)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I23)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A23=""),"",IF(AND(NOT(EXACT($J23,"")),EXACT($J23,$I23)),1,0))</f>
         <v/>
       </c>
       <c r="L23" s="3">
-        <f>IF(AND($A23=""),"",IF(AND(NOT(EXACT($I23,"")),EXACT($K23,$J23)),1,0))</f>
+        <f>IF(AND($A23=""),"",MID(IF(AND(NOT(($B23="")),($E23="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M23" s="3">
-        <f>IF(AND($A23=""),"",MID(IF(AND(NOT(($B23="")),($E23="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N23" s="3">
         <f>IF(OR(AND(NOT(($B23="")),($E23=""))),2,0)</f>
         <v/>
       </c>
@@ -1628,26 +1542,22 @@
         <v/>
       </c>
       <c r="I24" s="3">
-        <f>IF(AND($A24=""),"",IF(OR(($E24=""),($B24="")),"",(IF(ISNUMBER($E24),IF($E24=0,"0",ROUND($E24,9-INT(LOG10(ABS($E24))))&amp;""),$E24&amp;"")&amp;"|"&amp;IF(ISNUMBER($B24),IF($B24=0,"0",ROUND($B24,9-INT(LOG10(ABS($B24))))&amp;""),$B24&amp;""))))</f>
+        <f>IF(AND($A24=""),"",(IF(ISNUMBER($B24),IF($B24=0,"0",ROUND($B24,9-INT(LOG10(ABS($B24))))&amp;""),$B24&amp;"")&amp;" "&amp;IF(ISNUMBER($C24),IF($C24=0,"0",ROUND($C24,9-INT(LOG10(ABS($C24))))&amp;""),$C24&amp;"")&amp;" "&amp;IF(ISNUMBER($D24),IF($D24=0,"0",ROUND($D24,9-INT(LOG10(ABS($D24))))&amp;""),$D24&amp;"")))</f>
         <v/>
       </c>
       <c r="J24" s="3">
-        <f>IF(AND($A24=""),"",(IF(ISNUMBER($B24),IF($B24=0,"0",ROUND($B24,9-INT(LOG10(ABS($B24))))&amp;""),$B24&amp;"")&amp;" "&amp;IF(ISNUMBER($C24),IF($C24=0,"0",ROUND($C24,9-INT(LOG10(ABS($C24))))&amp;""),$C24&amp;"")&amp;" "&amp;IF(ISNUMBER($D24),IF($D24=0,"0",ROUND($D24,9-INT(LOG10(ABS($D24))))&amp;""),$D24&amp;"")))</f>
+        <f>IF(AND($A24=""),"",IF(OR(($E24=""),($B24="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E24))*(EXACT('Asignacion'!$B$4:$B$34,$B24)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E24))*(EXACT('Asignacion'!$B$4:$B$34,$B24)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E24))*(EXACT('Asignacion'!$B$4:$B$34,$B24)),0),0))))))</f>
         <v/>
       </c>
       <c r="K24" s="3">
-        <f>IF(AND($A24=""),"",IF(EXACT($I24,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I24)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I24)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I24)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A24=""),"",IF(AND(NOT(EXACT($J24,"")),EXACT($J24,$I24)),1,0))</f>
         <v/>
       </c>
       <c r="L24" s="3">
-        <f>IF(AND($A24=""),"",IF(AND(NOT(EXACT($I24,"")),EXACT($K24,$J24)),1,0))</f>
+        <f>IF(AND($A24=""),"",MID(IF(AND(NOT(($B24="")),($E24="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M24" s="3">
-        <f>IF(AND($A24=""),"",MID(IF(AND(NOT(($B24="")),($E24="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N24" s="3">
         <f>IF(OR(AND(NOT(($B24="")),($E24=""))),2,0)</f>
         <v/>
       </c>
@@ -1671,26 +1581,22 @@
         <v/>
       </c>
       <c r="I25" s="3">
-        <f>IF(AND($A25=""),"",IF(OR(($E25=""),($B25="")),"",(IF(ISNUMBER($E25),IF($E25=0,"0",ROUND($E25,9-INT(LOG10(ABS($E25))))&amp;""),$E25&amp;"")&amp;"|"&amp;IF(ISNUMBER($B25),IF($B25=0,"0",ROUND($B25,9-INT(LOG10(ABS($B25))))&amp;""),$B25&amp;""))))</f>
+        <f>IF(AND($A25=""),"",(IF(ISNUMBER($B25),IF($B25=0,"0",ROUND($B25,9-INT(LOG10(ABS($B25))))&amp;""),$B25&amp;"")&amp;" "&amp;IF(ISNUMBER($C25),IF($C25=0,"0",ROUND($C25,9-INT(LOG10(ABS($C25))))&amp;""),$C25&amp;"")&amp;" "&amp;IF(ISNUMBER($D25),IF($D25=0,"0",ROUND($D25,9-INT(LOG10(ABS($D25))))&amp;""),$D25&amp;"")))</f>
         <v/>
       </c>
       <c r="J25" s="3">
-        <f>IF(AND($A25=""),"",(IF(ISNUMBER($B25),IF($B25=0,"0",ROUND($B25,9-INT(LOG10(ABS($B25))))&amp;""),$B25&amp;"")&amp;" "&amp;IF(ISNUMBER($C25),IF($C25=0,"0",ROUND($C25,9-INT(LOG10(ABS($C25))))&amp;""),$C25&amp;"")&amp;" "&amp;IF(ISNUMBER($D25),IF($D25=0,"0",ROUND($D25,9-INT(LOG10(ABS($D25))))&amp;""),$D25&amp;"")))</f>
+        <f>IF(AND($A25=""),"",IF(OR(($E25=""),($B25="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E25))*(EXACT('Asignacion'!$B$4:$B$34,$B25)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E25))*(EXACT('Asignacion'!$B$4:$B$34,$B25)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E25))*(EXACT('Asignacion'!$B$4:$B$34,$B25)),0),0))))))</f>
         <v/>
       </c>
       <c r="K25" s="3">
-        <f>IF(AND($A25=""),"",IF(EXACT($I25,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I25)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I25)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I25)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A25=""),"",IF(AND(NOT(EXACT($J25,"")),EXACT($J25,$I25)),1,0))</f>
         <v/>
       </c>
       <c r="L25" s="3">
-        <f>IF(AND($A25=""),"",IF(AND(NOT(EXACT($I25,"")),EXACT($K25,$J25)),1,0))</f>
+        <f>IF(AND($A25=""),"",MID(IF(AND(NOT(($B25="")),($E25="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M25" s="3">
-        <f>IF(AND($A25=""),"",MID(IF(AND(NOT(($B25="")),($E25="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N25" s="3">
         <f>IF(OR(AND(NOT(($B25="")),($E25=""))),2,0)</f>
         <v/>
       </c>
@@ -1714,26 +1620,22 @@
         <v/>
       </c>
       <c r="I26" s="3">
-        <f>IF(AND($A26=""),"",IF(OR(($E26=""),($B26="")),"",(IF(ISNUMBER($E26),IF($E26=0,"0",ROUND($E26,9-INT(LOG10(ABS($E26))))&amp;""),$E26&amp;"")&amp;"|"&amp;IF(ISNUMBER($B26),IF($B26=0,"0",ROUND($B26,9-INT(LOG10(ABS($B26))))&amp;""),$B26&amp;""))))</f>
+        <f>IF(AND($A26=""),"",(IF(ISNUMBER($B26),IF($B26=0,"0",ROUND($B26,9-INT(LOG10(ABS($B26))))&amp;""),$B26&amp;"")&amp;" "&amp;IF(ISNUMBER($C26),IF($C26=0,"0",ROUND($C26,9-INT(LOG10(ABS($C26))))&amp;""),$C26&amp;"")&amp;" "&amp;IF(ISNUMBER($D26),IF($D26=0,"0",ROUND($D26,9-INT(LOG10(ABS($D26))))&amp;""),$D26&amp;"")))</f>
         <v/>
       </c>
       <c r="J26" s="3">
-        <f>IF(AND($A26=""),"",(IF(ISNUMBER($B26),IF($B26=0,"0",ROUND($B26,9-INT(LOG10(ABS($B26))))&amp;""),$B26&amp;"")&amp;" "&amp;IF(ISNUMBER($C26),IF($C26=0,"0",ROUND($C26,9-INT(LOG10(ABS($C26))))&amp;""),$C26&amp;"")&amp;" "&amp;IF(ISNUMBER($D26),IF($D26=0,"0",ROUND($D26,9-INT(LOG10(ABS($D26))))&amp;""),$D26&amp;"")))</f>
+        <f>IF(AND($A26=""),"",IF(OR(($E26=""),($B26="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E26))*(EXACT('Asignacion'!$B$4:$B$34,$B26)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E26))*(EXACT('Asignacion'!$B$4:$B$34,$B26)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E26))*(EXACT('Asignacion'!$B$4:$B$34,$B26)),0),0))))))</f>
         <v/>
       </c>
       <c r="K26" s="3">
-        <f>IF(AND($A26=""),"",IF(EXACT($I26,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I26)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I26)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I26)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A26=""),"",IF(AND(NOT(EXACT($J26,"")),EXACT($J26,$I26)),1,0))</f>
         <v/>
       </c>
       <c r="L26" s="3">
-        <f>IF(AND($A26=""),"",IF(AND(NOT(EXACT($I26,"")),EXACT($K26,$J26)),1,0))</f>
+        <f>IF(AND($A26=""),"",MID(IF(AND(NOT(($B26="")),($E26="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M26" s="3">
-        <f>IF(AND($A26=""),"",MID(IF(AND(NOT(($B26="")),($E26="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N26" s="3">
         <f>IF(OR(AND(NOT(($B26="")),($E26=""))),2,0)</f>
         <v/>
       </c>
@@ -1757,26 +1659,22 @@
         <v/>
       </c>
       <c r="I27" s="3">
-        <f>IF(AND($A27=""),"",IF(OR(($E27=""),($B27="")),"",(IF(ISNUMBER($E27),IF($E27=0,"0",ROUND($E27,9-INT(LOG10(ABS($E27))))&amp;""),$E27&amp;"")&amp;"|"&amp;IF(ISNUMBER($B27),IF($B27=0,"0",ROUND($B27,9-INT(LOG10(ABS($B27))))&amp;""),$B27&amp;""))))</f>
+        <f>IF(AND($A27=""),"",(IF(ISNUMBER($B27),IF($B27=0,"0",ROUND($B27,9-INT(LOG10(ABS($B27))))&amp;""),$B27&amp;"")&amp;" "&amp;IF(ISNUMBER($C27),IF($C27=0,"0",ROUND($C27,9-INT(LOG10(ABS($C27))))&amp;""),$C27&amp;"")&amp;" "&amp;IF(ISNUMBER($D27),IF($D27=0,"0",ROUND($D27,9-INT(LOG10(ABS($D27))))&amp;""),$D27&amp;"")))</f>
         <v/>
       </c>
       <c r="J27" s="3">
-        <f>IF(AND($A27=""),"",(IF(ISNUMBER($B27),IF($B27=0,"0",ROUND($B27,9-INT(LOG10(ABS($B27))))&amp;""),$B27&amp;"")&amp;" "&amp;IF(ISNUMBER($C27),IF($C27=0,"0",ROUND($C27,9-INT(LOG10(ABS($C27))))&amp;""),$C27&amp;"")&amp;" "&amp;IF(ISNUMBER($D27),IF($D27=0,"0",ROUND($D27,9-INT(LOG10(ABS($D27))))&amp;""),$D27&amp;"")))</f>
+        <f>IF(AND($A27=""),"",IF(OR(($E27=""),($B27="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E27))*(EXACT('Asignacion'!$B$4:$B$34,$B27)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E27))*(EXACT('Asignacion'!$B$4:$B$34,$B27)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E27))*(EXACT('Asignacion'!$B$4:$B$34,$B27)),0),0))))))</f>
         <v/>
       </c>
       <c r="K27" s="3">
-        <f>IF(AND($A27=""),"",IF(EXACT($I27,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I27)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I27)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I27)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A27=""),"",IF(AND(NOT(EXACT($J27,"")),EXACT($J27,$I27)),1,0))</f>
         <v/>
       </c>
       <c r="L27" s="3">
-        <f>IF(AND($A27=""),"",IF(AND(NOT(EXACT($I27,"")),EXACT($K27,$J27)),1,0))</f>
+        <f>IF(AND($A27=""),"",MID(IF(AND(NOT(($B27="")),($E27="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M27" s="3">
-        <f>IF(AND($A27=""),"",MID(IF(AND(NOT(($B27="")),($E27="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N27" s="3">
         <f>IF(OR(AND(NOT(($B27="")),($E27=""))),2,0)</f>
         <v/>
       </c>
@@ -1800,26 +1698,22 @@
         <v/>
       </c>
       <c r="I28" s="3">
-        <f>IF(AND($A28=""),"",IF(OR(($E28=""),($B28="")),"",(IF(ISNUMBER($E28),IF($E28=0,"0",ROUND($E28,9-INT(LOG10(ABS($E28))))&amp;""),$E28&amp;"")&amp;"|"&amp;IF(ISNUMBER($B28),IF($B28=0,"0",ROUND($B28,9-INT(LOG10(ABS($B28))))&amp;""),$B28&amp;""))))</f>
+        <f>IF(AND($A28=""),"",(IF(ISNUMBER($B28),IF($B28=0,"0",ROUND($B28,9-INT(LOG10(ABS($B28))))&amp;""),$B28&amp;"")&amp;" "&amp;IF(ISNUMBER($C28),IF($C28=0,"0",ROUND($C28,9-INT(LOG10(ABS($C28))))&amp;""),$C28&amp;"")&amp;" "&amp;IF(ISNUMBER($D28),IF($D28=0,"0",ROUND($D28,9-INT(LOG10(ABS($D28))))&amp;""),$D28&amp;"")))</f>
         <v/>
       </c>
       <c r="J28" s="3">
-        <f>IF(AND($A28=""),"",(IF(ISNUMBER($B28),IF($B28=0,"0",ROUND($B28,9-INT(LOG10(ABS($B28))))&amp;""),$B28&amp;"")&amp;" "&amp;IF(ISNUMBER($C28),IF($C28=0,"0",ROUND($C28,9-INT(LOG10(ABS($C28))))&amp;""),$C28&amp;"")&amp;" "&amp;IF(ISNUMBER($D28),IF($D28=0,"0",ROUND($D28,9-INT(LOG10(ABS($D28))))&amp;""),$D28&amp;"")))</f>
+        <f>IF(AND($A28=""),"",IF(OR(($E28=""),($B28="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E28))*(EXACT('Asignacion'!$B$4:$B$34,$B28)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E28))*(EXACT('Asignacion'!$B$4:$B$34,$B28)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E28))*(EXACT('Asignacion'!$B$4:$B$34,$B28)),0),0))))))</f>
         <v/>
       </c>
       <c r="K28" s="3">
-        <f>IF(AND($A28=""),"",IF(EXACT($I28,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I28)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I28)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I28)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A28=""),"",IF(AND(NOT(EXACT($J28,"")),EXACT($J28,$I28)),1,0))</f>
         <v/>
       </c>
       <c r="L28" s="3">
-        <f>IF(AND($A28=""),"",IF(AND(NOT(EXACT($I28,"")),EXACT($K28,$J28)),1,0))</f>
+        <f>IF(AND($A28=""),"",MID(IF(AND(NOT(($B28="")),($E28="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M28" s="3">
-        <f>IF(AND($A28=""),"",MID(IF(AND(NOT(($B28="")),($E28="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N28" s="3">
         <f>IF(OR(AND(NOT(($B28="")),($E28=""))),2,0)</f>
         <v/>
       </c>
@@ -1843,26 +1737,22 @@
         <v/>
       </c>
       <c r="I29" s="3">
-        <f>IF(AND($A29=""),"",IF(OR(($E29=""),($B29="")),"",(IF(ISNUMBER($E29),IF($E29=0,"0",ROUND($E29,9-INT(LOG10(ABS($E29))))&amp;""),$E29&amp;"")&amp;"|"&amp;IF(ISNUMBER($B29),IF($B29=0,"0",ROUND($B29,9-INT(LOG10(ABS($B29))))&amp;""),$B29&amp;""))))</f>
+        <f>IF(AND($A29=""),"",(IF(ISNUMBER($B29),IF($B29=0,"0",ROUND($B29,9-INT(LOG10(ABS($B29))))&amp;""),$B29&amp;"")&amp;" "&amp;IF(ISNUMBER($C29),IF($C29=0,"0",ROUND($C29,9-INT(LOG10(ABS($C29))))&amp;""),$C29&amp;"")&amp;" "&amp;IF(ISNUMBER($D29),IF($D29=0,"0",ROUND($D29,9-INT(LOG10(ABS($D29))))&amp;""),$D29&amp;"")))</f>
         <v/>
       </c>
       <c r="J29" s="3">
-        <f>IF(AND($A29=""),"",(IF(ISNUMBER($B29),IF($B29=0,"0",ROUND($B29,9-INT(LOG10(ABS($B29))))&amp;""),$B29&amp;"")&amp;" "&amp;IF(ISNUMBER($C29),IF($C29=0,"0",ROUND($C29,9-INT(LOG10(ABS($C29))))&amp;""),$C29&amp;"")&amp;" "&amp;IF(ISNUMBER($D29),IF($D29=0,"0",ROUND($D29,9-INT(LOG10(ABS($D29))))&amp;""),$D29&amp;"")))</f>
+        <f>IF(AND($A29=""),"",IF(OR(($E29=""),($B29="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E29))*(EXACT('Asignacion'!$B$4:$B$34,$B29)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E29))*(EXACT('Asignacion'!$B$4:$B$34,$B29)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E29))*(EXACT('Asignacion'!$B$4:$B$34,$B29)),0),0))))))</f>
         <v/>
       </c>
       <c r="K29" s="3">
-        <f>IF(AND($A29=""),"",IF(EXACT($I29,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I29)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I29)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I29)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A29=""),"",IF(AND(NOT(EXACT($J29,"")),EXACT($J29,$I29)),1,0))</f>
         <v/>
       </c>
       <c r="L29" s="3">
-        <f>IF(AND($A29=""),"",IF(AND(NOT(EXACT($I29,"")),EXACT($K29,$J29)),1,0))</f>
+        <f>IF(AND($A29=""),"",MID(IF(AND(NOT(($B29="")),($E29="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M29" s="3">
-        <f>IF(AND($A29=""),"",MID(IF(AND(NOT(($B29="")),($E29="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N29" s="3">
         <f>IF(OR(AND(NOT(($B29="")),($E29=""))),2,0)</f>
         <v/>
       </c>
@@ -1886,26 +1776,22 @@
         <v/>
       </c>
       <c r="I30" s="3">
-        <f>IF(AND($A30=""),"",IF(OR(($E30=""),($B30="")),"",(IF(ISNUMBER($E30),IF($E30=0,"0",ROUND($E30,9-INT(LOG10(ABS($E30))))&amp;""),$E30&amp;"")&amp;"|"&amp;IF(ISNUMBER($B30),IF($B30=0,"0",ROUND($B30,9-INT(LOG10(ABS($B30))))&amp;""),$B30&amp;""))))</f>
+        <f>IF(AND($A30=""),"",(IF(ISNUMBER($B30),IF($B30=0,"0",ROUND($B30,9-INT(LOG10(ABS($B30))))&amp;""),$B30&amp;"")&amp;" "&amp;IF(ISNUMBER($C30),IF($C30=0,"0",ROUND($C30,9-INT(LOG10(ABS($C30))))&amp;""),$C30&amp;"")&amp;" "&amp;IF(ISNUMBER($D30),IF($D30=0,"0",ROUND($D30,9-INT(LOG10(ABS($D30))))&amp;""),$D30&amp;"")))</f>
         <v/>
       </c>
       <c r="J30" s="3">
-        <f>IF(AND($A30=""),"",(IF(ISNUMBER($B30),IF($B30=0,"0",ROUND($B30,9-INT(LOG10(ABS($B30))))&amp;""),$B30&amp;"")&amp;" "&amp;IF(ISNUMBER($C30),IF($C30=0,"0",ROUND($C30,9-INT(LOG10(ABS($C30))))&amp;""),$C30&amp;"")&amp;" "&amp;IF(ISNUMBER($D30),IF($D30=0,"0",ROUND($D30,9-INT(LOG10(ABS($D30))))&amp;""),$D30&amp;"")))</f>
+        <f>IF(AND($A30=""),"",IF(OR(($E30=""),($B30="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E30))*(EXACT('Asignacion'!$B$4:$B$34,$B30)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E30))*(EXACT('Asignacion'!$B$4:$B$34,$B30)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E30))*(EXACT('Asignacion'!$B$4:$B$34,$B30)),0),0))))))</f>
         <v/>
       </c>
       <c r="K30" s="3">
-        <f>IF(AND($A30=""),"",IF(EXACT($I30,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I30)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I30)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I30)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A30=""),"",IF(AND(NOT(EXACT($J30,"")),EXACT($J30,$I30)),1,0))</f>
         <v/>
       </c>
       <c r="L30" s="3">
-        <f>IF(AND($A30=""),"",IF(AND(NOT(EXACT($I30,"")),EXACT($K30,$J30)),1,0))</f>
+        <f>IF(AND($A30=""),"",MID(IF(AND(NOT(($B30="")),($E30="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M30" s="3">
-        <f>IF(AND($A30=""),"",MID(IF(AND(NOT(($B30="")),($E30="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N30" s="3">
         <f>IF(OR(AND(NOT(($B30="")),($E30=""))),2,0)</f>
         <v/>
       </c>
@@ -1929,26 +1815,22 @@
         <v/>
       </c>
       <c r="I31" s="3">
-        <f>IF(AND($A31=""),"",IF(OR(($E31=""),($B31="")),"",(IF(ISNUMBER($E31),IF($E31=0,"0",ROUND($E31,9-INT(LOG10(ABS($E31))))&amp;""),$E31&amp;"")&amp;"|"&amp;IF(ISNUMBER($B31),IF($B31=0,"0",ROUND($B31,9-INT(LOG10(ABS($B31))))&amp;""),$B31&amp;""))))</f>
+        <f>IF(AND($A31=""),"",(IF(ISNUMBER($B31),IF($B31=0,"0",ROUND($B31,9-INT(LOG10(ABS($B31))))&amp;""),$B31&amp;"")&amp;" "&amp;IF(ISNUMBER($C31),IF($C31=0,"0",ROUND($C31,9-INT(LOG10(ABS($C31))))&amp;""),$C31&amp;"")&amp;" "&amp;IF(ISNUMBER($D31),IF($D31=0,"0",ROUND($D31,9-INT(LOG10(ABS($D31))))&amp;""),$D31&amp;"")))</f>
         <v/>
       </c>
       <c r="J31" s="3">
-        <f>IF(AND($A31=""),"",(IF(ISNUMBER($B31),IF($B31=0,"0",ROUND($B31,9-INT(LOG10(ABS($B31))))&amp;""),$B31&amp;"")&amp;" "&amp;IF(ISNUMBER($C31),IF($C31=0,"0",ROUND($C31,9-INT(LOG10(ABS($C31))))&amp;""),$C31&amp;"")&amp;" "&amp;IF(ISNUMBER($D31),IF($D31=0,"0",ROUND($D31,9-INT(LOG10(ABS($D31))))&amp;""),$D31&amp;"")))</f>
+        <f>IF(AND($A31=""),"",IF(OR(($E31=""),($B31="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E31))*(EXACT('Asignacion'!$B$4:$B$34,$B31)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E31))*(EXACT('Asignacion'!$B$4:$B$34,$B31)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E31))*(EXACT('Asignacion'!$B$4:$B$34,$B31)),0),0))))))</f>
         <v/>
       </c>
       <c r="K31" s="3">
-        <f>IF(AND($A31=""),"",IF(EXACT($I31,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I31)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I31)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I31)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A31=""),"",IF(AND(NOT(EXACT($J31,"")),EXACT($J31,$I31)),1,0))</f>
         <v/>
       </c>
       <c r="L31" s="3">
-        <f>IF(AND($A31=""),"",IF(AND(NOT(EXACT($I31,"")),EXACT($K31,$J31)),1,0))</f>
+        <f>IF(AND($A31=""),"",MID(IF(AND(NOT(($B31="")),($E31="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M31" s="3">
-        <f>IF(AND($A31=""),"",MID(IF(AND(NOT(($B31="")),($E31="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N31" s="3">
         <f>IF(OR(AND(NOT(($B31="")),($E31=""))),2,0)</f>
         <v/>
       </c>
@@ -1972,26 +1854,22 @@
         <v/>
       </c>
       <c r="I32" s="3">
-        <f>IF(AND($A32=""),"",IF(OR(($E32=""),($B32="")),"",(IF(ISNUMBER($E32),IF($E32=0,"0",ROUND($E32,9-INT(LOG10(ABS($E32))))&amp;""),$E32&amp;"")&amp;"|"&amp;IF(ISNUMBER($B32),IF($B32=0,"0",ROUND($B32,9-INT(LOG10(ABS($B32))))&amp;""),$B32&amp;""))))</f>
+        <f>IF(AND($A32=""),"",(IF(ISNUMBER($B32),IF($B32=0,"0",ROUND($B32,9-INT(LOG10(ABS($B32))))&amp;""),$B32&amp;"")&amp;" "&amp;IF(ISNUMBER($C32),IF($C32=0,"0",ROUND($C32,9-INT(LOG10(ABS($C32))))&amp;""),$C32&amp;"")&amp;" "&amp;IF(ISNUMBER($D32),IF($D32=0,"0",ROUND($D32,9-INT(LOG10(ABS($D32))))&amp;""),$D32&amp;"")))</f>
         <v/>
       </c>
       <c r="J32" s="3">
-        <f>IF(AND($A32=""),"",(IF(ISNUMBER($B32),IF($B32=0,"0",ROUND($B32,9-INT(LOG10(ABS($B32))))&amp;""),$B32&amp;"")&amp;" "&amp;IF(ISNUMBER($C32),IF($C32=0,"0",ROUND($C32,9-INT(LOG10(ABS($C32))))&amp;""),$C32&amp;"")&amp;" "&amp;IF(ISNUMBER($D32),IF($D32=0,"0",ROUND($D32,9-INT(LOG10(ABS($D32))))&amp;""),$D32&amp;"")))</f>
+        <f>IF(AND($A32=""),"",IF(OR(($E32=""),($B32="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E32))*(EXACT('Asignacion'!$B$4:$B$34,$B32)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E32))*(EXACT('Asignacion'!$B$4:$B$34,$B32)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E32))*(EXACT('Asignacion'!$B$4:$B$34,$B32)),0),0))))))</f>
         <v/>
       </c>
       <c r="K32" s="3">
-        <f>IF(AND($A32=""),"",IF(EXACT($I32,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I32)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I32)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I32)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A32=""),"",IF(AND(NOT(EXACT($J32,"")),EXACT($J32,$I32)),1,0))</f>
         <v/>
       </c>
       <c r="L32" s="3">
-        <f>IF(AND($A32=""),"",IF(AND(NOT(EXACT($I32,"")),EXACT($K32,$J32)),1,0))</f>
+        <f>IF(AND($A32=""),"",MID(IF(AND(NOT(($B32="")),($E32="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M32" s="3">
-        <f>IF(AND($A32=""),"",MID(IF(AND(NOT(($B32="")),($E32="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N32" s="3">
         <f>IF(OR(AND(NOT(($B32="")),($E32=""))),2,0)</f>
         <v/>
       </c>
@@ -2015,26 +1893,22 @@
         <v/>
       </c>
       <c r="I33" s="3">
-        <f>IF(AND($A33=""),"",IF(OR(($E33=""),($B33="")),"",(IF(ISNUMBER($E33),IF($E33=0,"0",ROUND($E33,9-INT(LOG10(ABS($E33))))&amp;""),$E33&amp;"")&amp;"|"&amp;IF(ISNUMBER($B33),IF($B33=0,"0",ROUND($B33,9-INT(LOG10(ABS($B33))))&amp;""),$B33&amp;""))))</f>
+        <f>IF(AND($A33=""),"",(IF(ISNUMBER($B33),IF($B33=0,"0",ROUND($B33,9-INT(LOG10(ABS($B33))))&amp;""),$B33&amp;"")&amp;" "&amp;IF(ISNUMBER($C33),IF($C33=0,"0",ROUND($C33,9-INT(LOG10(ABS($C33))))&amp;""),$C33&amp;"")&amp;" "&amp;IF(ISNUMBER($D33),IF($D33=0,"0",ROUND($D33,9-INT(LOG10(ABS($D33))))&amp;""),$D33&amp;"")))</f>
         <v/>
       </c>
       <c r="J33" s="3">
-        <f>IF(AND($A33=""),"",(IF(ISNUMBER($B33),IF($B33=0,"0",ROUND($B33,9-INT(LOG10(ABS($B33))))&amp;""),$B33&amp;"")&amp;" "&amp;IF(ISNUMBER($C33),IF($C33=0,"0",ROUND($C33,9-INT(LOG10(ABS($C33))))&amp;""),$C33&amp;"")&amp;" "&amp;IF(ISNUMBER($D33),IF($D33=0,"0",ROUND($D33,9-INT(LOG10(ABS($D33))))&amp;""),$D33&amp;"")))</f>
+        <f>IF(AND($A33=""),"",IF(OR(($E33=""),($B33="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E33))*(EXACT('Asignacion'!$B$4:$B$34,$B33)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E33))*(EXACT('Asignacion'!$B$4:$B$34,$B33)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E33))*(EXACT('Asignacion'!$B$4:$B$34,$B33)),0),0))))))</f>
         <v/>
       </c>
       <c r="K33" s="3">
-        <f>IF(AND($A33=""),"",IF(EXACT($I33,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I33)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I33)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I33)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A33=""),"",IF(AND(NOT(EXACT($J33,"")),EXACT($J33,$I33)),1,0))</f>
         <v/>
       </c>
       <c r="L33" s="3">
-        <f>IF(AND($A33=""),"",IF(AND(NOT(EXACT($I33,"")),EXACT($K33,$J33)),1,0))</f>
+        <f>IF(AND($A33=""),"",MID(IF(AND(NOT(($B33="")),($E33="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M33" s="3">
-        <f>IF(AND($A33=""),"",MID(IF(AND(NOT(($B33="")),($E33="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N33" s="3">
         <f>IF(OR(AND(NOT(($B33="")),($E33=""))),2,0)</f>
         <v/>
       </c>
@@ -2058,26 +1932,22 @@
         <v/>
       </c>
       <c r="I34" s="3">
-        <f>IF(AND($A34=""),"",IF(OR(($E34=""),($B34="")),"",(IF(ISNUMBER($E34),IF($E34=0,"0",ROUND($E34,9-INT(LOG10(ABS($E34))))&amp;""),$E34&amp;"")&amp;"|"&amp;IF(ISNUMBER($B34),IF($B34=0,"0",ROUND($B34,9-INT(LOG10(ABS($B34))))&amp;""),$B34&amp;""))))</f>
+        <f>IF(AND($A34=""),"",(IF(ISNUMBER($B34),IF($B34=0,"0",ROUND($B34,9-INT(LOG10(ABS($B34))))&amp;""),$B34&amp;"")&amp;" "&amp;IF(ISNUMBER($C34),IF($C34=0,"0",ROUND($C34,9-INT(LOG10(ABS($C34))))&amp;""),$C34&amp;"")&amp;" "&amp;IF(ISNUMBER($D34),IF($D34=0,"0",ROUND($D34,9-INT(LOG10(ABS($D34))))&amp;""),$D34&amp;"")))</f>
         <v/>
       </c>
       <c r="J34" s="3">
-        <f>IF(AND($A34=""),"",(IF(ISNUMBER($B34),IF($B34=0,"0",ROUND($B34,9-INT(LOG10(ABS($B34))))&amp;""),$B34&amp;"")&amp;" "&amp;IF(ISNUMBER($C34),IF($C34=0,"0",ROUND($C34,9-INT(LOG10(ABS($C34))))&amp;""),$C34&amp;"")&amp;" "&amp;IF(ISNUMBER($D34),IF($D34=0,"0",ROUND($D34,9-INT(LOG10(ABS($D34))))&amp;""),$D34&amp;"")))</f>
+        <f>IF(AND($A34=""),"",IF(OR(($E34=""),($B34="")),"",IF(ISNA(MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E34))*(EXACT('Asignacion'!$B$4:$B$34,$B34)),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E34))*(EXACT('Asignacion'!$B$4:$B$34,$B34)),0),0))),"",INDEX('Asignacion'!$I$4:$I$34,MATCH(1,INDEX(1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0)*(EXACT('Asignacion'!$E$4:$E$34,$E34))*(EXACT('Asignacion'!$B$4:$B$34,$B34)),0),0))))))</f>
         <v/>
       </c>
       <c r="K34" s="3">
-        <f>IF(AND($A34=""),"",IF(EXACT($I34,""),"",IF(ISNA(MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I34)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0)),"",IF(ISBLANK(INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I34)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))),"",INDEX('Asignacion'!$J$4:$J$34,MATCH(1,INDEX(EXACT('Asignacion'!$I$4:$I$34,$I34)*1*((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0),0),0))))))</f>
+        <f>IF(AND($A34=""),"",IF(AND(NOT(EXACT($J34,"")),EXACT($J34,$I34)),1,0))</f>
         <v/>
       </c>
       <c r="L34" s="3">
-        <f>IF(AND($A34=""),"",IF(AND(NOT(EXACT($I34,"")),EXACT($K34,$J34)),1,0))</f>
+        <f>IF(AND($A34=""),"",MID(IF(AND(NOT(($B34="")),($E34="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
         <v/>
       </c>
       <c r="M34" s="3">
-        <f>IF(AND($A34=""),"",MID(IF(AND(NOT(($B34="")),($E34="")),"; "&amp;"Esta fila de carga todavia no tiene profesor",""),3,32767))</f>
-        <v/>
-      </c>
-      <c r="N34" s="3">
         <f>IF(OR(AND(NOT(($B34="")),($E34=""))),2,0)</f>
         <v/>
       </c>
@@ -2219,7 +2089,7 @@
         <v/>
       </c>
       <c r="F4" s="3">
-        <f>IF(AND($A4=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A4)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A4=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A4)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G4" s="3">
@@ -2259,7 +2129,7 @@
         <v/>
       </c>
       <c r="F5" s="3">
-        <f>IF(AND($A5=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A5)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A5=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A5)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G5" s="3">
@@ -2299,7 +2169,7 @@
         <v/>
       </c>
       <c r="F6" s="3">
-        <f>IF(AND($A6=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A6)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A6=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A6)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G6" s="3">
@@ -2339,7 +2209,7 @@
         <v/>
       </c>
       <c r="F7" s="3">
-        <f>IF(AND($A7=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A7)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A7=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A7)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G7" s="3">
@@ -2365,7 +2235,7 @@
         <v/>
       </c>
       <c r="F8" s="3">
-        <f>IF(AND($A8=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A8)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A8=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A8)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G8" s="3">
@@ -2391,7 +2261,7 @@
         <v/>
       </c>
       <c r="F9" s="3">
-        <f>IF(AND($A9=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A9)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A9=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A9)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G9" s="3">
@@ -2417,7 +2287,7 @@
         <v/>
       </c>
       <c r="F10" s="3">
-        <f>IF(AND($A10=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A10)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A10=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A10)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G10" s="3">
@@ -2443,7 +2313,7 @@
         <v/>
       </c>
       <c r="F11" s="3">
-        <f>IF(AND($A11=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A11)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A11=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A11)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G11" s="3">
@@ -2469,7 +2339,7 @@
         <v/>
       </c>
       <c r="F12" s="3">
-        <f>IF(AND($A12=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A12)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A12=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A12)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G12" s="3">
@@ -2495,7 +2365,7 @@
         <v/>
       </c>
       <c r="F13" s="3">
-        <f>IF(AND($A13=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A13)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A13=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A13)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G13" s="3">
@@ -2521,7 +2391,7 @@
         <v/>
       </c>
       <c r="F14" s="3">
-        <f>IF(AND($A14=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A14)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A14=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A14)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G14" s="3">
@@ -2547,7 +2417,7 @@
         <v/>
       </c>
       <c r="F15" s="3">
-        <f>IF(AND($A15=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A15)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A15=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A15)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G15" s="3">
@@ -2573,7 +2443,7 @@
         <v/>
       </c>
       <c r="F16" s="3">
-        <f>IF(AND($A16=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A16)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A16=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A16)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G16" s="3">
@@ -2599,7 +2469,7 @@
         <v/>
       </c>
       <c r="F17" s="3">
-        <f>IF(AND($A17=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A17)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A17=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A17)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G17" s="3">
@@ -2625,7 +2495,7 @@
         <v/>
       </c>
       <c r="F18" s="3">
-        <f>IF(AND($A18=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A18)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A18=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A18)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G18" s="3">
@@ -2651,7 +2521,7 @@
         <v/>
       </c>
       <c r="F19" s="3">
-        <f>IF(AND($A19=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A19)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A19=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A19)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G19" s="3">
@@ -2677,7 +2547,7 @@
         <v/>
       </c>
       <c r="F20" s="3">
-        <f>IF(AND($A20=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A20)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A20=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A20)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G20" s="3">
@@ -2703,7 +2573,7 @@
         <v/>
       </c>
       <c r="F21" s="3">
-        <f>IF(AND($A21=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A21)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A21=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A21)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G21" s="3">
@@ -2729,7 +2599,7 @@
         <v/>
       </c>
       <c r="F22" s="3">
-        <f>IF(AND($A22=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A22)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A22=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A22)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G22" s="3">
@@ -2755,7 +2625,7 @@
         <v/>
       </c>
       <c r="F23" s="3">
-        <f>IF(AND($A23=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A23)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A23=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A23)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G23" s="3">
@@ -2781,7 +2651,7 @@
         <v/>
       </c>
       <c r="F24" s="3">
-        <f>IF(AND($A24=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A24)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A24=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A24)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G24" s="3">
@@ -2807,7 +2677,7 @@
         <v/>
       </c>
       <c r="F25" s="3">
-        <f>IF(AND($A25=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A25)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A25=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A25)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G25" s="3">
@@ -2833,7 +2703,7 @@
         <v/>
       </c>
       <c r="F26" s="3">
-        <f>IF(AND($A26=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A26)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A26=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A26)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G26" s="3">
@@ -2859,7 +2729,7 @@
         <v/>
       </c>
       <c r="F27" s="3">
-        <f>IF(AND($A27=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A27)))*(IFERROR(VALUE('Asignacion'!$L$4:$L$34&amp;""),0))))</f>
+        <f>IF(AND($A27=""),"",SUMPRODUCT(1*(((('Asignacion'!$A$4:$A$34&lt;&gt;""))&gt;0))*((EXACT('Asignacion'!$E$4:$E$34,$A27)))*(IFERROR(VALUE('Asignacion'!$K$4:$K$34&amp;""),0))))</f>
         <v/>
       </c>
       <c r="G27" s="3">
@@ -4097,7 +3967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z27"/>
+  <dimension ref="A1:X27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4109,9 +3979,9 @@
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
@@ -4122,9 +3992,7 @@
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="18" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4182,81 +4050,71 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Par</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
+          <t>Primera del par</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Cuenta</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>Profesor</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>Asignatura</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="W3" s="2" t="inlineStr">
         <is>
           <t>Primera del par</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Cuenta</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="n"/>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>Grupo</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>Profesor</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>Asignatura</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>Horas</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Nombre</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>Par</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>Codigo</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>Primera del par</t>
-        </is>
-      </c>
-      <c r="Z3" s="9" t="inlineStr">
+      <c r="X3" s="9" t="inlineStr">
         <is>
           <t>Cuenta</t>
         </is>
@@ -4301,7 +4159,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>PIAD|EST-CC</t>
+          <t xml:space="preserve">EST-CC Conf </t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -4309,20 +4167,16 @@
           <t xml:space="preserve">EST-CC Conf </t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EST-CC Conf </t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="n">
+      <c r="L4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N4" s="3" t="n"/>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>PIAD</t>
         </is>
       </c>
+      <c r="O4" s="3" t="n"/>
       <c r="P4" s="3" t="n"/>
       <c r="Q4" s="3" t="n"/>
       <c r="R4" s="3" t="n"/>
@@ -4331,8 +4185,6 @@
       <c r="U4" s="3" t="n"/>
       <c r="V4" s="3" t="n"/>
       <c r="W4" s="3" t="n"/>
-      <c r="X4" s="3" t="n"/>
-      <c r="Y4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3">
@@ -4377,69 +4229,60 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>PIAD|EST-CC</t>
+          <t>EST-CC CP 1</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>EST-CC CP 1</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">EST-CC Conf </t>
         </is>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="L5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3">
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <v/>
+      </c>
       <c r="O5" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P5" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q5" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R5" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S5" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T5" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U5" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V5" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W5" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="X5" s="3">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
-      <c r="Y5" s="3">
+      <c r="X5">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="Z5">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -4486,69 +4329,60 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>PIAD|EST-CC</t>
+          <t>EST-CC CP 2</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>EST-CC CP 2</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">EST-CC Conf </t>
         </is>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="L6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3">
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <v/>
+      </c>
       <c r="O6" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P6" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q6" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R6" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S6" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T6" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U6" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V6" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W6" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="X6" s="3">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
-      <c r="Y6" s="3">
+      <c r="X6">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="Z6">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -4591,7 +4425,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>PIAD|EST-MAT</t>
+          <t xml:space="preserve">EST-MAT Conf </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -4599,61 +4433,52 @@
           <t xml:space="preserve">EST-MAT Conf </t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EST-MAT Conf </t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="n">
+      <c r="L7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3">
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <v/>
+      </c>
       <c r="O7" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P7" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q7" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R7" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S7" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T7" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U7" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V7" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W7" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="X7" s="3">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
-      <c r="Y7" s="3">
+      <c r="X7">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -4696,7 +4521,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>MARA|PROB</t>
+          <t xml:space="preserve">PROB Conf </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -4704,61 +4529,52 @@
           <t xml:space="preserve">PROB Conf </t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PROB Conf </t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="n">
+      <c r="L8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3">
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <v/>
+      </c>
       <c r="O8" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P8" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q8" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R8" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S8" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T8" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U8" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V8" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W8" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="X8" s="3">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
-      <c r="Y8" s="3">
+      <c r="X8">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -4805,69 +4621,60 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>MARA|PROB</t>
+          <t>PROB CP 1</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>PROB CP 1</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">PROB Conf </t>
         </is>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="L9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3">
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <v/>
+      </c>
       <c r="O9" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P9" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q9" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R9" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S9" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T9" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U9" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V9" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W9" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="X9" s="3">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
-      <c r="Y9" s="3">
+      <c r="X9">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"PIAD"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -4910,7 +4717,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>MARA|MNUM</t>
+          <t xml:space="preserve">MNUM Conf </t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -4918,20 +4725,16 @@
           <t xml:space="preserve">MNUM Conf </t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MNUM Conf </t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="n">
+      <c r="L10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="inlineStr">
+      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>MARA</t>
         </is>
       </c>
+      <c r="O10" s="3" t="n"/>
       <c r="P10" s="3" t="n"/>
       <c r="Q10" s="3" t="n"/>
       <c r="R10" s="3" t="n"/>
@@ -4940,8 +4743,6 @@
       <c r="U10" s="3" t="n"/>
       <c r="V10" s="3" t="n"/>
       <c r="W10" s="3" t="n"/>
-      <c r="X10" s="3" t="n"/>
-      <c r="Y10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3">
@@ -4986,7 +4787,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>LUGO|EST-MAT</t>
+          <t>EST-MAT CP 1</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -4994,61 +4795,52 @@
           <t>EST-MAT CP 1</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>EST-MAT CP 1</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="n">
+      <c r="L11" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3">
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <v/>
+      </c>
       <c r="O11" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P11" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q11" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R11" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S11" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T11" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U11" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V11" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W11" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="X11" s="3">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
-      <c r="Y11" s="3">
+      <c r="X11">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="Z11">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -5066,53 +4858,48 @@
       <c r="K12" s="3" t="n"/>
       <c r="L12" s="3" t="n"/>
       <c r="M12" s="3" t="n"/>
-      <c r="N12" s="3" t="n"/>
+      <c r="N12" s="3">
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <v/>
+      </c>
       <c r="O12" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P12" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q12" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R12" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S12" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T12" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U12" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V12" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W12" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="X12" s="3">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
-      <c r="Y12" s="3">
+      <c r="X12">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -5130,53 +4917,48 @@
       <c r="K13" s="3" t="n"/>
       <c r="L13" s="3" t="n"/>
       <c r="M13" s="3" t="n"/>
-      <c r="N13" s="3" t="n"/>
+      <c r="N13" s="3">
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <v/>
+      </c>
       <c r="O13" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P13" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q13" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R13" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S13" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T13" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U13" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V13" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W13" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="X13" s="3">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
-      <c r="Y13" s="3">
+      <c r="X13">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -5194,53 +4976,48 @@
       <c r="K14" s="3" t="n"/>
       <c r="L14" s="3" t="n"/>
       <c r="M14" s="3" t="n"/>
-      <c r="N14" s="3" t="n"/>
+      <c r="N14" s="3">
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <v/>
+      </c>
       <c r="O14" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P14" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q14" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R14" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S14" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T14" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U14" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V14" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W14" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="X14" s="3">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
-      <c r="Y14" s="3">
+      <c r="X14">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -5258,53 +5035,48 @@
       <c r="K15" s="3" t="n"/>
       <c r="L15" s="3" t="n"/>
       <c r="M15" s="3" t="n"/>
-      <c r="N15" s="3" t="n"/>
+      <c r="N15" s="3">
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <v/>
+      </c>
       <c r="O15" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P15" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q15" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R15" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S15" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T15" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U15" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V15" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W15" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="X15" s="3">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
-      <c r="Y15" s="3">
+      <c r="X15">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="Z15">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"MARA"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -5322,12 +5094,12 @@
       <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="n"/>
       <c r="M16" s="3" t="n"/>
-      <c r="N16" s="3" t="n"/>
-      <c r="O16" s="3" t="inlineStr">
+      <c r="N16" s="3" t="inlineStr">
         <is>
           <t>LUGO</t>
         </is>
       </c>
+      <c r="O16" s="3" t="n"/>
       <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="n"/>
       <c r="R16" s="3" t="n"/>
@@ -5336,8 +5108,6 @@
       <c r="U16" s="3" t="n"/>
       <c r="V16" s="3" t="n"/>
       <c r="W16" s="3" t="n"/>
-      <c r="X16" s="3" t="n"/>
-      <c r="Y16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
@@ -5353,53 +5123,48 @@
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="n"/>
       <c r="M17" s="3" t="n"/>
-      <c r="N17" s="3" t="n"/>
+      <c r="N17" s="3">
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <v/>
+      </c>
       <c r="O17" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P17" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q17" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R17" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S17" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T17" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U17" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V17" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W17" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="X17" s="3">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
-      <c r="Y17" s="3">
+      <c r="X17">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="Z17">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -5417,53 +5182,48 @@
       <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="n"/>
       <c r="M18" s="3" t="n"/>
-      <c r="N18" s="3" t="n"/>
+      <c r="N18" s="3">
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <v/>
+      </c>
       <c r="O18" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P18" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q18" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R18" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S18" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T18" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U18" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V18" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W18" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="X18" s="3">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
-      <c r="Y18" s="3">
+      <c r="X18">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="Z18">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -5481,53 +5241,48 @@
       <c r="K19" s="3" t="n"/>
       <c r="L19" s="3" t="n"/>
       <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3" t="n"/>
+      <c r="N19" s="3">
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <v/>
+      </c>
       <c r="O19" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P19" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q19" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R19" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S19" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T19" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U19" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V19" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W19" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="X19" s="3">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
-      <c r="Y19" s="3">
+      <c r="X19">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="Z19">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -5545,53 +5300,48 @@
       <c r="K20" s="3" t="n"/>
       <c r="L20" s="3" t="n"/>
       <c r="M20" s="3" t="n"/>
-      <c r="N20" s="3" t="n"/>
+      <c r="N20" s="3">
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <v/>
+      </c>
       <c r="O20" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P20" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q20" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R20" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S20" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T20" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U20" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V20" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W20" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="X20" s="3">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
-      <c r="Y20" s="3">
+      <c r="X20">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="Z20">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -5609,53 +5359,48 @@
       <c r="K21" s="3" t="n"/>
       <c r="L21" s="3" t="n"/>
       <c r="M21" s="3" t="n"/>
-      <c r="N21" s="3" t="n"/>
+      <c r="N21" s="3">
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <v/>
+      </c>
       <c r="O21" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P21" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q21" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R21" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S21" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T21" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U21" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V21" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W21" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="X21" s="3">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
-      <c r="Y21" s="3">
+      <c r="X21">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="Z21">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"LUGO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -5673,12 +5418,12 @@
       <c r="K22" s="3" t="n"/>
       <c r="L22" s="3" t="n"/>
       <c r="M22" s="3" t="n"/>
-      <c r="N22" s="3" t="n"/>
-      <c r="O22" s="3" t="inlineStr">
+      <c r="N22" s="3" t="inlineStr">
         <is>
           <t>ROTO</t>
         </is>
       </c>
+      <c r="O22" s="3" t="n"/>
       <c r="P22" s="3" t="n"/>
       <c r="Q22" s="3" t="n"/>
       <c r="R22" s="3" t="n"/>
@@ -5687,8 +5432,6 @@
       <c r="U22" s="3" t="n"/>
       <c r="V22" s="3" t="n"/>
       <c r="W22" s="3" t="n"/>
-      <c r="X22" s="3" t="n"/>
-      <c r="Y22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
@@ -5704,53 +5447,48 @@
       <c r="K23" s="3" t="n"/>
       <c r="L23" s="3" t="n"/>
       <c r="M23" s="3" t="n"/>
-      <c r="N23" s="3" t="n"/>
+      <c r="N23" s="3">
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <v/>
+      </c>
       <c r="O23" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P23" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q23" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R23" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S23" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T23" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U23" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V23" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W23" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="X23" s="3">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
-      <c r="Y23" s="3">
+      <c r="X23">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="Z23">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"1")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -5768,53 +5506,48 @@
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="n"/>
       <c r="M24" s="3" t="n"/>
-      <c r="N24" s="3" t="n"/>
+      <c r="N24" s="3">
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <v/>
+      </c>
       <c r="O24" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P24" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q24" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R24" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S24" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T24" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U24" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V24" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W24" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="X24" s="3">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
-      <c r="Y24" s="3">
+      <c r="X24">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="Z24">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"2")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -5832,53 +5565,48 @@
       <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="n"/>
       <c r="M25" s="3" t="n"/>
-      <c r="N25" s="3" t="n"/>
+      <c r="N25" s="3">
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <v/>
+      </c>
       <c r="O25" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P25" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q25" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R25" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S25" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T25" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U25" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V25" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W25" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="X25" s="3">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
-      <c r="Y25" s="3">
+      <c r="X25">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="Z25">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"3")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -5896,53 +5624,48 @@
       <c r="K26" s="3" t="n"/>
       <c r="L26" s="3" t="n"/>
       <c r="M26" s="3" t="n"/>
-      <c r="N26" s="3" t="n"/>
+      <c r="N26" s="3">
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <v/>
+      </c>
       <c r="O26" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P26" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q26" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R26" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S26" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T26" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U26" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V26" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W26" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="X26" s="3">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
-      <c r="Y26" s="3">
+      <c r="X26">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="Z26">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"4")*1,0),0))))</f>
         <v/>
       </c>
     </row>
@@ -5960,53 +5683,48 @@
       <c r="K27" s="3" t="n"/>
       <c r="L27" s="3" t="n"/>
       <c r="M27" s="3" t="n"/>
-      <c r="N27" s="3" t="n"/>
+      <c r="N27" s="3">
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <v/>
+      </c>
       <c r="O27" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$B$4:$B$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="P27" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$C$4:$C$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="Q27" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$D$4:$D$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="R27" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$E$4:$E$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="S27" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$F$4:$F$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="T27" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$G$4:$G$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="U27" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$H$4:$H$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="V27" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$I$4:$I$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
+        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
       <c r="W27" s="3">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$J$4:$J$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="X27" s="3">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$K$4:$K$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
-      <c r="Y27" s="3">
+      <c r="X27">
         <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$L$4:$L$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
-        <v/>
-      </c>
-      <c r="Z27">
-        <f>IF(ISNA(MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0)),"",IF(ISBLANK(INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))),"",INDEX('Detalle - Lo que imparte'!$M$4:$M$11,MATCH(1,INDEX(EXACT('Detalle - Lo que imparte'!$A$4:$A$11,"ROTO"&amp;CHAR(30)&amp;"5")*1,0),0))))</f>
         <v/>
       </c>
     </row>

--- a/ejemplos/resultados/departamento.xlsx
+++ b/ejemplos/resultados/departamento.xlsx
@@ -2756,7 +2756,7 @@
       <c r="A30" s="7" t="n"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>sobrecarga</t>
+          <t>El profesor pasa de su tope de horas</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
       <c r="A30" s="6" t="n"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>cobertura incompleta</t>
+          <t>La asignatura no tiene cubiertas todas sus horas</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       <c r="A31" s="8" t="n"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>cobertura completa</t>
+          <t>La asignatura tiene cubiertas todas sus horas</t>
         </is>
       </c>
     </row>
